--- a/workspaces/nasdaq_hourly_24hrs/macd/macd_histogram_12_26.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/macd/macd_histogram_12_26.xlsx
@@ -618,247 +618,247 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.003462</t>
+          <t>X ≈ -0.003461</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>15</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-6.958450918531256</v>
+        <v>-6.925468336236435</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>12.5752734344912</v>
+        <v>12.60881828919685</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.14772990867415</v>
+        <v>11.18294187791616</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>17.06870178058629</v>
+        <v>17.10479631780503</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.080181788236</v>
+        <v>10.14554651198183</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.27017603658398</v>
+        <v>10.33535893019047</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.871364941683638</v>
+        <v>2.937431906397364</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.595037803099181</v>
+        <v>2.661463684167842</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.274108788467302</v>
+        <v>9.34056066339808</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>15.14527596281241</v>
+        <v>15.2126894793408</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>22.06384923642267</v>
+        <v>22.13101165301274</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>15.14937328101009</v>
+        <v>15.21686229129224</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>20.67813972973091</v>
+        <v>20.74698966613148</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>20.46317670027262</v>
+        <v>20.53231759493858</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>19.81259898099321</v>
+        <v>19.88253619727286</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>20.41203766600299</v>
+        <v>20.48131962774706</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>13.63168201983667</v>
+        <v>13.70113683089994</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>13.53084355513151</v>
+        <v>13.60045719119979</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>13.75050599302113</v>
+        <v>13.81990542942136</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>7.282754535634311</v>
+        <v>7.351963214053171</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>13.40295505783835</v>
+        <v>13.47284234829105</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.005740892805363274</v>
+        <v>0.07574407166104891</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.2804838131331309</v>
+        <v>0.3502079943754453</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.2046783625730981</v>
+        <v>0.2745327102788622</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.003213</t>
+          <t>X ≈ -0.003211</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>13</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-15.10676798926279</v>
+        <v>-15.07385567933158</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-15.44503739432228</v>
+        <v>-15.41171435442537</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-32.16885987935229</v>
+        <v>-32.13397545011695</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-17.59532032617742</v>
+        <v>-17.55947492792441</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-25.61365883721538</v>
+        <v>-25.54854008288658</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-17.78345990443447</v>
+        <v>-17.7184606093068</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-18.55759438103326</v>
+        <v>-18.49166112185159</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-18.84032061789703</v>
+        <v>-18.77402069400449</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-18.80462405453198</v>
+        <v>-18.73832559290889</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-19.58075045539072</v>
+        <v>-19.51351324124511</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-11.65113089062439</v>
+        <v>-11.58412694367732</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.268145741399181</v>
+        <v>-4.200741707754865</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>9.943869243234765</v>
+        <v>10.01267602608241</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.056510862398611</v>
+        <v>2.125584831299712</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>1.400479131326968</v>
+        <v>1.470356011705249</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>1.994427117433517</v>
+        <v>2.063655460788794</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>9.537502557251855</v>
+        <v>9.606946346105204</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-5.921417927251639</v>
+        <v>-5.851847024558232</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-5.70757074229482</v>
+        <v>-5.638206923255353</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-5.522419387485712</v>
+        <v>-5.453229748169278</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-6.066749817740508</v>
+        <v>-5.996883932598109</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1.543276168089811</v>
+        <v>1.613280102132066</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-5.871512147795414</v>
+        <v>-5.801790367696654</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>1.743139901034638</v>
+        <v>1.812994248741916</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.002963</t>
+          <t>X ≈ -0.002962</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>29</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>14.92775597883346</v>
+        <v>16.54846634298178</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.154355603930291</v>
+        <v>5.911170502046033</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.676324516366314</v>
+        <v>4.336505344672531</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.340854669577745</v>
+        <v>-6.732851390224809</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-10.1424000813003</v>
+        <v>-12.0105035506228</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.766150002412502</v>
+        <v>3.833613557035548</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.4606300949165174</v>
+        <v>-0.3922258149888975</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.7478678453294307</v>
+        <v>-0.6790897525516115</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.728384226790105</v>
+        <v>2.797172005640171</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.503573802047718</v>
+        <v>-1.433836570661825</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.216594991074338</v>
+        <v>2.286059560973996</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.931126536099811</v>
+        <v>2.000964508265767</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>7.647582527207113</v>
+        <v>7.718834571952932</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.5473917013632317</v>
+        <v>0.6189226437442841</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>3.30212479783571</v>
+        <v>3.374505621004509</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>3.918934274307809</v>
+        <v>3.990640783592106</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>3.78057115267616</v>
+        <v>3.852481933031001</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-1.155428244618918</v>
+        <v>-3.140844652882237</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-4.383214976322698</v>
+        <v>-6.358620991091087</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-4.197686158425405</v>
+        <v>-6.167201935979463</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-4.741629184269911</v>
+        <v>-6.729452185999243</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-1.372738346350268</v>
+        <v>-1.30273707421928</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>5.796055176940307</v>
+        <v>5.86578092630306</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>9.170195603952415</v>
+        <v>9.240049951659692</v>
       </c>
     </row>
     <row r="9">
@@ -871,240 +871,240 @@
         <v>37</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>11.1197672847029</v>
+        <v>6.83183524779006</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.640416976702319</v>
+        <v>-5.51698352605559</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.300223644501919</v>
+        <v>-0.1553760409658196</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.5912786431746397</v>
+        <v>0.6275805792916316</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-7.836305833924349</v>
+        <v>-7.773329971799129</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.963863615132759</v>
+        <v>-4.898772641734311</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.734162276355384</v>
+        <v>-5.668141383844301</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.6325232014312121</v>
+        <v>-0.5661090835064044</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.5915225776894601</v>
+        <v>-0.5251153540560338</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.329735415652472</v>
+        <v>1.39708865058914</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.089675725700303</v>
+        <v>-1.022610054379939</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>12.09971027094177</v>
+        <v>12.16719576206695</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2045284656944872</v>
+        <v>0.2733113909309637</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.01625526457662119</v>
+        <v>0.05282606272655244</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.6731582176245965</v>
+        <v>-0.6032719947274998</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-2.776586019435577</v>
+        <v>-2.707354259345379</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-11.00438641947618</v>
+        <v>-10.93497418225673</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-5.713625276481608</v>
+        <v>-5.645752186361918</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-5.499730696232383</v>
+        <v>-5.431974373383937</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-5.314574924719217</v>
+        <v>-5.246939181793962</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-8.559091142030049</v>
+        <v>-8.491778558574829</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-5.936556738581203</v>
+        <v>-5.866559818919221</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-2.961777114444246</v>
+        <v>-2.89205501227508</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-3.038564880670144</v>
+        <v>-2.968710532962866</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.002465</t>
+          <t>X ≈ -0.002463</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>52</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.589689148359248</v>
+        <v>9.634948516238495</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>14.97494521638847</v>
+        <v>15.02717158198169</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.020445404116366</v>
+        <v>2.058208051931416</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.84618394989041</v>
+        <v>10.89025380597614</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>14.30156665410232</v>
+        <v>14.37348917286194</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.758436022023133</v>
+        <v>8.826273984601315</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.3008476592998974</v>
+        <v>0.3696111380140295</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-13.39272548459219</v>
+        <v>-13.32365478974837</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-7.605107726713712</v>
+        <v>-7.536013548581167</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.493178337744794</v>
+        <v>-6.423098994118611</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-10.04273594294136</v>
+        <v>-9.972958600595483</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.7392895317431467</v>
+        <v>-0.669103719440038</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>7.684042790581053</v>
+        <v>7.755660535988035</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.621155623403737</v>
+        <v>3.693069033176087</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>2.933668021969943</v>
+        <v>3.006426510502749</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.207562813517981</v>
+        <v>-2.135492173419493</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>4.555753903210871</v>
+        <v>3.482220636913659</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>4.449148374118892</v>
+        <v>3.374318748101977</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>3.893329297853086</v>
+        <v>1.681411361627994</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>4.081359804752957</v>
+        <v>1.876279127693536</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>9.30382181246555</v>
+        <v>8.229504954601673</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>5.387036819340942</v>
+        <v>4.308703325807535</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>5.663413850710377</v>
+        <v>5.733138634954955</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-2.103013945119216</v>
+        <v>-2.033159597411938</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.002215</t>
+          <t>X ≈ -0.002214</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>61</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.679668324175204</v>
+        <v>3.717839342893946</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6.605722237797643</v>
+        <v>6.647967572037722</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.917231388842353</v>
+        <v>1.954310461808824</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.468522492902068</v>
+        <v>4.507438227483597</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.736914537593726</v>
+        <v>5.804247363385699</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.232502832811811</v>
+        <v>-2.167371651671736</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.001688112036064</v>
+        <v>-2.935627675349657</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.911947297582678</v>
+        <v>-4.845533380354091</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.239597536479167</v>
+        <v>-3.173178473779366</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.378098164370378</v>
+        <v>-2.310735303408279</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.373761249804879</v>
+        <v>-5.306685070932538</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.8838445009644573</v>
+        <v>0.9513143231068071</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.872746428864559</v>
+        <v>-1.803937344157703</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.458383026314614</v>
+        <v>-0.3892689317175808</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>5.429086936031815</v>
+        <v>5.499024187942233</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>4.388297847384358</v>
+        <v>4.457582222763506</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>4.254451474988272</v>
+        <v>4.325313635772133</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>4.149616451944901</v>
+        <v>4.221952835579849</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>4.3652449713707</v>
+        <v>4.438996968173484</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>4.553460806746592</v>
+        <v>4.627211867311509</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>7.28777666257583</v>
+        <v>7.362461432952436</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>8.852552893067262</v>
+        <v>8.925458927560889</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>7.491266384259269</v>
+        <v>7.560991255323742</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>9.057137378966537</v>
+        <v>9.126991726674198</v>
       </c>
     </row>
     <row r="12">
@@ -1117,240 +1117,240 @@
         <v>71</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.804076946915309</v>
+        <v>1.840016921826582</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.548527451222505</v>
+        <v>-5.521734590713194</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.13309823005072</v>
+        <v>1.394105091565024</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.611223104829243</v>
+        <v>4.868347251139937</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3653174987757808</v>
+        <v>-1.086607271966258</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.38615288488409</v>
+        <v>-5.108578752008214</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.781596109073369</v>
+        <v>-3.713473030372647</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.670080503792406</v>
+        <v>-2.601568541704005</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1832735254282767</v>
+        <v>0.2517890155584013</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.014505102119763</v>
+        <v>-1.945028641963994</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.07472032174892</v>
+        <v>1.14392592190049</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.6040913696939612</v>
+        <v>-0.5345267549033181</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.3525269122697594</v>
+        <v>-0.2815699223034045</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.8267016477867699</v>
+        <v>0.8979716914341651</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>2.962117229262169</v>
+        <v>3.034228329283131</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.219574097613183</v>
+        <v>-1.984516736262549</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.35569482099968</v>
+        <v>-2.123916620215248</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.05527469055461864</v>
+        <v>-0.8246022174671737</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.164902530853297</v>
+        <v>-0.6005446502286631</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>3.999780727033311</v>
+        <v>3.241748824024803</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.6442213284386824</v>
+        <v>-0.1235132519645461</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-2.246450705911975</v>
+        <v>-3.016707891022229</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.5644033728180275</v>
+        <v>-1.328862513137615</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-3.457293468412814</v>
+        <v>-3.387439120705537</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.001717</t>
+          <t>X ≈ -0.001716</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4.140298418653401</v>
+        <v>4.100112026862099</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.185567394807009</v>
+        <v>-3.101419741770378</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.771608444713181</v>
+        <v>-3.674708033004997</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-9.733381765927916</v>
+        <v>-9.537238276080075</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-12.72738204101658</v>
+        <v>-12.44749019105711</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-7.302329782598846</v>
+        <v>-7.108595761742912</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.594690566461843</v>
+        <v>-4.442266919690624</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.3835703241229</v>
+        <v>-1.284787499440831</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.338619890676092</v>
+        <v>-1.244790473717181</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.125536491667454</v>
+        <v>-2.015675478021727</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.099752059218517</v>
+        <v>-6.901674258386862</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-11.75709524393734</v>
+        <v>-11.48341229949767</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-8.523589613548779</v>
+        <v>-8.306465083269174</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.998132634866145</v>
+        <v>-6.808723499765541</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-9.423814172139522</v>
+        <v>-9.189976187679626</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-10.57483337235342</v>
+        <v>-10.32139631390984</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-4.57546279674132</v>
+        <v>-4.428235494150634</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-5.558142346651927</v>
+        <v>-5.396307559553961</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-3.583339968631812</v>
+        <v>-3.458080670950416</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.7615642978363937</v>
+        <v>-0.6850279644308657</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.08537669048627805</v>
+        <v>-0.3655051668796432</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.3450153162241136</v>
+        <v>-1.303420093805997</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.824167408146096</v>
+        <v>-2.753083312358413</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-5.409356725146196</v>
+        <v>-6.277191427650855</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.001467</t>
+          <t>X ≈ -0.001466</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-8.757849933124369</v>
+        <v>-8.667812023085808</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-6.214639976618713</v>
+        <v>-6.138604745588871</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-13.44266175989794</v>
+        <v>-13.31475279697172</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-6.950654271438118</v>
+        <v>-6.86371541974281</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-8.767549140489713</v>
+        <v>-8.634203808921299</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-8.582625744186139</v>
+        <v>-8.446906290737182</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-7.923852877337389</v>
+        <v>-7.788464375123155</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-4.595404909917036</v>
+        <v>-4.48644202636865</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-7.444584892980977</v>
+        <v>-7.314127052652069</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-6.062025542580535</v>
+        <v>-5.941282619054611</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-7.23565108940884</v>
+        <v>-7.104186287574699</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-11.8605019947548</v>
+        <v>-11.69293706428463</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-7.934149072678579</v>
+        <v>-7.798636173209836</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-10.33320228047731</v>
+        <v>-10.17841554416422</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-6.22043856202778</v>
+        <v>-6.532854381075865</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-7.071580907460863</v>
+        <v>-7.376362060947493</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-5.756447456301998</v>
+        <v>-6.074340715385965</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-5.862128891686744</v>
+        <v>-6.182254838670062</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-6.367594551155264</v>
+        <v>-6.255153357628849</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-5.453377778820581</v>
+        <v>-5.348883087229176</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-5.275454711610905</v>
+        <v>-5.172004794763545</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-5.35234045963908</v>
+        <v>-5.247850756172646</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.472255176395336</v>
+        <v>-2.815102662395631</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.824307144673277</v>
+        <v>-2.171510455187416</v>
       </c>
     </row>
     <row r="15">
@@ -1360,79 +1360,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.787417123332517</v>
+        <v>-3.728930882148624</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.179081619754406</v>
+        <v>-6.101769931741714</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.928997993632144</v>
+        <v>-2.86881352224956</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.271525733338954</v>
+        <v>-3.591220433944862</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.905510200080187</v>
+        <v>-2.592078195267646</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.6511287967849526</v>
+        <v>-1.728622438226417</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.75440571293376</v>
+        <v>-5.216841651986634</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.39306356935203</v>
+        <v>-6.456460404640929</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.995062532754801</v>
+        <v>-4.674242366259158</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.416345247987771</v>
+        <v>-3.712469341948143</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.10469241377767</v>
+        <v>-1.021269539774444</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.464305399359205</v>
+        <v>-5.345256350229079</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.596278493123812</v>
+        <v>-6.469212970138614</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.141596053223431</v>
+        <v>-6.017862091578692</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-4.763567930202406</v>
+        <v>-4.653013818787052</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-2.805794120378259</v>
+        <v>-2.710394523282787</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-6.340284117626688</v>
+        <v>-6.222744464897566</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-3.724902279186374</v>
+        <v>-3.627373729414536</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-3.506127453179772</v>
+        <v>-3.41148234849021</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-2.635677765081923</v>
+        <v>-2.548960862846513</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.141195631183145</v>
+        <v>-1.064480003785519</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-2.578659145630866</v>
+        <v>-2.491677316545811</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-5.702110739732852</v>
+        <v>-5.595580982442449</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-4.69328082110038</v>
+        <v>-4.995737559989742</v>
       </c>
     </row>
     <row r="16">
@@ -1445,650 +1445,650 @@
         <v>193</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.413239392054734</v>
+        <v>-2.379965099735905</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.932767808607281</v>
+        <v>2.966440817220622</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.02974100800396</v>
+        <v>3.065095431672447</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6.449270576980503</v>
+        <v>6.485464294399407</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.943220463350478</v>
+        <v>2.008893493246156</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.717091033129883</v>
+        <v>4.782565636116153</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6.003894986127001</v>
+        <v>6.070287037276948</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.922772731456035</v>
+        <v>2.687344845140281</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.8966817471710371</v>
+        <v>0.6626366763723652</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.9152139917615045</v>
+        <v>-1.150678757974205</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.9122967289490447</v>
+        <v>0.6762123482817302</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.404746465653588</v>
+        <v>-0.3343133806763561</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.056437895496067</v>
+        <v>1.1254388933569</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1102735690872763</v>
+        <v>-0.1313716294526017</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1.005746475127452</v>
+        <v>0.761030444270375</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>2.637075954800764</v>
+        <v>2.393158685266634</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.575521120755226</v>
+        <v>4.332079080096165</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>3.952402989634166</v>
+        <v>4.02211513769079</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.614122007488376</v>
+        <v>2.683602373537511</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.24676165803109</v>
+        <v>1.316044038427819</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.887112326096407</v>
+        <v>-1.817175704667754</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.481202096765031</v>
+        <v>-2.41115638110287</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-4.278965790386295</v>
+        <v>-4.209220528724209</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-2.800502984577157</v>
+        <v>-2.73064863686988</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.0007189</t>
+          <t>X ≈ -0.000719</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>210</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.8537003358609283</v>
+        <v>-0.8204260435420991</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.2413761090203721</v>
+        <v>-0.2077031004070307</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2688888899917075</v>
+        <v>-0.2335344663232206</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.885919803529262</v>
+        <v>-2.849726086110358</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.355860580888752</v>
+        <v>-1.290187550993075</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.165730245627032</v>
+        <v>-1.100255642640761</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.946504970360799</v>
+        <v>-1.880112919210852</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.753781180349428</v>
+        <v>-1.687045928433996</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.434551485702272</v>
+        <v>-1.644570172434356</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.3098440003943423</v>
+        <v>-0.5224863655010807</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4412024147556437</v>
+        <v>0.2297717307857852</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.6354503675212584</v>
+        <v>0.4223007628676001</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.2062428002387193</v>
+        <v>-0.421323584681538</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.429543245869674</v>
+        <v>2.21049598335582</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.246802483022954</v>
+        <v>2.027065754930639</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.889481580263386</v>
+        <v>1.672047399283485</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.6255644948378105</v>
+        <v>-0.5559950590552845</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.682928863314046</v>
+        <v>-1.613216715257423</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.03823427181090722</v>
+        <v>0.03124609423822733</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-3.18452380952381</v>
+        <v>-3.115241429127082</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.775343266140816</v>
+        <v>-2.705406644712163</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-2.851298321783425</v>
+        <v>-2.781252606121264</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-3.528904107682244</v>
+        <v>-3.459158846020159</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-4.081035923141187</v>
+        <v>-4.011181575433909</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.0004696</t>
+          <t>X ≈ -0.0004698</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>205</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.670395783979515</v>
+        <v>1.703670076298344</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.283006727393079</v>
+        <v>3.316679736006421</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.348930285623801</v>
+        <v>1.384284709292288</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.121267645325503</v>
+        <v>1.157461362744407</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2657445350125798</v>
+        <v>0.3314175649082571</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.007544196861943</v>
+        <v>-0.9420695938756722</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.2465323208394</v>
+        <v>-3.180140269689453</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.527148292554919</v>
+        <v>-3.460413040639487</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.485116895982998</v>
+        <v>-3.418410527175496</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.802051155455374</v>
+        <v>-2.732418852978235</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.5765735311171483</v>
+        <v>-0.5074807634629863</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.5683950196145346</v>
+        <v>-0.788291493108062</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.7172764820042232</v>
+        <v>-0.9397075457239836</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.9386332930384711</v>
+        <v>-1.162000092414395</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-2.085369410124663</v>
+        <v>-2.310949230011815</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.490309360503282</v>
+        <v>-1.420916481892206</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.790231091689371</v>
+        <v>1.859800527471897</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.685247675594091</v>
+        <v>1.754959823650715</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.5376535517179946</v>
+        <v>-0.46817318566886</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.814024390243794</v>
+        <v>-1.744742009847066</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.8938101650956298</v>
+        <v>-0.8238735436669771</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.005844535359322833</v>
+        <v>0.07589025102148383</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.23183921403669</v>
+        <v>2.301584475698775</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.643702752816893</v>
+        <v>2.71355710052417</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.0002203</t>
+          <t>X ≈ -0.0002205</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.018792114753339</v>
+        <v>-1.791324855175127</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.104842382185012</v>
+        <v>-3.255739093352794</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.312564926987271</v>
+        <v>-2.077449479042492</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-4.152127044648729</v>
+        <v>-3.920404516504249</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-6.022044067047773</v>
+        <v>-5.766498794987918</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.960046979160794</v>
+        <v>-3.697651891623579</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-5.117224791247153</v>
+        <v>-4.855357036298344</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.400126034466346</v>
+        <v>-5.137931419344824</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-7.230182496048599</v>
+        <v>-6.975052750977305</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-4.415466214305575</v>
+        <v>-4.369963453264113</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.917692456232892</v>
+        <v>-4.091177294617459</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.046659333176187</v>
+        <v>0.8888682583777268</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.201427390928842</v>
+        <v>-1.367567030217351</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.546379707581266</v>
+        <v>-2.490066001918663</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.83077911141249</v>
+        <v>-2.545286899158668</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-4.857441908233049</v>
+        <v>-4.582478924584187</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-4.617003767176065</v>
+        <v>-4.340456211937514</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-4.347455348065353</v>
+        <v>-4.069357066134728</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-4.880395855545522</v>
+        <v>-4.605345384458602</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-4.31882022471919</v>
+        <v>-4.042559724866422</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-5.611084304128951</v>
+        <v>-5.336985592080488</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-4.56344385415359</v>
+        <v>-4.285012004617329</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-5.037732358083524</v>
+        <v>-4.762416991383567</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-4.739141862145914</v>
+        <v>-4.462309394982697</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 2.903e-05</t>
+          <t>X ≈ 2.878e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.83847557192999</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.231519142617302</v>
+        <v>-1.011197034311422</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.083918019401899</v>
+        <v>-1.263445332354273</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.400885935769708</v>
+        <v>-1.581142434800924</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1788541334920239</v>
+        <v>-0.3359052393640525</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.959943488739206</v>
+        <v>-4.10150822322715</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.161381049364749</v>
+        <v>-1.316144654153071</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.043110298057918</v>
+        <v>-1.199099181910192</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.588895820336866</v>
+        <v>-2.738639667979498</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.362731231106295</v>
+        <v>-3.511555344016081</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.866149741768737</v>
+        <v>-6.004294120826572</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.335719835719836</v>
+        <v>-7.468814275262538</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-4.491957085953004</v>
+        <v>-4.63940717215818</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-6.300615484288947</v>
+        <v>-6.441513716589043</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-6.562721326500856</v>
+        <v>-6.704400097173554</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-5.967661276879475</v>
+        <v>-6.110013175230478</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-7.292231161504581</v>
+        <v>-7.429701063196269</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-8.984516164901457</v>
+        <v>-9.115569435001554</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-7.577916811493445</v>
+        <v>-7.713907303088995</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-7.390873015873012</v>
+        <v>-7.527061493121145</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-8.330898821696358</v>
+        <v>-8.46486457808313</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-8.010028480513576</v>
+        <v>-8.145453622496277</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-9.322554901333042</v>
+        <v>-9.452006577998326</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-8.604845446950712</v>
+        <v>-8.7373249972295</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0002784</t>
+          <t>X ≈ 0.000278</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.060572471800228</v>
+        <v>2.916529935748358</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.684580630625284</v>
+        <v>0.5325728095297393</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4.142839350212626</v>
+        <v>4.422422612957718</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.020882771713296</v>
+        <v>2.889796462367393</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.063776251995364</v>
+        <v>2.963842055393883</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.25094086500215</v>
+        <v>3.150808241491319</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.335217590091034</v>
+        <v>5.247712016617356</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>5.464826209878588</v>
+        <v>5.379336637438051</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5.914505540207351</v>
+        <v>5.830659884926526</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.916180333519549</v>
+        <v>3.828236012168723</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.966049804716519</v>
+        <v>3.282623523183155</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.870629370629374</v>
+        <v>2.18420198858756</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.7461381521422297</v>
+        <v>1.061039921731442</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.198250728862973</v>
+        <v>4.528485635448803</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.5423131632355407</v>
+        <v>-0.2280183178694699</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.05274688638584024</v>
+        <v>0.3663686040734788</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>2.367632784073642</v>
+        <v>2.691467860538673</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>3.89530242920285</v>
+        <v>4.225971419012524</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>3.295099061522421</v>
+        <v>3.622190668789358</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>2.66581632653061</v>
+        <v>2.989364347609843</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>3.755268978757144</v>
+        <v>4.086162441938903</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>3.679313923114535</v>
+        <v>4.010316480529802</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>2.729599293678305</v>
+        <v>3.055282996290487</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>3.469984485022081</v>
+        <v>3.799122874214802</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.0005277</t>
+          <t>X ≈ 0.0005273</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>282</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.999637459497428</v>
+        <v>2.032911751816258</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.309852015775093</v>
+        <v>1.698134953466408</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5793714098449811</v>
+        <v>0.2601159044354517</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.347847600197966</v>
+        <v>2.384041317616827</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.982577815173919</v>
+        <v>2.048250845069632</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.105912640946656</v>
+        <v>1.171387243932898</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.751486225204644</v>
+        <v>1.817878276354634</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.827541508764106</v>
+        <v>1.894276760679489</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.996717148254859</v>
+        <v>4.063423517062326</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.095222163017311</v>
+        <v>1.162848266557781</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.7580781443354425</v>
+        <v>-1.045361594826467</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.02665773942369754</v>
+        <v>-0.2602812110403789</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.7432235499854301</v>
+        <v>-1.028833348818488</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.8014597936439</v>
+        <v>-4.086791657889187</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.332731458213161</v>
+        <v>-2.617275381001654</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.383061479513721</v>
+        <v>-1.668278529980611</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-3.644814748130692</v>
+        <v>-3.929855241426175</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.395188235147948</v>
+        <v>-3.680086016169305</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-2.824455143138159</v>
+        <v>-3.109584706167048</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.5097517730496506</v>
+        <v>-0.7950793217308885</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.7200974633424764</v>
+        <v>0.4354241556931058</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>2.062582124011911</v>
+        <v>1.778017910596063</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>3.046577148650073</v>
+        <v>2.761712481234191</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>2.970635809381605</v>
+        <v>2.685880228010873</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.0007771</t>
+          <t>X ≈ 0.0007765</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.550525900132783</v>
+        <v>-2.244199068739192</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.4850851020768232</v>
+        <v>0.2143202222964646</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.416171154844577</v>
+        <v>2.686915698405109</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.949568852887317</v>
+        <v>4.208598550470747</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>6.393287831908275</v>
+        <v>6.666104167308887</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>6.018654692106068</v>
+        <v>6.294411135529231</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>9.740170582523952</v>
+        <v>9.99173619465558</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>8.899818184196405</v>
+        <v>9.154865532025539</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>7.817738743600998</v>
+        <v>8.079034278185986</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.920307827213598</v>
+        <v>6.188800166395168</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.509273835902022</v>
+        <v>4.786882154925941</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.982988921191172</v>
+        <v>2.273495879969566</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.42029545551302</v>
+        <v>1.708993030990534</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.884331902905622</v>
+        <v>3.163891808175237</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.787198416677448</v>
+        <v>3.064407728471835</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.696865207871738</v>
+        <v>1.982816996783477</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.124569266531672</v>
+        <v>2.407559077682976</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.3341925920094155</v>
+        <v>0.6267407202305009</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.67391126055935</v>
+        <v>1.959950536909147</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>3.546348314606739</v>
+        <v>3.822774000508403</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>4.126743411226762</v>
+        <v>4.39754626829663</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.488990602775168</v>
+        <v>3.763041089010422</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>5.449159027684267</v>
+        <v>5.713493455123768</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>5.373217688415799</v>
+        <v>5.637661201900492</v>
       </c>
     </row>
     <row r="24">
@@ -2101,76 +2101,76 @@
         <v>164</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.6253409179459481</v>
+        <v>-0.592066625627119</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.527288445458503</v>
+        <v>4.560961454071844</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.477831883811419</v>
+        <v>2.513186307479906</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.06522972206465738</v>
+        <v>-0.02903600464575362</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.25976779977163</v>
+        <v>-2.194094769875953</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.585933398601</v>
+        <v>1.651408001587271</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.2033111689859979</v>
+        <v>0.2697032201359448</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.144268718589423</v>
+        <v>1.211003970504855</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.472751801753866</v>
+        <v>-2.406045432946364</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.021705470403646</v>
+        <v>1.089331573944087</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.125333030201801</v>
+        <v>3.192659508788829</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.285263516970801</v>
+        <v>5.352934495584734</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.551016200922717</v>
+        <v>3.620016331167676</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.378439877693275</v>
+        <v>6.447717942525998</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>8.768289126460751</v>
+        <v>8.838355132750216</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>6.924324785838301</v>
+        <v>6.993717664449377</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>8.619499384372375</v>
+        <v>8.689068820154901</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>7.295003773155145</v>
+        <v>7.364715921211769</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>5.681858643403963</v>
+        <v>5.751339009453098</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.429878048780488</v>
+        <v>3.499160429177216</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>5.935458127587417</v>
+        <v>6.00539474901607</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>4.639990876822857</v>
+        <v>4.710036592485018</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.865985555500103</v>
+        <v>1.935730817162188</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.619312508914561</v>
+        <v>3.689166856621839</v>
       </c>
     </row>
     <row r="25">
@@ -2183,76 +2183,76 @@
         <v>123</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.610431439777706</v>
+        <v>1.643705732096535</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-6.041817245598331</v>
+        <v>-6.00814423698499</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.461571721209793</v>
+        <v>1.49692614487828</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.504254112308608</v>
+        <v>-2.468060394889704</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.195516753073896</v>
+        <v>1.261189782969574</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.008697626243325</v>
+        <v>3.074172229229596</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.455225416379847</v>
+        <v>-3.3888333652299</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.3312605885080515</v>
+        <v>0.3979958404234836</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.62480917385593</v>
+        <v>3.691515542663431</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.663981893167801</v>
+        <v>3.731607996708242</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.190373680608388</v>
+        <v>7.257700159195416</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>7.724287907214787</v>
+        <v>7.79195888582872</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>6.599796688727601</v>
+        <v>6.668796818972559</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.378439877693204</v>
+        <v>6.447717942525927</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>6.532516768737231</v>
+        <v>6.602582775026697</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>12.00562559884643</v>
+        <v>12.0750184774575</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>7.806491254291004</v>
+        <v>7.87606069007353</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>8.514515968277024</v>
+        <v>8.584228116333648</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>7.917631001127539</v>
+        <v>7.987111367176674</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>11.35670731707317</v>
+        <v>11.4259896974699</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>10.00049877799392</v>
+        <v>10.07043539942257</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>13.17657624267651</v>
+        <v>13.24662195833867</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>9.386310758752096</v>
+        <v>9.456056020414181</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>8.49736128940237</v>
+        <v>8.567215637109648</v>
       </c>
     </row>
     <row r="26">
@@ -2265,240 +2265,240 @@
         <v>111</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.421869153498598</v>
+        <v>-1.388594861179769</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.657945569043797</v>
+        <v>-2.624272560430455</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-6.800348735832607</v>
+        <v>-6.76499431216412</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-7.514142049025665</v>
+        <v>-7.477948331606761</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-5.176709131347117</v>
+        <v>-5.11103610145144</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-6.791346320142132</v>
+        <v>-6.725871717155862</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.96060884859255</v>
+        <v>-3.894216797442603</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.43736169230926</v>
+        <v>-2.370626440393828</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.811361579920629</v>
+        <v>4.87806794872813</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.740228871853752</v>
+        <v>6.807854975394193</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.113687238068188</v>
+        <v>6.181013716655215</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.834593334593386</v>
+        <v>5.902264313207318</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.412804818808887</v>
+        <v>7.481804949053846</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.389646205972745</v>
+        <v>5.458924270805468</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.631615867836352</v>
+        <v>5.701681874125818</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>7.196969696969688</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>6.09258222330881</v>
+        <v>6.162151659091336</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>5.086697906312622</v>
+        <v>5.156410054369246</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>6.203721970145345</v>
+        <v>6.27320233619448</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>4.588963963963913</v>
+        <v>4.658246344360641</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.442159951362413</v>
+        <v>0.5120965727910658</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.435596906082061</v>
+        <v>-1.3655511904199</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>1.54188096310282</v>
+        <v>1.611626224764905</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-4.840366682471945</v>
+        <v>-4.770512334764668</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.001775</t>
+          <t>X ≈ 0.001773</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>83</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>10.18130028099618</v>
+        <v>10.21457457331501</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.822028380809662</v>
+        <v>3.855701389423004</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.79196647094043</v>
+        <v>4.827320894608917</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.282992434855636</v>
+        <v>5.31918615227454</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>10.94181903537383</v>
+        <v>11.0074920652695</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>12.33380292548898</v>
+        <v>12.39927752847525</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.151298239218157</v>
+        <v>9.217690290368104</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>10.07756287080795</v>
+        <v>10.14429812272338</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>12.52871749004746</v>
+        <v>12.59542385885496</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>10.55006280216973</v>
+        <v>10.61768890571017</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>13.23406062350193</v>
+        <v>13.30138710208896</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>12.95496672002689</v>
+        <v>13.02263769864082</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.216017670214519</v>
+        <v>8.285017800459478</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>9.199480136288592</v>
+        <v>9.268758201121315</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>9.745368174359733</v>
+        <v>9.815434180649198</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>9.135608946872672</v>
+        <v>9.205001825483748</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>6.591876698506894</v>
+        <v>6.66144613428942</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>6.486893282411614</v>
+        <v>6.556605430468238</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.293377891126546</v>
+        <v>4.362858257175681</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>2.070783132530188</v>
+        <v>2.140065512926917</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>2.732402000640604</v>
+        <v>2.802338622069257</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.451627667889625</v>
+        <v>1.521673383551786</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>6.545679942805485</v>
+        <v>6.61542520446757</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>8.879377157753815</v>
+        <v>8.949231505461093</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.002024</t>
+          <t>X ≈ 0.002023</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.847617724683985</v>
+        <v>2.241505827744547</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.063166847720822</v>
+        <v>0.4361407941005666</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.275084341003001</v>
+        <v>-3.943054725518657</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-8.336703741152675</v>
+        <v>-9.067773450843752</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-11.60052425081441</v>
+        <v>-12.34474039397926</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-11.41335963780762</v>
+        <v>-12.15777420788188</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-6.389124320586284</v>
+        <v>-7.047369950595758</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-3.769128241467158</v>
+        <v>-4.384404924760595</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-6.626162901082211</v>
+        <v>-7.28409421343413</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.60289686257628</v>
+        <v>-2.17465694829415</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.570013129176701</v>
+        <v>1.040579164456055</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.189469950339515</v>
+        <v>3.703006231596248</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.76063090576542</v>
+        <v>11.40337357650484</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>7.191448007774532</v>
+        <v>6.770529994175888</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>9.431067493374918</v>
+        <v>9.053563167183562</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>8.57685218067747</v>
+        <v>8.177361853832451</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>5.54420776189086</v>
+        <v>5.102268246266732</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>8.337775070433267</v>
+        <v>7.938604013033796</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>7.104622871046224</v>
+        <v>6.683907158663992</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>4.393115942028949</v>
+        <v>3.929576498043829</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>2.400640170712187</v>
+        <v>1.91644209478364</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.324685115069578</v>
+        <v>1.84059613337454</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>4.048735643870543</v>
+        <v>3.585659081150709</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>9.769895753877442</v>
+        <v>9.392179769103898</v>
       </c>
     </row>
     <row r="29">
@@ -2508,489 +2508,489 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.366429098058482</v>
+        <v>-0.6105440831289854</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.990703079604828</v>
+        <v>6.630436694278785</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.012541077057158</v>
+        <v>3.677266130096278</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.29874776386405</v>
+        <v>2.96431211065358</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>8.087324132686149</v>
+        <v>8.689127698712369</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.120642591846789</v>
+        <v>2.815487824203686</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.886237998254295</v>
+        <v>3.558690655464851</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.223067968120347</v>
+        <v>7.825933756166322</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.187660956219865</v>
+        <v>4.837117907777944</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.875364006988981</v>
+        <v>2.549050716590031</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.6112617356428274</v>
+        <v>1.307958843600396</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-4.283216783216737</v>
+        <v>-3.516245105302104</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.407708001703924</v>
+        <v>-4.639407172158272</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.013680197353658</v>
+        <v>-0.3150315031503084</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-3.211072974852463</v>
+        <v>-2.488326315882347</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.4609101516919551</v>
+        <v>1.13636363636364</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-5.827029696303121</v>
+        <v>-5.058159561219902</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-7.470474650859934</v>
+        <v>-6.678151780192593</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-5.715889949466586</v>
+        <v>-4.947108884116759</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-2.451923076923038</v>
+        <v>-1.729960043845736</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-4.533585024382567</v>
+        <v>-3.787657726963246</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-7.68646315694825</v>
+        <v>-6.893806718675371</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-5.873226452004587</v>
+        <v>-5.104180491041809</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-4.410706252811515</v>
+        <v>-3.664861229113569</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.002523</t>
+          <t>X ≈ 0.002521</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>45</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.325878594249204</v>
+        <v>6.359152886568033</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.76848085738272</v>
+        <v>3.802153865996061</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>17.88433594885214</v>
+        <v>17.91969037252063</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>14.9483204134367</v>
+        <v>14.9845141308556</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>19.02749507285709</v>
+        <v>19.09316810275277</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>12.54799301919721</v>
+        <v>12.61346762218348</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.108460220476516</v>
+        <v>5.174852271626463</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.3854611305135052</v>
+        <v>0.4521963824289372</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-6.239689471130461</v>
+        <v>-6.172983102322959</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.791302659677797</v>
+        <v>-4.723676556137356</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-6.739165614784675</v>
+        <v>-6.671839136197647</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-9.240481740481798</v>
+        <v>-9.172810761867865</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-12.58719518119111</v>
+        <v>-12.51819505094615</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-10.58632977000324</v>
+        <v>-10.51705170517052</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-9.023038786818375</v>
+        <v>-8.95297278052891</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-15.0946454038636</v>
+        <v>-15.02525252525253</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-17.45096132023475</v>
+        <v>-17.38139188445222</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-13.11150029188561</v>
+        <v>-13.04178814382899</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-12.89537712895373</v>
+        <v>-12.8258967629046</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-17.15277777777781</v>
+        <v>-17.08349539738109</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-15.47375596455351</v>
+        <v>-15.40381934312486</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-17.77193324241834</v>
+        <v>-17.70188752675618</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-15.27493585371399</v>
+        <v>-15.20519059205191</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-17.57309941520472</v>
+        <v>-17.50324506749744</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.002772</t>
+          <t>X ≈ 0.00277</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.931939200309813</v>
+        <v>4.423669015600339</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>6.596763685665486</v>
+        <v>4.088892217250482</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.126760191276318</v>
+        <v>-0.5749332833934204</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.50387596899224</v>
+        <v>8.389532052002551</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>13.16890921427124</v>
+        <v>11.27954803106817</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>7.295467766671955</v>
+        <v>5.014901313939752</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.492298604314904</v>
+        <v>1.017146178436505</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-5.877165132112751</v>
+        <v>-8.938484621155283</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-11.89625512769614</v>
+        <v>-15.34861034246639</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-21.76099962937469</v>
+        <v>-22.57313892172873</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-21.48664036225936</v>
+        <v>-22.29907927956676</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-18.73543123543124</v>
+        <v>-19.35202223140185</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-25.92052851452444</v>
+        <v>-26.92679720148378</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-23.11158229525576</v>
+        <v>-23.92206962631752</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-29.83111959489912</v>
+        <v>-31.03182582712388</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-29.23605954527774</v>
+        <v>-30.43743890518084</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-20.27924414851758</v>
+        <v>-20.89393668731965</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-14.32362150400675</v>
+        <v>-14.54716448791498</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-14.10749834107502</v>
+        <v>-14.33127310699074</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-19.98106060606057</v>
+        <v>-20.59604020024839</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-14.4636549544525</v>
+        <v>-14.68697346498866</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-11.50930697979208</v>
+        <v>-11.5370129747849</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-17.29513787391601</v>
+        <v>-17.71415116552865</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-20.40138224348747</v>
+        <v>-21.01578987036474</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.003021</t>
+          <t>X ≈ 0.00302</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-10.81697854860794</v>
+        <v>-7.694901167486059</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.990703079604877</v>
+        <v>8.18653825038038</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.693859758375879</v>
+        <v>4.045816498646687</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>18.12292358803987</v>
+        <v>19.54907869542016</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.32908237444439</v>
+        <v>8.402477412062083</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.8019612731654604</v>
+        <v>3.184038192754052</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11.45766656968282</v>
+        <v>13.22290031967447</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2494595044071275</v>
+        <v>2.133878064110625</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.065086296527383</v>
+        <v>-0.5273374566773725</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.9817788501539226</v>
+        <v>-1.30025313271382</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.56456244018144</v>
+        <v>-3.728896193254641</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-6.700799200799203</v>
+        <v>-6.710348299405346</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.111004705000589</v>
+        <v>-2.428104960856011</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-13.76093294460641</v>
+        <v>-13.45999464811342</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-2.991292755072287</v>
+        <v>-3.30732713488316</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-5.253375562593718</v>
+        <v>-5.415642915642877</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.3268164575429964</v>
+        <v>-0.1441546472149824</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>3.078975898590606</v>
+        <v>2.45370735166658</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-2.419186652763294</v>
+        <v>-2.735806672814498</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-2.232142857142819</v>
+        <v>-2.548960862846471</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-2.775343266140773</v>
+        <v>-3.091507030812501</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-2.851298321783425</v>
+        <v>-3.167352992221602</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-2.576523155301295</v>
+        <v>-2.892878279739548</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-5.509607351712617</v>
+        <v>-5.671413235665568</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.00327</t>
+          <t>X ≈ 0.003269</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>17</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-24.26235669986844</v>
+        <v>-24.22908240754961</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-18.7151792733363</v>
+        <v>-18.68150626472296</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-14.27252679624597</v>
+        <v>-14.23717237257748</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3.221614227086178</v>
+        <v>-3.185420509667274</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-15.35158989446317</v>
+        <v>-15.2859168645675</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.482633542073032</v>
+        <v>2.548108145059302</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.709767410019083</v>
+        <v>1.77615946116903</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.313565705676908</v>
+        <v>7.38030095759234</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>7.355081770699542</v>
+        <v>7.421788139507044</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.46359930110659</v>
+        <v>12.53122540464703</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.73795856822193</v>
+        <v>12.80528504680895</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.45886466474703</v>
+        <v>12.52653564336096</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>17.21672638743626</v>
+        <v>17.28572651768122</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>16.99536957640199</v>
+        <v>17.06464764123471</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>16.3364383373646</v>
+        <v>16.40650434365407</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>11.04914544580944</v>
+        <v>11.11853832442051</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>28.56211057519009</v>
+        <v>28.63168001097262</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>28.45712715909481</v>
+        <v>28.52683930715143</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>22.79089738085015</v>
+        <v>22.86037774689928</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>22.97794117647051</v>
+        <v>23.04722355686724</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>28.31709370864902</v>
+        <v>28.38703033007767</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>28.24113865300649</v>
+        <v>28.31118436866866</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>22.63356087831215</v>
+        <v>22.70330613997423</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>16.67526659786713</v>
+        <v>16.74512094557441</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.00352</t>
+          <t>X ≈ 0.003518</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>28</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>14.18302145139207</v>
+        <v>14.21629574371089</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>6.704988793890585</v>
+        <v>6.738661802503927</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>12.4081454726616</v>
+        <v>12.44349989633009</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.551495016611291</v>
+        <v>4.587688734030195</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.186225231587244</v>
+        <v>4.251898261482921</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>11.51624698745118</v>
+        <v>11.58172159043745</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>14.31480942682573</v>
+        <v>14.38120147797567</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>10.46482620987862</v>
+        <v>10.53156146179406</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.07777084632983</v>
+        <v>14.14447721513733</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.30393543556037</v>
+        <v>13.37156153910081</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>13.57829470267571</v>
+        <v>13.64562118126273</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>16.87062937062937</v>
+        <v>16.93830034924331</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>12.17470958071369</v>
+        <v>12.24370971095865</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.52478134110785</v>
+        <v>15.59405940594057</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>7.722992959213478</v>
+        <v>7.793058965502944</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>11.88948158026341</v>
+        <v>11.95887445887449</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>15.3268164575431</v>
+        <v>15.39638589332563</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>15.22183304144775</v>
+        <v>15.29154518950438</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>15.43795620437957</v>
+        <v>15.5074365704287</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>15.625</v>
+        <v>15.69428238039673</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>15.08179959100205</v>
+        <v>15.1517362124307</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>11.43441596393087</v>
+        <v>11.50446167959303</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>15.28061970184157</v>
+        <v>15.35036496350365</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>15.20467836257317</v>
+        <v>15.27453271028045</v>
       </c>
     </row>
   </sheetData>
@@ -3180,247 +3180,247 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.003586</t>
+          <t>X &gt; -0.003585</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3351</v>
+        <v>3355</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1492336624175508</v>
+        <v>0.148377279700064</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1264872480009629</v>
+        <v>0.1256494077325812</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.03736085988410309</v>
+        <v>0.03659400601186746</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08164715459493976</v>
+        <v>0.08081042715189568</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1779121147459435</v>
+        <v>-0.1790442399989942</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.03338622291221327</v>
+        <v>-0.0346860161865834</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.0472536882065171</v>
+        <v>-0.04855619021616064</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.04155929650691093</v>
+        <v>-0.04287596669264815</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01271383239017609</v>
+        <v>-0.01406453984362344</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.03286772169919772</v>
+        <v>0.03144365757598422</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.02725002796872644</v>
+        <v>0.02583835126612399</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.02648629990288498</v>
+        <v>-0.02784161689866238</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.05607271490249133</v>
+        <v>0.05459163948760448</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.08813148245653935</v>
+        <v>-0.08944728053785411</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.07418343540390282</v>
+        <v>0.07265808220071079</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.032211134127202</v>
+        <v>0.03074906063309868</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.06475570709633871</v>
+        <v>0.06325085465810076</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.007355829651501722</v>
+        <v>0.005915912503489551</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.1162750232724008</v>
+        <v>-0.1175634295712982</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1499627421758589</v>
+        <v>-0.1512073486893115</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1388324900951474</v>
+        <v>-0.1401041687485787</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.167134886054221</v>
+        <v>-0.1683754624130174</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.172840918683498</v>
+        <v>-0.1740688863175635</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1713287994680854</v>
+        <v>-0.172561179436471</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.003337</t>
+          <t>X &gt; -0.003336</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3336</v>
+        <v>3340</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1811926758210944</v>
+        <v>0.1801460474363026</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.07051248996818771</v>
+        <v>0.06958727203737425</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.01259583547916776</v>
+        <v>-0.01346444251464618</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.005266513291019237</v>
+        <v>0.004355400696866241</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2240366376910075</v>
+        <v>-0.2254121625378289</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.07971518990635218</v>
+        <v>-0.08125807432899279</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.06037697341286474</v>
+        <v>-0.06196631639856065</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.05341449929290576</v>
+        <v>-0.05502120464561244</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.05447112834727363</v>
+        <v>-0.05607632967853959</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.03508375420508969</v>
+        <v>-0.03673559012655403</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.07183540012684375</v>
+        <v>-0.07343637913094625</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.09472307859404339</v>
+        <v>-0.09630585600729802</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.03665240656706459</v>
+        <v>-0.03833829176977588</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1805384437098212</v>
+        <v>-0.1820599970444832</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.01456843305648903</v>
+        <v>-0.01630843628014844</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.05942477653770339</v>
+        <v>-0.06109481915932946</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.003753340582221654</v>
+        <v>0.002002863746831451</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.05345121947385678</v>
+        <v>-0.05513741659245142</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.178625657338479</v>
+        <v>-0.1801568525907271</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1833832335329291</v>
+        <v>-0.1849042224740813</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1997218225948458</v>
+        <v>-0.2012401561005603</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1679122052037769</v>
+        <v>-0.1694718076259178</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.1748792493121698</v>
+        <v>-0.1764234232069128</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.173019479153524</v>
+        <v>-0.1745690861268088</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.003088</t>
+          <t>X &gt; -0.003087</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3323</v>
+        <v>3327</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.2410011286185991</v>
+        <v>0.2397499014934041</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1312113008305928</v>
+        <v>0.1300792832017947</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1132035724565412</v>
+        <v>0.1120440164871113</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.07412225476351608</v>
+        <v>0.07298473471311695</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1247091960437601</v>
+        <v>-0.1264639620675823</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.01045588166414291</v>
+        <v>-0.01234204398492977</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.01198650124830891</v>
+        <v>0.01004631734682704</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.02008227456862244</v>
+        <v>0.01812186519558878</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.01888186233596656</v>
+        <v>0.0169231414431863</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.04138138786996848</v>
+        <v>0.03936844037075105</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.02653571870148141</v>
+        <v>-0.02845922934462664</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.07839611662700463</v>
+        <v>-0.08026808441946542</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.07569748073120053</v>
+        <v>-0.07761186740309967</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1892900660328394</v>
+        <v>-0.191076944074382</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.02010427968212269</v>
+        <v>-0.02211746478144505</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.06745970720927374</v>
+        <v>-0.06939711962200334</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.03354390281732833</v>
+        <v>-0.03552772395099169</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.03049498498661762</v>
+        <v>-0.03248721373595487</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.1569957186973596</v>
+        <v>-0.1588299361739445</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1624962428614296</v>
+        <v>-0.1643186403177737</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1767692604711968</v>
+        <v>-0.1785941178996353</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1746065924601155</v>
+        <v>-0.1764377754127722</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.1525932945483248</v>
+        <v>-0.1544427288040353</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.1805157391422156</v>
+        <v>-0.1823353390132851</v>
       </c>
     </row>
     <row r="9">
@@ -3430,243 +3430,243 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3294</v>
+        <v>3298</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1117006153653435</v>
+        <v>0.09634396553126123</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.07818422590955265</v>
+        <v>0.07924494561947881</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.07303037653262123</v>
+        <v>0.07489744931991993</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1305989793554616</v>
+        <v>0.1328298674066275</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.03651458897865467</v>
+        <v>-0.02196513002752454</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.04370468877957023</v>
+        <v>-0.0461603315621204</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.0161473638132108</v>
+        <v>0.01358357988100778</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02684321976504833</v>
+        <v>0.02425259197384122</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.004972287199308312</v>
+        <v>-0.007524165124948468</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.05498299701010012</v>
+        <v>0.05232263846655627</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.04628398542386236</v>
+        <v>-0.04881127449903033</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.0960877246807641</v>
+        <v>-0.09856879551342246</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1436923563323518</v>
+        <v>-0.1461676426430429</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1957757282230332</v>
+        <v>-0.1981994389339121</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.04935280525832297</v>
+        <v>-0.05198467808884288</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.1025554647878977</v>
+        <v>-0.1050978774125468</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.06712293639635902</v>
+        <v>-0.0697158015897017</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.02059120097649725</v>
+        <v>-0.005154780220117061</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.1197885667631979</v>
+        <v>-0.104313883841435</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.1269708914493606</v>
+        <v>-0.1115340388701682</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1365807547668325</v>
+        <v>-0.1209910602965749</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.1640583772619237</v>
+        <v>-0.1665339914026518</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.2049645166713248</v>
+        <v>-0.2073798076391142</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.2628383344517999</v>
+        <v>-0.2651883327760203</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.002589</t>
+          <t>X &gt; -0.002588</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3257</v>
+        <v>3261</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.013352644310892</v>
+        <v>0.01992164800793716</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1090679362247684</v>
+        <v>0.1427409448381098</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.05908928015102077</v>
+        <v>0.07751018134707977</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.12536559048187</v>
+        <v>0.1272163205376486</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.05209218905726232</v>
+        <v>0.06598350509838014</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.01218904173165924</v>
+        <v>0.008898440433085852</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.08147172877674791</v>
+        <v>0.07804964049365282</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.03433371948389663</v>
+        <v>0.03095096118352103</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.001691010543453331</v>
+        <v>-0.001651465342533243</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.04050162166783622</v>
+        <v>0.03706463710238239</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.03443090148458339</v>
+        <v>-0.03776234630043973</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2346337872653592</v>
+        <v>-0.2377387705610943</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1476481961895786</v>
+        <v>-0.1509271410307278</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1978151071468659</v>
+        <v>-0.2010476276985429</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.04226628384059694</v>
+        <v>-0.045729654870307</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.07217808360216083</v>
+        <v>-0.0755721226957391</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.0571259886493749</v>
+        <v>0.05356373232157807</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.0440825051314846</v>
+        <v>0.05884463837149667</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.05867163130406539</v>
+        <v>-0.04386511410422145</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.0680389451088601</v>
+        <v>-0.05326663921111674</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.0408997955010264</v>
+        <v>-0.02601432388556901</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.09848194515605968</v>
+        <v>-0.1018602852946699</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.1736467192756805</v>
+        <v>-0.1769189114197047</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2313056718143756</v>
+        <v>-0.2345135945340999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.00234</t>
+          <t>X &gt; -0.002339</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3205</v>
+        <v>3209</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1691586265944665</v>
+        <v>-0.1358843342756373</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1321257045142303</v>
+        <v>-0.0984526959008889</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.02726696550322316</v>
+        <v>0.04541411114752236</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.04857592424176715</v>
+        <v>-0.04719251375427547</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1791005323724804</v>
+        <v>-0.1658613982122219</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1297157454680757</v>
+        <v>-0.1339820607500712</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.07791243130803593</v>
+        <v>0.07332505405829437</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.2521830419837201</v>
+        <v>0.2473546692073469</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1251086499622858</v>
+        <v>0.1204385403690296</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1465082855959068</v>
+        <v>0.1417478745045315</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1279503347574646</v>
+        <v>0.1232317968043759</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2264459249524577</v>
+        <v>-0.230748749575838</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2747146334164441</v>
+        <v>-0.2790488484800804</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.259776566737699</v>
+        <v>-0.2641495492832888</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.09054977335764391</v>
+        <v>-0.09518809070682721</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.03753221590929456</v>
+        <v>-0.04219230261544737</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.01586267018282683</v>
+        <v>-0.001995681526601345</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.02738814235286924</v>
+        <v>0.005119286640123732</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.1227914591718289</v>
+        <v>-0.07182222745357336</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.1353614833281469</v>
+        <v>-0.08453381898021206</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.1925146234617898</v>
+        <v>-0.1597902673200835</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.1874825616159228</v>
+        <v>-0.1733309327790238</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.2683509781334834</v>
+        <v>-0.2726879959979058</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.2009378620758895</v>
+        <v>-0.205367570180826</v>
       </c>
     </row>
     <row r="12">
@@ -3676,79 +3676,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3144</v>
+        <v>3148</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.2438337042016343</v>
+        <v>-0.2105594118828051</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2628536703160904</v>
+        <v>-0.229180661702749</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.009402191565378359</v>
+        <v>0.008424696474612858</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1362168286456367</v>
+        <v>-0.1354493356143536</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2938832675085905</v>
+        <v>-0.2815464790436906</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.08891739549098787</v>
+        <v>-0.09458029294631132</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1376629507558818</v>
+        <v>0.1316306819153112</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.3523776827959182</v>
+        <v>0.3460415087954232</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.190390799253926</v>
+        <v>0.18426021694561</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1954907898732472</v>
+        <v>0.189270579032069</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2346947389108678</v>
+        <v>0.2284493727039703</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2479878193484311</v>
+        <v>-0.2536540378330301</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2437095635938107</v>
+        <v>-0.2495005008827675</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2559231971339528</v>
+        <v>-0.2617250631560708</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.1976419614214961</v>
+        <v>-0.2035892816209355</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.1234023284604717</v>
+        <v>-0.1293861546002404</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.09871545735058618</v>
+        <v>-0.08584760921250734</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.1084305342905836</v>
+        <v>-0.07659190982916897</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.2098685018763859</v>
+        <v>-0.1592300962379625</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.2263341804320191</v>
+        <v>-0.1758351172215669</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.3376475014669751</v>
+        <v>-0.3055518155146828</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.3628776515445651</v>
+        <v>-0.3496416638720206</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.4189033506226636</v>
+        <v>-0.4244841949593479</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.3805633677067988</v>
+        <v>-0.3862042655773195</v>
       </c>
     </row>
     <row r="13">
@@ -3758,161 +3758,161 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3073</v>
+        <v>3077</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.2911495702053202</v>
+        <v>-0.257875277886491</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1407310414698983</v>
+        <v>-0.1070580328565569</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.05890350296620284</v>
+        <v>-0.02354907929771599</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2690083142547266</v>
+        <v>-0.2509090553607223</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2922328182993681</v>
+        <v>-0.262970165654842</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.01036790218129369</v>
+        <v>0.02111482911848128</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.22821530781669</v>
+        <v>0.2203542319875993</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.4222099415813929</v>
+        <v>0.4140559103506547</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.1905552400094166</v>
+        <v>0.1827020288723205</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2465515475470141</v>
+        <v>0.2385183023634667</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2152864029585473</v>
+        <v>0.2073252794335971</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.239760239760237</v>
+        <v>-0.2471730619110346</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.2411953977116141</v>
+        <v>-0.2487605174830705</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2809366575925765</v>
+        <v>-0.2884843967849022</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.2706464855147388</v>
+        <v>-0.2783000552232124</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.09807587365740744</v>
+        <v>-0.08658008658008498</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.06967363020477535</v>
+        <v>-0.03882034246528576</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.1096586712594245</v>
+        <v>-0.0593320034780831</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.2185273835307271</v>
+        <v>-0.1490470174815925</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.323976275593111</v>
+        <v>-0.2546938951963824</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.3603330487898901</v>
+        <v>-0.3097522503577324</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.3193587166730794</v>
+        <v>-0.2881006492059015</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.4155416514440518</v>
+        <v>-0.4036161869675894</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.3094771857510139</v>
+        <v>-0.3169525025893094</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.001592</t>
+          <t>X &gt; -0.001591</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2959</v>
+        <v>2961</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4618778806919295</v>
+        <v>-0.4286035883731003</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.02342406469381331</v>
+        <v>0.01024894391952813</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.08413413250494983</v>
+        <v>0.1194885561734367</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.09562114620175777</v>
+        <v>0.1128917516651029</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.1868503217444868</v>
+        <v>0.214370031220092</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.2921007633049584</v>
+        <v>0.300428043755403</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4140251319693533</v>
+        <v>0.4030168640695635</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.49178038777616</v>
+        <v>0.480609721744031</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2494690503839152</v>
+        <v>0.2386254095884226</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3379398667326967</v>
+        <v>0.32682849436776</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4971094461110184</v>
+        <v>0.4858271188078476</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2039627039627092</v>
+        <v>0.1930173303753762</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.0778965051628191</v>
+        <v>0.06690774649234044</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.02214641041137355</v>
+        <v>-0.03304780916391792</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.08199329693717772</v>
+        <v>0.07082335962479647</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.3055572303815808</v>
+        <v>0.3143786038522904</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.1039187878368537</v>
+        <v>0.1331391839094209</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.1002524943352938</v>
+        <v>0.1497491057771683</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.08889283310776364</v>
+        <v>-0.01941246705862909</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.3071175278622107</v>
+        <v>-0.2378351474654821</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.3775046980894814</v>
+        <v>-0.3075680766608286</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.3183702569404616</v>
+        <v>-0.2483245412783006</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3612721900503217</v>
+        <v>-0.3115735707753089</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.1129965275925002</v>
+        <v>-0.08345445621742442</v>
       </c>
     </row>
     <row r="15">
@@ -3922,79 +3922,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2821</v>
+        <v>2822</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.05604869131380497</v>
+        <v>-0.0227743989949758</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2794429313521434</v>
+        <v>0.3131159399654848</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7458490680425669</v>
+        <v>0.7812034917110537</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4403166469583439</v>
+        <v>0.4565304465005724</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6248890051150369</v>
+        <v>0.6502140297245731</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.7262419394955941</v>
+        <v>0.7312854046676875</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.8219043114391695</v>
+        <v>0.80649521001137</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.740639505493867</v>
+        <v>0.7252660622782869</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.6258531142564294</v>
+        <v>0.6106426286711368</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.6510186425161919</v>
+        <v>0.6355696158297377</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.875386990918436</v>
+        <v>0.8596796572512204</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7941421185047233</v>
+        <v>0.7784700805021458</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.469836345553496</v>
+        <v>0.4543317737207531</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.482258307798169</v>
+        <v>0.4666708709087501</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.3903008462236528</v>
+        <v>0.3960930995104803</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.6664381460222231</v>
+        <v>0.6931925487166311</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.3906010075075912</v>
+        <v>0.4388938635699731</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.391925174686591</v>
+        <v>0.4616373227432149</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.2182538656127377</v>
+        <v>0.2877342316618723</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.05536853295534883</v>
+        <v>0.0139138474413798</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.1379027477647838</v>
+        <v>-0.06796612633613108</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.07211435904169861</v>
+        <v>-0.002068643379537605</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.2580053867480885</v>
+        <v>-0.1882601250860034</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.02928122622520135</v>
+        <v>0.01939451042212426</v>
       </c>
     </row>
     <row r="16">
@@ -4007,76 +4007,76 @@
         <v>2674</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1490788926453277</v>
+        <v>0.1823531849641569</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.6344927103396714</v>
+        <v>0.6681657189530128</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.947869456249812</v>
+        <v>0.9832238799182988</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.6443708092259897</v>
+        <v>0.6805645266448934</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.763994720583888</v>
+        <v>0.8296677504795653</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.8019612731654604</v>
+        <v>0.8674358761517311</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.073481564087942</v>
+        <v>1.139873615237889</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.077832606467076</v>
+        <v>1.122758776228942</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.8798825084638509</v>
+        <v>0.9031493523995167</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8746171809993939</v>
+        <v>0.8762239784890937</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.984239523637342</v>
+        <v>0.9637860451195053</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.138192898282583</v>
+        <v>1.11740482685525</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8582876848525061</v>
+        <v>0.837534698960539</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.8463968983255299</v>
+        <v>0.8255754626993692</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.6736287108962955</v>
+        <v>0.675550026925599</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.8573200245416217</v>
+        <v>0.881573583367306</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.7606234882086937</v>
+        <v>0.8076008465965856</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.6182429142974186</v>
+        <v>0.6879550623540425</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.4229973412531649</v>
+        <v>0.4924777073022995</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.08648092744951441</v>
+        <v>0.155763307846243</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.08274790338838045</v>
+        <v>-0.01281128195972769</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.06567998786503892</v>
+        <v>0.1357257035271999</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.04127789181913499</v>
+        <v>0.11102315348122</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.2271166572627052</v>
+        <v>0.2969710049699827</v>
       </c>
     </row>
     <row r="17">
@@ -4089,732 +4089,732 @@
         <v>2481</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3484047406691531</v>
+        <v>0.3816790329879822</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4557071021310222</v>
+        <v>0.4893801107443636</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.7859181424696615</v>
+        <v>0.8212725661381484</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1928006136691067</v>
+        <v>0.2289943310880105</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.6722613193932503</v>
+        <v>0.7379343492889276</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.4973985792222422</v>
+        <v>0.5628731822085129</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.6899387223090017</v>
+        <v>0.7563307734589486</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.9343124758250383</v>
+        <v>1.00104772774047</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8785756753036438</v>
+        <v>0.9218591252625714</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.01385031938829</v>
+        <v>1.033899201438473</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.9898360409186111</v>
+        <v>0.9861567518868029</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.258220023328811</v>
+        <v>1.230335747473397</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.8428733395666512</v>
+        <v>0.8151382823871884</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9036608251868685</v>
+        <v>0.9000175379856898</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.6477928670846822</v>
+        <v>0.6689004015537563</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.7188706514904268</v>
+        <v>0.7639855444045622</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.4638579730609749</v>
+        <v>0.5334274088435009</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.358874556965695</v>
+        <v>0.4285867050223189</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.2525470951494171</v>
+        <v>0.3220274611985516</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.003778718258764968</v>
+        <v>0.06550366213796366</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.05761579414593854</v>
+        <v>0.1275524155745913</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.2638050351579082</v>
+        <v>0.3338507508200692</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.3773548892659875</v>
+        <v>0.4471001509280725</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.4626388623715698</v>
+        <v>0.5324932100788473</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.0005943</t>
+          <t>X &gt; -0.0005944</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2271</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4595637305728673</v>
+        <v>0.4928380228916964</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5201665800446307</v>
+        <v>0.5538395886579721</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.8834564413762607</v>
+        <v>0.9188108650447475</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.4774907447178407</v>
+        <v>0.5136844621367445</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.8598023141353153</v>
+        <v>0.9254753440309926</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.6511885630260039</v>
+        <v>0.7166631660122746</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.9337314019482221</v>
+        <v>1.000123453098169</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.182881241917798</v>
+        <v>1.24961649383323</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.092471185568392</v>
+        <v>1.159177554375894</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.136252700345736</v>
+        <v>1.177818606571591</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.040568344526811</v>
+        <v>1.056099884617417</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.315807706164385</v>
+        <v>1.305054966657558</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.9398854000506418</v>
+        <v>0.9294742542429475</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.7625620544500151</v>
+        <v>0.778837232601397</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.4999320043162783</v>
+        <v>0.5433104745572237</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.6106239341666324</v>
+        <v>0.6800168127777084</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.5645971708851718</v>
+        <v>0.6341666066676979</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.5476806856573475</v>
+        <v>0.6173928337139714</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.2794357288181359</v>
+        <v>0.3489160948672705</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.2903456627036505</v>
+        <v>0.3596280431003791</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.3195803043441856</v>
+        <v>0.3895169257728384</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.551859506737685</v>
+        <v>0.621905222399846</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.7385677423523518</v>
+        <v>0.8083130040144368</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.882793730252537</v>
+        <v>0.9526480779598145</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.000345</t>
+          <t>X &gt; -0.0003451</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2066</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3394182460867299</v>
+        <v>0.372692538405559</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2460222285410438</v>
+        <v>0.2796952371543853</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.8372695400835397</v>
+        <v>0.8726239637520266</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.4136116234087552</v>
+        <v>0.449805340827659</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9187480279398414</v>
+        <v>0.9844210578355188</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8157772444282472</v>
+        <v>0.8812518474145179</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.34852039670691</v>
+        <v>1.414912447856857</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.650236544225102</v>
+        <v>1.716971796140534</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.546684910988539</v>
+        <v>1.613391279796041</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.527033092620293</v>
+        <v>1.565814095055487</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.201030147289167</v>
+        <v>1.211247044760931</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.502768770435765</v>
+        <v>1.512768434349688</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.104318210225486</v>
+        <v>1.114944858789514</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.9313641097429155</v>
+        <v>0.9714178965066367</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.7564599762235318</v>
+        <v>0.8265259825129974</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.8190902097752115</v>
+        <v>0.8884830883862875</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.4429829628673332</v>
+        <v>0.5125523986498592</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.4348049678756354</v>
+        <v>0.5045171159322592</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.3605118674967045</v>
+        <v>0.429992233545839</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.4991529525653391</v>
+        <v>0.5684353329620677</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.4399796490853021</v>
+        <v>0.5099162705139548</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.606038146201648</v>
+        <v>0.676083861863809</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.5903970493730242</v>
+        <v>0.6601423110351092</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.7080665523117275</v>
+        <v>0.777920900019005</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -9.563e-05</t>
+          <t>X &gt; -9.584e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6894138916366401</v>
+        <v>0.6924862199013688</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7433434353580779</v>
+        <v>0.8021538659959973</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.304754700010122</v>
+        <v>1.308579261409449</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.09123931900151</v>
+        <v>1.095625241966708</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.948871145984143</v>
+        <v>1.982056991641656</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.524584952987595</v>
+        <v>1.557912066627928</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.308139054396598</v>
+        <v>2.341518938293135</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.696621651790764</v>
+        <v>2.729974160206716</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.849310590632186</v>
+        <v>2.882572453232541</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.40899380131912</v>
+        <v>2.442990110529379</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.960729388612336</v>
+        <v>1.994827530469074</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.570462611318646</v>
+        <v>1.604967015909978</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.446527257200593</v>
+        <v>1.48180494905386</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.447516193803814</v>
+        <v>1.482948294829491</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.288862886951065</v>
+        <v>1.324804997248933</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.661577188934871</v>
+        <v>1.696969696969703</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.193964873329577</v>
+        <v>1.229719226658887</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.144567894143691</v>
+        <v>1.180434078393269</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.138345309437931</v>
+        <v>1.174103237095373</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.214216231239575</v>
+        <v>1.249837935952279</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.338053065154355</v>
+        <v>1.37395843465292</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.373270883330534</v>
+        <v>1.409223584354926</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.425700302175088</v>
+        <v>1.461476074614765</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.516518273634802</v>
+        <v>1.552310488058154</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0001537</t>
+          <t>X &gt; 0.0001534</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1547</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.400216021527811</v>
+        <v>1.43349031384664</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.065040506883484</v>
+        <v>1.098713515496826</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.693859758375879</v>
+        <v>1.729214182044366</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.497196374077355</v>
+        <v>1.533390091496258</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.295468929066246</v>
+        <v>2.361141958961923</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.417992300961203</v>
+        <v>2.483466903947473</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.873309750031929</v>
+        <v>2.939701801181876</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.305808756743488</v>
+        <v>3.37254400865892</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.735172268437104</v>
+        <v>3.801878637244606</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.34918430433865</v>
+        <v>3.41681040787909</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.235696124783011</v>
+        <v>3.303022603370039</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.021243462419939</v>
+        <v>3.088914441033872</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.413882172827428</v>
+        <v>2.482882303072387</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.709655290687706</v>
+        <v>2.778933355520429</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>2.567853980545038</v>
+        <v>2.637919986834504</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>2.904349065719103</v>
+        <v>2.973741944330179</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>2.576331648234692</v>
+        <v>2.645901084017218</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>2.794554437698558</v>
+        <v>2.864266585755182</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>2.558188912847569</v>
+        <v>2.627669278896704</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>2.615950226244344</v>
+        <v>2.685232606641073</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.913085951700168</v>
+        <v>2.983022573128821</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>2.901772137169388</v>
+        <v>2.971817852831549</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>3.176547303651517</v>
+        <v>3.246292565313603</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>3.165247205494879</v>
+        <v>3.235101553202156</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.000403</t>
+          <t>X &gt; 0.0004027</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.08778335615397</v>
+        <v>1.155776063851221</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.136632419082609</v>
+        <v>1.20472911968406</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.233030265288328</v>
+        <v>1.224883516547166</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.210481191726508</v>
+        <v>1.279389205469734</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.150894970450544</v>
+        <v>2.248280237143497</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.261254667942737</v>
+        <v>2.358500452404343</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.41004752206382</v>
+        <v>2.507503418552361</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.89954203169119</v>
+        <v>2.9967516821646</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.325082674286783</v>
+        <v>3.421968718261951</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.242491503148692</v>
+        <v>3.339766779754243</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.286436023720249</v>
+        <v>3.306842538570038</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.237756866789127</v>
+        <v>3.258331047631643</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.727704972418728</v>
+        <v>2.749136747467773</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.42954324586978</v>
+        <v>2.451311900184649</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>3.153100486095148</v>
+        <v>3.174596077661654</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>3.440940873658164</v>
+        <v>3.461999116258525</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.615602939877903</v>
+        <v>2.63736824175227</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>2.587424439297216</v>
+        <v>2.609273508767622</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.419523024656066</v>
+        <v>2.441435035509286</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>2.606566820276498</v>
+        <v>2.628280845477313</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>2.754610650909875</v>
+        <v>2.776448415040065</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>2.755460510781859</v>
+        <v>2.77734842446749</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>3.260650423807775</v>
+        <v>3.282061049459145</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>3.107904169024714</v>
+        <v>3.129482825399336</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.0006524</t>
+          <t>X &gt; 0.0006519</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.8356825158178296</v>
+        <v>0.9135113586542261</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.088742295291155</v>
+        <v>1.068450525044859</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.413747713557953</v>
+        <v>1.49135214202758</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.8960328317373438</v>
+        <v>0.9742845084810199</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.197429713379968</v>
+        <v>2.303528316051271</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.580672757759302</v>
+        <v>2.686380888044837</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.592120351195469</v>
+        <v>2.697977747739202</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.195918646853379</v>
+        <v>3.301255039518949</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.139395496189735</v>
+        <v>3.244799028485559</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.836148320714429</v>
+        <v>3.941031246670413</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.404625234888591</v>
+        <v>4.50892046767661</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.12553133141369</v>
+        <v>4.230171064228614</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.687314622730462</v>
+        <v>3.792611348009125</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4.15223232150003</v>
+        <v>4.25713482219917</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>4.669771670698033</v>
+        <v>4.774309839995688</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>4.774635641888032</v>
+        <v>4.878980797198238</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>4.346424300680283</v>
+        <v>4.451234081376484</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>4.241440884585003</v>
+        <v>4.346393377555302</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>3.869328753399174</v>
+        <v>3.974625600791093</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>3.468137254901961</v>
+        <v>3.573812253070571</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>3.317093708649104</v>
+        <v>3.423038856896909</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.947021005947668</v>
+        <v>3.053363316643534</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>3.319835388116076</v>
+        <v>3.425781222073681</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>3.14585483316133</v>
+        <v>3.252005775902312</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.0009017</t>
+          <t>X &gt; 0.0009012</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>842</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.55153180090003</v>
+        <v>1.584806093218859</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.216356286255703</v>
+        <v>1.250029294869044</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.201833969437978</v>
+        <v>1.237188393106464</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.2505109650334205</v>
+        <v>0.2867046824523243</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.310419327277785</v>
+        <v>1.376092357173462</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.853878477101674</v>
+        <v>1.919353080087944</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.081012345047647</v>
+        <v>1.147404396197594</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.990106155586091</v>
+        <v>2.056841407501523</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.150387066214421</v>
+        <v>2.217093435021923</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.395554030741913</v>
+        <v>3.463180134282354</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.382502371491448</v>
+        <v>4.449828850078475</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.578467850439345</v>
+        <v>4.646138829053278</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.166565705586407</v>
+        <v>4.235565835831366</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.420268276974859</v>
+        <v>4.489546341807582</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5.067750339600259</v>
+        <v>5.137816345889725</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>5.425280698010248</v>
+        <v>5.494673576621324</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>4.816127621438525</v>
+        <v>4.885697057221051</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>5.067438742160348</v>
+        <v>5.137150890216972</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>4.333443140246551</v>
+        <v>4.402923506295686</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.451603325415675</v>
+        <v>3.520885705812404</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.145932607629121</v>
+        <v>3.215869229057773</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.832447860775112</v>
+        <v>2.902493576437273</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.869693336045842</v>
+        <v>2.939438597707927</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.674987151171671</v>
+        <v>2.744841498878948</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.001151</t>
+          <t>X &gt; 0.00115</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>678</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.078090983629735</v>
+        <v>2.111365275948565</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4154818406668213</v>
+        <v>0.4491548492801627</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.8931855063741949</v>
+        <v>0.9285399300426818</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3268848185497717</v>
+        <v>0.3630785359686755</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.174004414056697</v>
+        <v>2.239677443952374</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.918691150957294</v>
+        <v>1.984165753943564</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.293317644271994</v>
+        <v>1.359709695421941</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.194704001703279</v>
+        <v>2.261439253618711</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.268668444307046</v>
+        <v>3.335374813114548</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.969759287224932</v>
+        <v>4.037385390765373</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.686596430446464</v>
+        <v>4.753922909033491</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.407502526971562</v>
+        <v>4.475173505585495</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.315459686065537</v>
+        <v>4.384459816310496</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.946610249662442</v>
+        <v>4.015888314495164</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.172634762837539</v>
+        <v>4.242700769127005</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>5.062680063196375</v>
+        <v>5.132072941807451</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.89613799146634</v>
+        <v>3.965707427248866</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>4.528617702214717</v>
+        <v>4.598329850271341</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>4.007277738302875</v>
+        <v>4.07675810435201</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.456858407079643</v>
+        <v>3.526140787476372</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.471180121975493</v>
+        <v>2.541116743404146</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.395225066332884</v>
+        <v>2.465270781995045</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3.112478108921209</v>
+        <v>3.182223370583294</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>2.446566268177818</v>
+        <v>2.516420615885096</v>
       </c>
     </row>
     <row r="26">
@@ -4827,240 +4827,240 @@
         <v>555</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.181734450105054</v>
+        <v>2.215008742423883</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.846558935460727</v>
+        <v>1.880231944074069</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.767218831734958</v>
+        <v>0.8025732554034448</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.9543264194427081</v>
+        <v>0.9905201368616119</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.390858436220455</v>
+        <v>2.456531466116132</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.677122148326333</v>
+        <v>1.742596751312604</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.345697457713754</v>
+        <v>2.412089508863701</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.607683352735734</v>
+        <v>2.674418604651166</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.189739958298915</v>
+        <v>3.256446327106417</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.0375261691511</v>
+        <v>4.105152272691541</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.131705256086256</v>
+        <v>4.199031734673284</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.672431172431175</v>
+        <v>3.740102151045107</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.809201215205292</v>
+        <v>3.87820134545025</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.407664223990757</v>
+        <v>3.47694228882348</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3.649633885854364</v>
+        <v>3.719699892143829</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.523973214755017</v>
+        <v>3.593366093366093</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.029519160245741</v>
+        <v>3.099088596028267</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>3.645256464871174</v>
+        <v>3.714968612927798</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.140658907082276</v>
+        <v>3.210139273131411</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.706081081081081</v>
+        <v>1.775363461477809</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.8025203117227662</v>
+        <v>0.8724569331514189</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.00584453535943652</v>
+        <v>0.07589025102159752</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>1.722061143283014</v>
+        <v>1.791806404945099</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>1.105579263473999</v>
+        <v>1.175433611181276</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.00165</t>
+          <t>X &gt; 0.001649</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>444</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.082635351005962</v>
+        <v>3.115909643324791</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.972685061586851</v>
+        <v>3.006358070200193</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.659110723626846</v>
+        <v>2.694465147295332</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.071443536559812</v>
+        <v>3.107637253978716</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.28275032811235</v>
+        <v>4.348423358008027</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.794239265443451</v>
+        <v>3.859713868429722</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.922274034290332</v>
+        <v>3.988666085440279</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.868944613996987</v>
+        <v>3.935679865912419</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.784334552893498</v>
+        <v>2.851040921700999</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.36185049347543</v>
+        <v>3.429476597015871</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.636209760590766</v>
+        <v>3.703536239177794</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.131890631890627</v>
+        <v>3.19956161050456</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.908300314304391</v>
+        <v>2.97730044454935</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.91216872849526</v>
+        <v>2.981446793327983</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>3.15413839035886</v>
+        <v>3.224204396648325</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>2.623072313854117</v>
+        <v>2.692465192465193</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.26375339447997</v>
+        <v>2.333322830262496</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.284896104510814</v>
+        <v>3.354608252567438</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.374893141316505</v>
+        <v>2.44437350736564</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.9853603603603673</v>
+        <v>1.054642740757096</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.8926104018128598</v>
+        <v>0.9625470232415125</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.3662048957198039</v>
+        <v>0.4362506113819649</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.767106188328057</v>
+        <v>1.836851449990142</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.592065749960483</v>
+        <v>2.66192009766776</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.001899</t>
+          <t>X &gt; 0.001898</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>361</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.450532333861389</v>
+        <v>1.483806626180218</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.777406680712915</v>
+        <v>2.811079689326256</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.1687311473747</v>
+        <v>2.204085571043187</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.562971075178773</v>
+        <v>2.599164792597676</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.751717910653333</v>
+        <v>2.817390940549011</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.830849282662889</v>
+        <v>1.89632388564916</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.720033012104707</v>
+        <v>2.786425063254654</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.441478366586146</v>
+        <v>2.508213618501578</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.543936259863635</v>
+        <v>0.6106426286711368</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.709159020839351</v>
+        <v>1.776785124379792</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.429501667456073</v>
+        <v>1.4968281460431</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.8733994537318708</v>
+        <v>0.9410704323458035</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.687966406989872</v>
+        <v>1.756966537234831</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.466609595955518</v>
+        <v>1.535887660788241</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.638703287666139</v>
+        <v>1.708769293955605</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.12573009629029</v>
+        <v>1.195122974901366</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.268644712390675</v>
+        <v>1.338214148173201</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>2.548702847541939</v>
+        <v>2.618414995598563</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>1.933801079725832</v>
+        <v>2.003281445774967</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.7358033240997273</v>
+        <v>0.8050857044964559</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.4696112253510805</v>
+        <v>0.5395478467797332</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0.1166478594591638</v>
+        <v>0.1866935751213248</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.6684313361906007</v>
+        <v>0.7381765978526857</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>1.146506617420741</v>
+        <v>1.216360965128018</v>
       </c>
     </row>
     <row r="29">
@@ -5070,571 +5070,571 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.120399142194408</v>
+        <v>1.30795834731888</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.18248390152268</v>
+        <v>3.362260047262588</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.455112204559839</v>
+        <v>3.630725639869823</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.13857916533928</v>
+        <v>5.306850118720597</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.14317239401386</v>
+        <v>6.336247359483906</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.960473993322019</v>
+        <v>5.158025832270702</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.872539368117309</v>
+        <v>5.068671005035647</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.909053215749431</v>
+        <v>4.107865703627276</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.238240513648783</v>
+        <v>2.442868243903753</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.491802363153319</v>
+        <v>2.693843352850202</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.396298616570036</v>
+        <v>1.602715281701535</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.08980745282115521</v>
+        <v>0.300075093270614</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.6922180122413337</v>
+        <v>-0.481790045257867</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.1138224369982908</v>
+        <v>0.3210218632784816</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.2026430486143624</v>
+        <v>0.004175494025574267</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.6349802592669462</v>
+        <v>-0.4253283690143732</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.2583233068580952</v>
+        <v>0.4646452789910924</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>1.180737151036794</v>
+        <v>1.383695360152842</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.7119288071192926</v>
+        <v>0.9169928844218731</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.1284246575342394</v>
+        <v>0.07994790940696106</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.01330644031710904</v>
+        <v>0.2199955980962329</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.4051143687501479</v>
+        <v>-0.197147291640519</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.1303392022680185</v>
+        <v>0.07732742084153443</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.8912120483858033</v>
+        <v>-0.6810986890370287</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.002398</t>
+          <t>X &gt; 0.002397</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>227</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.832486523764622</v>
+        <v>1.865760816083451</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.378368277842767</v>
+        <v>2.412041286456109</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.581839619924033</v>
+        <v>3.617194043592519</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.951746747259506</v>
+        <v>5.98794046467841</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.586476962235459</v>
+        <v>5.652149992131136</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.773641575242245</v>
+        <v>5.839116178228515</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.441304077549447</v>
+        <v>5.507696128699394</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.96010626022472</v>
+        <v>3.026841512140152</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.68003642216366</v>
+        <v>1.746742790971162</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.668315548839153</v>
+        <v>2.735941652379594</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.621088912870789</v>
+        <v>1.688415391457816</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.341995009395887</v>
+        <v>1.40966598800982</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.6580324252699796</v>
+        <v>0.7270325555149384</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.4366756142356252</v>
+        <v>0.5059536790683481</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.6588016439207891</v>
+        <v>0.7288676502102547</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.9487814782639887</v>
+        <v>-0.8793885996529127</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>2.000825268115719</v>
+        <v>2.070394703898245</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.657956389465376</v>
+        <v>3.727668537522</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2.55249364931349</v>
+        <v>2.621974015362625</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.53689427312775</v>
+        <v>0.6061766535244786</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.315279767213497</v>
+        <v>1.385216388642149</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>1.679853345932123</v>
+        <v>1.749899061594284</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.514099878053017</v>
+        <v>1.583845139715102</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.1165726357008481</v>
+        <v>0.1864269834081256</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.002647</t>
+          <t>X &gt; 0.002646</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>182</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.7214829898535982</v>
+        <v>0.7547572821724273</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.034659123560921</v>
+        <v>2.068332132174262</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.04550811002423671</v>
+        <v>0.08086253369272356</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.727319192435473</v>
+        <v>3.763512909854377</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.263148308510331</v>
+        <v>2.328821338406009</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.09866456986876</v>
+        <v>4.16413917285503</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.52360063561693</v>
+        <v>5.589992686766877</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3.596694341746726</v>
+        <v>3.663429593662158</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.63821040676936</v>
+        <v>3.704916775576862</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.512726644351574</v>
+        <v>4.580352747892015</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.688184812565815</v>
+        <v>3.755511291152843</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.958541458541461</v>
+        <v>4.026212437155394</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.932951338955412</v>
+        <v>4.001951469200371</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.16214397847051</v>
+        <v>3.231422043303233</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>3.052663288883757</v>
+        <v>3.122729295173222</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>2.548822239604043</v>
+        <v>2.618215118215119</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>6.810332941059514</v>
+        <v>6.87990237684204</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>7.804250623865343</v>
+        <v>7.873962771921967</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>6.372022138445494</v>
+        <v>6.441502504494629</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>4.910714285714292</v>
+        <v>4.97999666611102</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>5.466414975617433</v>
+        <v>5.536351597046085</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>6.489361018875918</v>
+        <v>6.559406734538079</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>5.665235086456953</v>
+        <v>5.734980348119038</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>4.49039264828739</v>
+        <v>4.560246995994667</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.002896</t>
+          <t>X &gt; 0.002895</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.6539871775628754</v>
+        <v>0.001536992528293979</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.024260126584743</v>
+        <v>1.653515161065897</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.4154403375013942</v>
+        <v>0.2154961120349057</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.22647104729203</v>
+        <v>2.813800370737866</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.1522215565239691</v>
+        <v>0.4912549313031747</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.390647754469398</v>
+        <v>3.989479395546248</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.973486320401946</v>
+        <v>6.528788989801598</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.694931674883385</v>
+        <v>6.250577545048522</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.078729619100642</v>
+        <v>7.616568038221502</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>10.33173984591512</v>
+        <v>10.15491064033071</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.263817233835823</v>
+        <v>9.104466971234352</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.984723330360922</v>
+        <v>8.825717567786356</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.54479587026304</v>
+        <v>10.35156212344679</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.981157180034053</v>
+        <v>8.805979935741931</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>10.33564875978869</v>
+        <v>10.13459160504879</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>9.588426930215441</v>
+        <v>9.404475215733498</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>12.8100379340531</v>
+        <v>12.58181635690173</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>12.70505451795782</v>
+        <v>12.47697565308054</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>10.90775486209768</v>
+        <v>10.70611206711745</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>10.42365771812081</v>
+        <v>10.23070622145633</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>9.880457309122853</v>
+        <v>9.6881600534903</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>10.47564319307755</v>
+        <v>10.27456574771035</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>10.75041835955968</v>
+        <v>10.5490404601924</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>10.00333608069391</v>
+        <v>9.810956551339977</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.003146</t>
+          <t>X &gt; 0.003145</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>114</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.466229471442183</v>
+        <v>2.499503763761012</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.5005249905705611</v>
+        <v>-0.4668519819572197</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.063032472200554</v>
+        <v>-1.027678048532067</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.654018767849855</v>
+        <v>-2.617825050430952</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.142095570417759</v>
+        <v>-2.076422540522081</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.185419919782007</v>
+        <v>4.250894522768277</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.289746770184124</v>
+        <v>4.356138821334071</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.519964054490117</v>
+        <v>7.586699306405549</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>10.19305906688118</v>
+        <v>10.25976543568868</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>13.80518856839245</v>
+        <v>13.87281467193289</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>13.20235485305165</v>
+        <v>13.26968133163867</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>13.80045393203288</v>
+        <v>13.86812491064681</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>14.43034867845801</v>
+        <v>14.49934880870297</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>15.96337783233594</v>
+        <v>16.03265589716867</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>14.42725361084251</v>
+        <v>14.49731961713197</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>14.14512067800774</v>
+        <v>14.21451355661881</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>16.64260593122725</v>
+        <v>16.71217536700978</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>15.66042953267582</v>
+        <v>15.73014168073244</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>14.9993597131515</v>
+        <v>15.06884007920063</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>14.30921052631578</v>
+        <v>14.37849290671251</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>13.76601011731783</v>
+        <v>13.83594673874648</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>14.56724804413137</v>
+        <v>14.63729375979353</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>14.8420232106135</v>
+        <v>14.91176847227558</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>14.76608187134503</v>
+        <v>14.83593621905231</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.003395</t>
+          <t>X &gt; 0.003394</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>97</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>7.150620862290438</v>
+        <v>7.183895154609267</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.691734007439926</v>
+        <v>2.725407016053268</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.252033543353789</v>
+        <v>1.287387967022276</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-2.554543274994003</v>
+        <v>-2.5183495575751</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1729704451365848</v>
+        <v>0.2386434750322621</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.483846398349556</v>
+        <v>4.549321001335827</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.741908101347079</v>
+        <v>4.808300152497026</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.556136960983153</v>
+        <v>7.622872212898585</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.69043653116043</v>
+        <v>10.75714289996793</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>14.04031246059719</v>
+        <v>14.10793856413763</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>13.28374389266098</v>
+        <v>13.35107037124801</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>14.03557782423762</v>
+        <v>14.10324880285155</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>13.94201444080202</v>
+        <v>14.01101457104698</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.78251329987076</v>
+        <v>15.85179136470349</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>14.09265422578192</v>
+        <v>14.16272023207139</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>14.6877142754033</v>
+        <v>14.75710715401438</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>14.55362058125438</v>
+        <v>14.6231900170369</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>13.41770933010754</v>
+        <v>13.48742147816417</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>13.63383249303936</v>
+        <v>13.70331285908849</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>12.78994845360825</v>
+        <v>12.85923083400498</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>11.21582020955875</v>
+        <v>11.2857568309874</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>12.17079298896768</v>
+        <v>12.24083870462984</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>13.47649599050136</v>
+        <v>13.54624125216344</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>14.43148248628444</v>
+        <v>14.50133683399172</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.003644</t>
+          <t>X &gt; 0.003643</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4.296893087002829</v>
+        <v>4.330167379321658</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.063166847720822</v>
+        <v>1.096839856334164</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-3.275084341003001</v>
+        <v>-3.239729917334515</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-5.438153016514995</v>
+        <v>-5.401959299096092</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-1.455596714582519</v>
+        <v>-1.389923684686842</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.630118623061946</v>
+        <v>1.695593226048217</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.8572524910079196</v>
+        <v>0.9236445421578665</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>6.375799294764711</v>
+        <v>6.442534546680143</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>9.315866084425025</v>
+        <v>9.382572453232527</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>14.33913212293097</v>
+        <v>14.40675822647141</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>13.16421602772746</v>
+        <v>13.23154250631449</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>12.88512212425256</v>
+        <v>12.95279310286649</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>14.65918163040309</v>
+        <v>14.72818176064805</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>15.88710018168759</v>
+        <v>15.95637824652032</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>16.67744430496912</v>
+        <v>16.74751031125859</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>15.82322899227167</v>
+        <v>15.89262187088275</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>14.23985993580389</v>
+        <v>14.30942937158642</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>12.68560115738978</v>
+        <v>12.75531330544641</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>12.9017243203216</v>
+        <v>12.97120468637073</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>11.63949275362319</v>
+        <v>11.70877513401992</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>9.64701698230639</v>
+        <v>9.716953603735043</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>12.46961265130147</v>
+        <v>12.53965836696363</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>12.7443878177836</v>
+        <v>12.81413307944568</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>14.11772184083396</v>
+        <v>14.18757618854124</v>
       </c>
     </row>
   </sheetData>
@@ -5824,247 +5824,247 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.003586</t>
+          <t>X &lt; -0.003585</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.297309811547898</v>
+        <v>-7.264035519229068</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.183209963873381</v>
+        <v>-6.149536955260039</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.825808978684151</v>
+        <v>-1.790454555015664</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-3.988877654196159</v>
+        <v>-3.952683936777255</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.689330821649364</v>
+        <v>8.755003851545041</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.630118623061946</v>
+        <v>1.695593226048217</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.306527853326756</v>
+        <v>2.372919904476703</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.027973207808195</v>
+        <v>2.094708459723627</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.6202139105119926</v>
+        <v>0.6869202793194944</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.60289686257628</v>
+        <v>-1.535270759035839</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.328537595460944</v>
+        <v>-1.261211116873916</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.290919225701835</v>
+        <v>1.358590204315767</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-2.732122717422989</v>
+        <v>-2.66312258717803</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>4.292897283136853</v>
+        <v>4.362175347969576</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-3.612410767494644</v>
+        <v>-3.542344761205179</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-1.56807535555442</v>
+        <v>-1.498682476943344</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-3.151444412022187</v>
+        <v>-3.081874976239661</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.3578771034797867</v>
+        <v>-0.2881649554231629</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>5.655347508727395</v>
+        <v>5.72482787477653</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>7.291666666666657</v>
+        <v>7.360949047063386</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>6.748466257668703</v>
+        <v>6.818402879097356</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>8.121786564344951</v>
+        <v>8.191832280007112</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>8.396561730827081</v>
+        <v>8.466306992489166</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>8.320620391558613</v>
+        <v>8.39047473926589</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.003337</t>
+          <t>X &lt; -0.003336</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>84</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-7.245549977179365</v>
+        <v>-7.212275684860536</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.818820729918933</v>
+        <v>-2.785147721305592</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.5033835678996965</v>
+        <v>0.5387379915681834</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.210409745293461</v>
+        <v>-0.1742160278745573</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.948129993492017</v>
+        <v>9.013803023387695</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.182913654117847</v>
+        <v>3.248388257104118</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.41004752206382</v>
+        <v>2.476439573213767</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.131492876545259</v>
+        <v>2.198228128460691</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.173008941567893</v>
+        <v>2.239715310375395</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.399173530798464</v>
+        <v>1.466799634338905</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.864008988389983</v>
+        <v>2.931335466977011</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>3.775391275391279</v>
+        <v>3.843062254005211</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.460423866427938</v>
+        <v>1.529423996672897</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.191448007774532</v>
+        <v>7.260726072607255</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.5801358163562824</v>
+        <v>0.650201822645748</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>2.36567205645386</v>
+        <v>2.435064935064936</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1493740186474426</v>
+        <v>-0.07980458286491654</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>2.126594946209657</v>
+        <v>2.196307094266281</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>7.104622871046224</v>
+        <v>7.174103237095359</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>7.291666666666657</v>
+        <v>7.360949047063386</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>7.938942448144907</v>
+        <v>8.00887906957356</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>6.947286368508223</v>
+        <v>7.017031630170308</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.003088</t>
+          <t>X &lt; -0.003087</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>97</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-8.313296663482753</v>
+        <v>-8.280022371163923</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.524760837920894</v>
+        <v>-4.491087829307553</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.902605631903945</v>
+        <v>-3.867251208235459</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.554543274994003</v>
+        <v>-2.5183495575751</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.29668178534277</v>
+        <v>4.362354815238447</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.3601350581433707</v>
+        <v>0.4256096611296414</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.4127310739106562</v>
+        <v>-0.3463390227607093</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.6912857194292172</v>
+        <v>-0.6245504675137852</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.6497696544065832</v>
+        <v>-0.5830632855990814</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.423605065176012</v>
+        <v>-1.355978961635572</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.9126098720424238</v>
+        <v>0.9799363506294512</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.695371638670608</v>
+        <v>2.76304261728454</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.601808255235014</v>
+        <v>2.670808385479972</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>6.504162784406837</v>
+        <v>6.57344084923956</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.6905923701118084</v>
+        <v>0.760658376401274</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>2.316580254784739</v>
+        <v>2.385973133395815</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.151558725584266</v>
+        <v>1.221128161366792</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.046575309488986</v>
+        <v>1.11628745754561</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>5.386409812626987</v>
+        <v>5.455890178676121</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>5.573453608247419</v>
+        <v>5.642735988644148</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>6.061181034301008</v>
+        <v>6.13111765572966</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>5.985225978658399</v>
+        <v>6.05527169432056</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>5.229073310088985</v>
+        <v>5.29881857175107</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>6.18405980587206</v>
+        <v>6.253914153579338</v>
       </c>
     </row>
     <row r="9">
@@ -6077,240 +6077,240 @@
         <v>126</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.892871405750796</v>
+        <v>-2.478056415757543</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.040792983387256</v>
+        <v>-2.03763941565775</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.905690297867082</v>
+        <v>-1.925270867789521</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.406885185863395</v>
+        <v>-3.413418685681862</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.9522544779314543</v>
+        <v>0.5688625471972131</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.13941909093824</v>
+        <v>1.204893693924511</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.4208486159189349</v>
+        <v>-0.3544565647689879</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.6994032614374959</v>
+        <v>-0.6326680095220638</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1295143783882864</v>
+        <v>0.1962207471957882</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.431722607184291</v>
+        <v>-1.36409650364385</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.20484138434049</v>
+        <v>1.272167862927517</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.500550630471899</v>
+        <v>2.568221609085832</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.7382641363942</v>
+        <v>3.807264266639159</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.091710474966142</v>
+        <v>5.160988539798865</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.283172936716248</v>
+        <v>1.353238943005714</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2.665634561140777</v>
+        <v>2.735027439751853</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.744139292188706</v>
+        <v>1.813708727971232</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.5392933589080684</v>
+        <v>0.1340648745437534</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>3.136368902792263</v>
+        <v>2.712160979877524</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>3.323412698412696</v>
+        <v>2.899006789845551</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.573863083065532</v>
+        <v>3.143862196682669</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>4.291558821073728</v>
+        <v>4.361604536735889</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>5.359984781206641</v>
+        <v>5.429730042868727</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.002589</t>
+          <t>X &lt; -0.002588</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>163</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2652725336431487</v>
+        <v>-0.3864092436094779</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.180028627712197</v>
+        <v>-2.785147721305592</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.180704701554426</v>
+        <v>-1.521427391950496</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.504254112308558</v>
+        <v>-2.51213914893021</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.04025560464968</v>
+        <v>-1.310872301287638</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2433348940819187</v>
+        <v>-0.1778602910956479</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.625957123696921</v>
+        <v>-1.559565072546974</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.6849995740935384</v>
+        <v>-0.6182643221781063</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.03372741150992908</v>
+        <v>0.03297895729757272</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.8075628222793583</v>
+        <v>-0.7399367187389174</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.6863086399579288</v>
+        <v>0.7536351185449561</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.675507419409861</v>
+        <v>4.743178398023794</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.941260103361742</v>
+        <v>3.010260233606701</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.939415487449338</v>
+        <v>4.008693552282061</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.8414598581681361</v>
+        <v>0.9115258644576016</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.436519907789517</v>
+        <v>1.505912786400593</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-1.136598176603314</v>
+        <v>-1.067028740820788</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.8824614370798542</v>
+        <v>-1.17186944464197</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.174152523397979</v>
+        <v>0.8732902289652884</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.361196319018411</v>
+        <v>1.060136038933315</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.817995910020457</v>
+        <v>0.517589870967285</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>1.969034719408512</v>
+        <v>2.039080435070673</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>3.47080375092132</v>
+        <v>3.540549012583405</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>4.621856276683523</v>
+        <v>4.691710624390801</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.00234</t>
+          <t>X &lt; -0.002339</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>215</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.490262155893042</v>
+        <v>1.964534052487323</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.954005831898449</v>
+        <v>1.429781493623622</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.4031258248482317</v>
+        <v>-0.6625117390933113</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.7179432472797131</v>
+        <v>0.6915848379263068</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.64625144390704</v>
+        <v>2.441722136238312</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.915984864253268</v>
+        <v>1.981459467239539</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.150459249452133</v>
+        <v>-1.084067198302186</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.722591876622062</v>
+        <v>-3.65585662470663</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.846213426278332</v>
+        <v>-1.77950705747083</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.161333240717489</v>
+        <v>-2.093707137177049</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.886973973602153</v>
+        <v>-1.819647495015126</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.338519278886253</v>
+        <v>3.406190257500185</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.048890445720211</v>
+        <v>4.11789057596517</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.827533634685857</v>
+        <v>3.89681169951858</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1.333740010327453</v>
+        <v>1.403806016616919</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.5526532709580039</v>
+        <v>0.6220461495690799</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.2346505589255159</v>
+        <v>0.02941341626133465</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.4070182266329354</v>
+        <v>-0.0754272875598474</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.833305041588872</v>
+        <v>1.057895286025037</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>2.020348837209305</v>
+        <v>1.244741095993064</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>2.872497265420648</v>
+        <v>2.363717779250969</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2.796542209778039</v>
+        <v>2.575890251021598</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>4.001549934399705</v>
+        <v>4.07129519606179</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>2.995376036991701</v>
+        <v>3.065230384698978</v>
       </c>
     </row>
     <row r="12">
@@ -6323,76 +6323,76 @@
         <v>276</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.754450022820635</v>
+        <v>2.345068379525785</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.979950391432837</v>
+        <v>2.561478561716456</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1065581710742975</v>
+        <v>-0.09449402464255741</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.54330249228974</v>
+        <v>1.524648571345914</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.328570341674293</v>
+        <v>3.180469690054352</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.006774381204373</v>
+        <v>1.072248984190644</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.558206446190148</v>
+        <v>-1.491814395040201</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.987298726117309</v>
+        <v>-3.920563474201877</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.153667965754181</v>
+        <v>-2.086961596946679</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.210657498387413</v>
+        <v>-2.143031394846972</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.653144109408274</v>
+        <v>-2.585817630821246</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.802529012206435</v>
+        <v>2.870199990820367</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.753306610923588</v>
+        <v>2.822306741168546</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.890372738957339</v>
+        <v>2.959650803790062</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>2.231441499920038</v>
+        <v>2.301507506209504</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.392809793269016</v>
+        <v>1.462202671880092</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1.118183364017852</v>
+        <v>0.9698625958345275</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>1.2326633663575</v>
+        <v>0.8650218920133455</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.394477943509997</v>
+        <v>1.797759151073862</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>2.58152173913043</v>
+        <v>1.984604961041889</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>3.849915533031023</v>
+        <v>3.461088730416307</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>4.136279317968125</v>
+        <v>3.974807218530621</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>4.773373325029972</v>
+        <v>4.843118586692057</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>4.335113145181786</v>
+        <v>4.404967492889064</v>
       </c>
     </row>
     <row r="13">
@@ -6405,158 +6405,158 @@
         <v>347</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.540567859785924</v>
+        <v>2.225074674277529</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.231496280738021</v>
+        <v>0.9263368725319481</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5169117064278339</v>
+        <v>0.2043345672771153</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.359936575052856</v>
+        <v>2.183262174674063</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.562848608210629</v>
+        <v>2.294674694089871</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.0908958696916784</v>
+        <v>-0.1847697086317481</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.000125638109338</v>
+        <v>-1.933733586959391</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.699134829082446</v>
+        <v>-3.632399577167014</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.668982400423452</v>
+        <v>-1.602276031615951</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.158726902101968</v>
+        <v>-2.091100798561527</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.884367634986631</v>
+        <v>-1.817041156399604</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.0979020979021</v>
+        <v>2.165573076516033</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.109774515778597</v>
+        <v>2.178774646023555</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.456599522926055</v>
+        <v>2.525877587758778</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2.365850102070574</v>
+        <v>2.43591610836004</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.859770550552355</v>
+        <v>0.7575757575757578</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.6125307432573166</v>
+        <v>0.3395677115073781</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.9668187148001905</v>
+        <v>0.5188179167771025</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.93220907794278</v>
+        <v>1.302891115883241</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2.872838616714702</v>
+        <v>2.232743918858269</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>3.19419152183778</v>
+        <v>2.723164783859268</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2.830052028154832</v>
+        <v>2.54007363211042</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>3.681196070717647</v>
+        <v>3.568755768101354</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2.74070141732814</v>
+        <v>2.810555765035417</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.001592</t>
+          <t>X &lt; -0.001591</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.921623275100274</v>
+        <v>2.688266810618664</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1484855955963482</v>
+        <v>-0.06441883778600754</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.5344674699513376</v>
+        <v>-0.752626011660233</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.60723514211886</v>
+        <v>-0.7125842414020127</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.186180140818117</v>
+        <v>-1.356004474079384</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.853716382512197</v>
+        <v>-1.90441913450924</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.626582514566223</v>
+        <v>-2.560190463416276</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.118812373759994</v>
+        <v>-3.052077121844562</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.581569813010859</v>
+        <v>-1.514863444203357</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.141730010105078</v>
+        <v>-2.074103906564638</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.149422025041019</v>
+        <v>-3.082095546453992</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.291763791763792</v>
+        <v>-1.224092813149859</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.4931780871740088</v>
+        <v>-0.42417795692905</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.1401659564924884</v>
+        <v>0.2094440213252113</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.5187652825448126</v>
+        <v>-0.448699276255347</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.937376786209541</v>
+        <v>-1.991064491064492</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.660308005976276</v>
+        <v>-0.8429303459906805</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.638382012315688</v>
+        <v>-0.9477710498118626</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.5672665492071616</v>
+        <v>0.122821185813315</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.964092872570191</v>
+        <v>1.507986877184742</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>2.419461928664383</v>
+        <v>1.954311319726841</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>2.044890088504772</v>
+        <v>1.581266595107621</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.319665254986901</v>
+        <v>1.988295997986413</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.7252857378442528</v>
+        <v>0.53371197593912</v>
       </c>
     </row>
     <row r="15">
@@ -6566,79 +6566,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2603048237573944</v>
+        <v>0.1050812253302524</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.299937314483792</v>
+        <v>-1.44707578780136</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.475313173954945</v>
+        <v>-3.616257339897736</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.050948592411267</v>
+        <v>-2.116777012988734</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.909639430066882</v>
+        <v>-3.019764501983111</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.380369553902213</v>
+        <v>-3.401858048314601</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.824288317535171</v>
+        <v>-3.757896266385224</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.444948226211636</v>
+        <v>-3.378212974296204</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.91001110855742</v>
+        <v>-2.843304739749918</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.025951782484746</v>
+        <v>-2.958325678944306</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.067381989053622</v>
+        <v>-4.000055510466595</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.688581155686414</v>
+        <v>-3.620910177072481</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.18149342680514</v>
+        <v>-2.112493296560181</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.238376553628974</v>
+        <v>-2.169098488796251</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.81454528507934</v>
+        <v>-1.840399681113645</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-3.103446283951612</v>
+        <v>-3.219696969696969</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.821943873035487</v>
+        <v>-2.03782463299023</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.831147091002585</v>
+        <v>-2.142665336811412</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.021413613199208</v>
+        <v>-1.337703462520224</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.2595514950166091</v>
+        <v>-0.06479352719402698</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.6475233846792534</v>
+        <v>0.3170254686290477</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.3391778686927722</v>
+        <v>0.009665085458678391</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1.215511187651252</v>
+        <v>0.881044897168664</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.1379003993009817</v>
+        <v>-0.09091579470301525</v>
       </c>
     </row>
     <row r="16">
@@ -6648,79 +6648,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.524515106538189</v>
+        <v>-0.6382361473745277</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.23531531724138</v>
+        <v>-2.341636983677198</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.343734226586527</v>
+        <v>-3.450292175472462</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.27609768054662</v>
+        <v>-2.391341410137557</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.702202962909539</v>
+        <v>-2.919080366188609</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.840235367710179</v>
+        <v>-3.055973172093054</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.806883694867402</v>
+        <v>-4.021054161122073</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.820888075835697</v>
+        <v>-3.965897600882428</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.117996349437398</v>
+        <v>-3.194384450901154</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.098180966556036</v>
+        <v>-3.103245028176033</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.485197360816365</v>
+        <v>-3.417870882229337</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.028841528841525</v>
+        <v>-3.961170550227592</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.036930630926548</v>
+        <v>-2.967930500681589</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.993737177410651</v>
+        <v>-2.924459112577928</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.385805527068499</v>
+        <v>-2.392126219682289</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-3.040416108254995</v>
+        <v>-3.120490620490621</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.701071988672105</v>
+        <v>-2.857582360642695</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.198379724509692</v>
+        <v>-2.433322535363345</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.506118362864107</v>
+        <v>-1.744219058710371</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.30833333333333</v>
+        <v>-0.5524019697358966</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.2954177485454395</v>
+        <v>0.04549451256350068</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.2347971758705185</v>
+        <v>-0.4826203872762775</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.1477604855747714</v>
+        <v>-0.3953074732473496</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.8140883934590804</v>
+        <v>-1.05880062305296</v>
       </c>
     </row>
     <row r="17">
@@ -6730,735 +6730,735 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.9050513953014701</v>
+        <v>-0.9873611612987716</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.185029137968343</v>
+        <v>-1.267290578448446</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.045856023224715</v>
+        <v>-2.128971427966057</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5024133391838532</v>
+        <v>-0.5942378988358854</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.753663840515884</v>
+        <v>-1.916932907348247</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.298879062968986</v>
+        <v>-1.463705785533854</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.80356221205065</v>
+        <v>-1.968835919182141</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.444948226211636</v>
+        <v>-2.608600263273367</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.298169003294269</v>
+        <v>-2.40476577691787</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.650951782484739</v>
+        <v>-2.699867032327759</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.587118831158875</v>
+        <v>-2.577902928696709</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.287265366212736</v>
+        <v>-3.219594387598804</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.201230268910408</v>
+        <v>-2.132230138665449</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.362468395456929</v>
+        <v>-2.353309015112039</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.695331332528582</v>
+        <v>-1.748294417955748</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.883334832468549</v>
+        <v>-1.996012759170647</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.216523923006655</v>
+        <v>-1.393087790884962</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.9421881225734197</v>
+        <v>-1.120467455384983</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.6637387108746751</v>
+        <v>-0.8427744000354309</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.009941675503711167</v>
+        <v>-0.1716099110499414</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.1517460565563411</v>
+        <v>-0.3345217156876998</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.6955369736735051</v>
+        <v>-0.8764907013593515</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.9959760428392883</v>
+        <v>-1.175058765309906</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.22237169067504</v>
+        <v>-1.400971001278485</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.0005943</t>
+          <t>X &lt; -0.0005944</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.893967427992024</v>
+        <v>-0.9554251185470619</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.012721577929362</v>
+        <v>-1.074600020996797</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.721490957746042</v>
+        <v>-1.78426635961722</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.931229805736173</v>
+        <v>-0.9983918520503821</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.678275074973136</v>
+        <v>-1.800283090099619</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.272167347354902</v>
+        <v>-1.395284280404042</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.825713850412946</v>
+        <v>-1.948826677245286</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.314863979450159</v>
+        <v>-2.437073676652432</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.139775603774794</v>
+        <v>-2.262634985966322</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.224549860366785</v>
+        <v>-2.300996143766149</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.036323237523632</v>
+        <v>-2.064979482046446</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.573815073815069</v>
+        <v>-2.553954383975281</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.8400687444095</v>
+        <v>-1.820520632341491</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.494200539823964</v>
+        <v>-1.52480364315501</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.9804365991384074</v>
+        <v>-1.063222565197236</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.198553979682295</v>
+        <v>-1.330162085976035</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.109169701626513</v>
+        <v>-1.241545141157196</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.076868257253551</v>
+        <v>-1.209749029650062</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.5499120798492001</v>
+        <v>-0.6842732741308879</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.5718777103208978</v>
+        <v>-0.7058904804502859</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.6300059645535114</v>
+        <v>-0.7652188048703366</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.088855725283487</v>
+        <v>-1.222811047679706</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.458510732941043</v>
+        <v>-1.590709559893227</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.744842960316376</v>
+        <v>-1.876377957542694</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.000345</t>
+          <t>X &lt; -0.0003451</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.5104850421144249</v>
+        <v>-0.5589036761585859</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.3702867311665941</v>
+        <v>-0.4197458276018082</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.261087697664067</v>
+        <v>-1.310520230239057</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.6234320970913316</v>
+        <v>-0.676015584906672</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.385828535214877</v>
+        <v>-1.480569270984603</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.231406818596781</v>
+        <v>-1.326367409354603</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.037063681804142</v>
+        <v>-2.131128144332102</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.494655828550819</v>
+        <v>-2.587972065902768</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.339827648810761</v>
+        <v>-2.43362010694252</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.308981274649689</v>
+        <v>-2.363579232536317</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.815163338916939</v>
+        <v>-1.829699699463553</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.27285525601777</v>
+        <v>-2.286845849587102</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.671444265440194</v>
+        <v>-1.686690539851284</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.410702529859861</v>
+        <v>-1.468852079063062</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.146622385090105</v>
+        <v>-1.249160702173974</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.242467234504815</v>
+        <v>-1.343781889169875</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.6724487885995174</v>
+        <v>-0.77577527883561</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.6605198997287189</v>
+        <v>-0.7641732855689369</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.5480629273349251</v>
+        <v>-0.6517710597987332</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.7593888070692145</v>
+        <v>-0.862252127679632</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.6698584782684023</v>
+        <v>-0.7740536479660705</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.9233590044635775</v>
+        <v>-1.027050925448989</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.9001921062765135</v>
+        <v>-1.003571754671484</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.080402878194995</v>
+        <v>-1.183493799292521</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -9.563e-05</t>
+          <t>X &lt; -9.584e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.7544133765537211</v>
+        <v>-0.7568155408757988</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.8139226051181865</v>
+        <v>-0.8772034986590569</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.429508955735827</v>
+        <v>-1.431880042879641</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.196306846364237</v>
+        <v>-1.19958968098544</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.13781658025944</v>
+        <v>-2.171456229430902</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.673415698855798</v>
+        <v>-1.707820779494689</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.535007422991129</v>
+        <v>-2.568393716592105</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.963483415743184</v>
+        <v>-2.996313102665901</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.133196670261192</v>
+        <v>-3.165729356814239</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.650629876803109</v>
+        <v>-2.684604517065246</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.158722258331458</v>
+        <v>-2.193457272354514</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.730105473216305</v>
+        <v>-1.765856129974296</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.594548122367577</v>
+        <v>-1.631344898040943</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.596616574281462</v>
+        <v>-1.633602772761975</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.422493456211626</v>
+        <v>-1.460287198437271</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.834976895576311</v>
+        <v>-1.871657754010698</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.319375188648614</v>
+        <v>-1.357139551187018</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.265567081477883</v>
+        <v>-1.303546835035505</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.259460769790174</v>
+        <v>-1.297351643199292</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.344230769230769</v>
+        <v>-1.381884695770353</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.482239817864944</v>
+        <v>-1.520052355485717</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.522189968645492</v>
+        <v>-1.560026108141997</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.581279188417376</v>
+        <v>-1.618865805727118</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.683045264817409</v>
+        <v>-1.720541181345233</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0001537</t>
+          <t>X &lt; 0.0001534</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1873</v>
+        <v>1877</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.142475836130544</v>
+        <v>-1.167162902905652</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.8694552317407656</v>
+        <v>-0.8950551914026335</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.383527479518222</v>
+        <v>-1.409427997693705</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.223540829739925</v>
+        <v>-1.250476790482189</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.876897692000796</v>
+        <v>-1.926522473899837</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.978124849067669</v>
+        <v>-2.027400158525985</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.351857239840939</v>
+        <v>-2.401118630637995</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.707298118942404</v>
+        <v>-2.756114939986972</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.060546344953494</v>
+        <v>-3.108618526330538</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.745727672926279</v>
+        <v>-2.79524362823318</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.654094329289151</v>
+        <v>-2.703585167943615</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.479503255365323</v>
+        <v>-2.529672122964215</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.982099639789823</v>
+        <v>-2.034437988799255</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.226148026921869</v>
+        <v>-2.278224642814038</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.110770514294991</v>
+        <v>-2.16376575802385</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-2.388637961014048</v>
+        <v>-2.440519250864078</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.119992053095267</v>
+        <v>-2.172616229816697</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-2.300785372602277</v>
+        <v>-2.353170689412238</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-2.107304711488375</v>
+        <v>-2.159938562408705</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.156033564198189</v>
+        <v>-2.208428943367224</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.402208937782596</v>
+        <v>-2.454646766292704</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.394155464640569</v>
+        <v>-2.446728163028432</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.622261834978069</v>
+        <v>-2.674129179201351</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.614328578163686</v>
+        <v>-2.666330369101622</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.000403</t>
+          <t>X &lt; 0.0004027</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2118</v>
+        <v>2121</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.6615104762785791</v>
+        <v>-0.7024142776110764</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.6915399110493325</v>
+        <v>-0.7325067862568204</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.7505401614798544</v>
+        <v>-0.7451088805139889</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7371592664302682</v>
+        <v>-0.7786287411149289</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.310465723690506</v>
+        <v>-1.368929508877557</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.378349053212283</v>
+        <v>-1.436711589286055</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.469733898701207</v>
+        <v>-1.528193149847397</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.769073910619468</v>
+        <v>-1.827219205362873</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.029656653502762</v>
+        <v>-2.087464999950981</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.980170702204305</v>
+        <v>-2.038274526472961</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.00794918014256</v>
+        <v>-2.019126442247781</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.979135887586594</v>
+        <v>-1.990438516204421</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.668140852085109</v>
+        <v>-1.680171286093113</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.486496854380846</v>
+        <v>-1.498854718883422</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.930106644520869</v>
+        <v>-1.942018163940425</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-2.107293046802873</v>
+        <v>-2.118828017137083</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.602595307162851</v>
+        <v>-1.614892302163163</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.586076563072027</v>
+        <v>-1.59844070612327</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.483852556807427</v>
+        <v>-1.496326364660668</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.599316682375118</v>
+        <v>-1.61159997254444</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.690949112439732</v>
+        <v>-1.70325437137344</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.692268672187737</v>
+        <v>-1.704609042431066</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.00347656998477</v>
+        <v>-2.015327779191921</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.910524659145509</v>
+        <v>-1.922544140261813</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.0006524</t>
+          <t>X &lt; 0.0006519</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2400</v>
+        <v>2403</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.351793712808167</v>
+        <v>-0.3844579955424337</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4585124447551578</v>
+        <v>-0.449850715905491</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.5956310069513151</v>
+        <v>-0.6281644129579931</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.3776667307322654</v>
+        <v>-0.4105425023355807</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.9265722644264542</v>
+        <v>-0.9710579730340072</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.088621262578364</v>
+        <v>-1.132918168811969</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.09390267199808</v>
+        <v>-1.138279041504852</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.349270289648381</v>
+        <v>-1.393378005518329</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.325955861744738</v>
+        <v>-1.370115718810482</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.620907741146937</v>
+        <v>-1.664788126955102</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.861880538577033</v>
+        <v>-1.905466803600092</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.744627677463498</v>
+        <v>-1.788407725290853</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.559958903021595</v>
+        <v>-1.604082927223416</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.757376335240679</v>
+        <v>-1.801299068986879</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.977238316360314</v>
+        <v>-2.020966147029675</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-2.022478552626978</v>
+        <v>-2.06612998504329</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.841858241252154</v>
+        <v>-1.885771783022996</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.798117083240527</v>
+        <v>-1.842120231832276</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.641045874622513</v>
+        <v>-1.685254459471629</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.471505823627282</v>
+        <v>-1.515937810712529</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.408004820150687</v>
+        <v>-1.452586314585091</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.251441059977786</v>
+        <v>-1.296251121119774</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.410342397283799</v>
+        <v>-1.454959495730954</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.336988304093566</v>
+        <v>-1.381730294297235</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.0009017</t>
+          <t>X &lt; 0.0009012</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2578</v>
+        <v>2582</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5022644276654447</v>
+        <v>-0.512248265063441</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.3939123050105025</v>
+        <v>-0.4041953403532119</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.3893590620495573</v>
+        <v>-0.4001969369941065</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.08118946595771348</v>
+        <v>-0.09277684190040958</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.4248644873191765</v>
+        <v>-0.445470882252998</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.6012964860244949</v>
+        <v>-0.6215751128592544</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.350756221398882</v>
+        <v>-0.3717254719501213</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6459789448741375</v>
+        <v>-0.6666129580894093</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.6982745506180237</v>
+        <v>-0.7188265969535763</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.103031054739454</v>
+        <v>-1.123265667590807</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.424186413275109</v>
+        <v>-1.443836567154555</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.48844398844399</v>
+        <v>-1.508114454149137</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.355059221361053</v>
+        <v>-1.375374637011191</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.43812437759383</v>
+        <v>-1.458409729861877</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.649418548876469</v>
+        <v>-1.669641591369796</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.766468038563261</v>
+        <v>-1.786299286299283</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.568734799710349</v>
+        <v>-1.588936625021297</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.651231974032122</v>
+        <v>-1.671360529197329</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.41260515837692</v>
+        <v>-1.433035018284087</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.125580945003868</v>
+        <v>-1.146398207383626</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.026298045572922</v>
+        <v>-1.047490093178581</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.9243880227801</v>
+        <v>-0.9457815756037888</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.9369064710936854</v>
+        <v>-0.9581909791986334</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.8736769516239562</v>
+        <v>-0.8951032308505376</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.001151</t>
+          <t>X &lt; 0.00115</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2742</v>
+        <v>2746</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.5095644437254876</v>
+        <v>-0.5169756797013818</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.1019163125803644</v>
+        <v>-0.1100169753655962</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.2191747279485057</v>
+        <v>-0.2275208068554235</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.08024182004951541</v>
+        <v>-0.08899755870815795</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5338554845094095</v>
+        <v>-0.5491867294754798</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4713306523003737</v>
+        <v>-0.4867092551279839</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3178214435724556</v>
+        <v>-0.3336529762924627</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.5395247690916705</v>
+        <v>-0.5551252041830139</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.8038292365760569</v>
+        <v>-0.8190453181063475</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.9765953544043811</v>
+        <v>-0.9917924981662765</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.153362025351257</v>
+        <v>-1.16823477068673</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.085071428208686</v>
+        <v>-1.1001332983274</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.062797554359761</v>
+        <v>-1.078224067993659</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.9723116821479394</v>
+        <v>-0.9879434968170244</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.028370181462684</v>
+        <v>-1.044120189280612</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.248180757398949</v>
+        <v>-1.263451508549551</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.9609245391830541</v>
+        <v>-0.9766616911277666</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.117322708188354</v>
+        <v>-1.132873415146783</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.9890550806586589</v>
+        <v>-1.004740819611278</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.853514202476326</v>
+        <v>-0.8693539832396269</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.6103679864114255</v>
+        <v>-0.6267286838952373</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.5918231031245327</v>
+        <v>-0.6082436645533633</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.769325613506588</v>
+        <v>-0.7854195286696282</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.6049496461796409</v>
+        <v>-0.6213157966387755</v>
       </c>
     </row>
     <row r="26">
@@ -7468,243 +7468,243 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2865</v>
+        <v>2869</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4192737603214383</v>
+        <v>-0.4250794785771959</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3549844853414399</v>
+        <v>-0.3609577063165474</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1475420830259537</v>
+        <v>-0.1541273898785107</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1835879247108068</v>
+        <v>-0.1902868383378902</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4600993176499202</v>
+        <v>-0.4720827436615167</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.322859102435352</v>
+        <v>-0.334998682708175</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.4517217519192016</v>
+        <v>-0.463863367089175</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.5023478864173327</v>
+        <v>-0.5144895409294179</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.6146894711305251</v>
+        <v>-0.626673963780874</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7783351941225547</v>
+        <v>-0.7902738506221993</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.7967673443807826</v>
+        <v>-0.8086268607715681</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.7084460551613816</v>
+        <v>-0.7204986788719268</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.7350857699718247</v>
+        <v>-0.7473617176128116</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6578273545443025</v>
+        <v>-0.6702684856884389</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.7047831616733404</v>
+        <v>-0.7173153023418308</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.6807536144061999</v>
+        <v>-0.6931936676462271</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.5854398098664433</v>
+        <v>-0.5980508243378608</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.7046734023000738</v>
+        <v>-0.7171504626695366</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.607339962867826</v>
+        <v>-0.6199120725775629</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.3300365981178146</v>
+        <v>-0.3429609192900145</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.1552994327078565</v>
+        <v>-0.1685980494077413</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.001131397671606749</v>
+        <v>-0.01467052919435474</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.3334765996238858</v>
+        <v>-0.3464991479946065</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.2141698049661684</v>
+        <v>-0.2273843339859241</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.00165</t>
+          <t>X &lt; 0.001649</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2976</v>
+        <v>2980</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4563821593353197</v>
+        <v>-0.4606939332787903</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4402508897079969</v>
+        <v>-0.444644564679848</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3939423294262028</v>
+        <v>-0.3986479591466647</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4551805508119315</v>
+        <v>-0.4599303135888491</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6349052239338633</v>
+        <v>-0.6437812507354295</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5626727567992234</v>
+        <v>-0.571618731682058</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.5818542169144365</v>
+        <v>-0.5909134941393006</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.5741348290824462</v>
+        <v>-0.5832582978855498</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.413321478263029</v>
+        <v>-0.422658487223778</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.4992179328103887</v>
+        <v>-0.5085796957498445</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.540139556273779</v>
+        <v>-0.5494053091195923</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.4653813388753179</v>
+        <v>-0.4748012550347624</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4323017541182352</v>
+        <v>-0.4419663648879677</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.4330217399369971</v>
+        <v>-0.4427298917182583</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.4691582731388095</v>
+        <v>-0.4789383580166771</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.3902962826243979</v>
+        <v>-0.400085189241814</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.3369448565702768</v>
+        <v>-0.3468347293728016</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.4890992187802894</v>
+        <v>-0.4988098004487398</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.3537244396995973</v>
+        <v>-0.3635852051156903</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.1468120805369182</v>
+        <v>-0.1569240539196244</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.1330376026871107</v>
+        <v>-0.1432688160641007</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.05459871514425885</v>
+        <v>-0.06495481940093839</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.2635522833784592</v>
+        <v>-0.2735867305587476</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.3867194868892625</v>
+        <v>-0.3966082293169393</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.001899</t>
+          <t>X &lt; 0.001898</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3059</v>
+        <v>3063</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1699033655171789</v>
+        <v>-0.1735755645013128</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.3254280466528314</v>
+        <v>-0.3289464401448328</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2541921896760613</v>
+        <v>-0.2580009374664627</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3004977454171893</v>
+        <v>-0.3043459260874997</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3227323475457666</v>
+        <v>-0.3300058823939551</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2147990221128708</v>
+        <v>-0.2221917957544122</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.3192236402372544</v>
+        <v>-0.3265907298165445</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.2866255903537009</v>
+        <v>-0.2940776603699362</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.06387800579400249</v>
+        <v>-0.07161857990585929</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.2007830805476729</v>
+        <v>-0.2084561033152781</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.1679850592290606</v>
+        <v>-0.1756680626533011</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.1026692291752482</v>
+        <v>-0.1104801385615772</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.1984872550238919</v>
+        <v>-0.2063321144898467</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.1725141948973459</v>
+        <v>-0.1804280655856019</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.1928200413453354</v>
+        <v>-0.2008026416399602</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.1325036076820325</v>
+        <v>-0.1404882428978809</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.1493740186474426</v>
+        <v>-0.1573600350131983</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.3001897970514307</v>
+        <v>-0.3079986358459053</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.2278401402679506</v>
+        <v>-0.2357185795061056</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.08672053542279201</v>
+        <v>-0.09476228866097358</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.05536566046758651</v>
+        <v>-0.06352797543623012</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.01375690207930802</v>
+        <v>-0.02198903119700191</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.07885742234144288</v>
+        <v>-0.08697185111775241</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.1353020231738782</v>
+        <v>-0.143358246298142</v>
       </c>
     </row>
     <row r="29">
@@ -7714,571 +7714,571 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3128</v>
+        <v>3131</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1038262613521894</v>
+        <v>-0.1215065934573332</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2950112061094075</v>
+        <v>-0.3124459859968169</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3203851266216304</v>
+        <v>-0.3375008288330719</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4766407612068164</v>
+        <v>-0.4934646413154979</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5700051919453699</v>
+        <v>-0.5893715797869135</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.460412716481251</v>
+        <v>-0.4799306347587518</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.4523947521431566</v>
+        <v>-0.4717663927812765</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.3630545607502711</v>
+        <v>-0.382460963191221</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.2079434393844934</v>
+        <v>-0.2275144295816176</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2315742488990296</v>
+        <v>-0.2509685540175255</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1298055383758268</v>
+        <v>-0.1493624610491509</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.008351521090368408</v>
+        <v>-0.02797391101758961</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.06439237323174751</v>
+        <v>0.0449282250988432</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.01059150784049478</v>
+        <v>-0.02994568797853958</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.01886253433069385</v>
+        <v>-0.0003896241240397558</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.05912443740624695</v>
+        <v>0.03970092772259193</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.02406073543942711</v>
+        <v>-0.04338466116774953</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1100112470015162</v>
+        <v>-0.1292389992109548</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.06635276465969042</v>
+        <v>-0.0856756744692504</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.01197318007663029</v>
+        <v>-0.007472005568189388</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.001240971118683376</v>
+        <v>-0.02056755272565169</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.03779341714857054</v>
+        <v>0.01843733049813778</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.0121633260026428</v>
+        <v>-0.007234014784984311</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.08319498661401781</v>
+        <v>0.06373743720467928</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.002398</t>
+          <t>X &lt; 0.002397</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3193</v>
+        <v>3197</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1293452863478137</v>
+        <v>-0.1315303432456361</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1679283356361836</v>
+        <v>-0.1700942441831543</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2529799607102561</v>
+        <v>-0.2551594306698277</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4204937789069092</v>
+        <v>-0.422524863376438</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3948101713659611</v>
+        <v>-0.3989546169818965</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4081646333167157</v>
+        <v>-0.4122797425996581</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3847900391288803</v>
+        <v>-0.3890003177395016</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.2093936182832721</v>
+        <v>-0.2138478130270158</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1188803827403788</v>
+        <v>-0.1234466418276625</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1888704800706194</v>
+        <v>-0.1934159934880668</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1147807807927919</v>
+        <v>-0.1193988454395338</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.09504925651571483</v>
+        <v>-0.09971772492309583</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.04662089904379485</v>
+        <v>-0.05144525875994077</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.03094766295081541</v>
+        <v>-0.03581274872107088</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.04670455127108397</v>
+        <v>-0.05160728527688718</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.06728316012682001</v>
+        <v>0.06228430955420095</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.1419335424569681</v>
+        <v>-0.1466852677231358</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.2595673961890057</v>
+        <v>-0.2641838145543147</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.1811807562208116</v>
+        <v>-0.1858801066481277</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.03812167657179089</v>
+        <v>-0.04298722285225409</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.0934194327776865</v>
+        <v>-0.09826378756930154</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.1193510827939264</v>
+        <v>-0.124172268515764</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.1076082255222417</v>
+        <v>-0.1124242797733999</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.008287500251839219</v>
+        <v>-0.01323707389229156</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.002647</t>
+          <t>X &lt; 0.002646</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3238</v>
+        <v>3242</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.0402667599366211</v>
+        <v>-0.04207222828648582</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1135913989227291</v>
+        <v>-0.1153297941347233</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.002541416392887186</v>
+        <v>-0.004510260843417768</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2082173397861453</v>
+        <v>-0.2099814069875805</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1264639214457759</v>
+        <v>-0.1299740826709268</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.229102257898063</v>
+        <v>-0.2324764814293374</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3088464871527705</v>
+        <v>-0.3121751055512689</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.2011672926238219</v>
+        <v>-0.2046483075649164</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2035518887279579</v>
+        <v>-0.2070294298909872</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2525572722238465</v>
+        <v>-0.2560270884878193</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.2064748187902197</v>
+        <v>-0.2099855775698316</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.2216783216783256</v>
+        <v>-0.2251907386485215</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.2203130636164659</v>
+        <v>-0.2239026029494227</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1771891022418828</v>
+        <v>-0.1808483431368941</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1711070891828896</v>
+        <v>-0.1748190500527542</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.1429099345680598</v>
+        <v>-0.1466200466200434</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.3819662851380201</v>
+        <v>-0.3853931156002659</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4378463666903514</v>
+        <v>-0.4412134311852824</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.3576034625954563</v>
+        <v>-0.3610574240277202</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.2756785934608246</v>
+        <v>-0.2792234729612559</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.306969307486078</v>
+        <v>-0.3105134023612877</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.3645258350109302</v>
+        <v>-0.3680061731460924</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.3183305914588388</v>
+        <v>-0.3218521194442445</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.2523939042582768</v>
+        <v>-0.2560039954568225</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.002896</t>
+          <t>X &lt; 0.002895</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3271</v>
+        <v>3273</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.02958229795291345</v>
+        <v>-7.041440284183409e-05</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.04634520463441305</v>
+        <v>-0.07577565685006959</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.01880334455883315</v>
+        <v>-0.009878540654909784</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1008034597528109</v>
+        <v>-0.1290263759433401</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.006893924596369061</v>
+        <v>-0.02253326082223595</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1536048997920147</v>
+        <v>-0.1830481278418361</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.2706963083150455</v>
+        <v>-0.2996495858541195</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2581517552654802</v>
+        <v>-0.2869678349961404</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3209770886323753</v>
+        <v>-0.3497876440910659</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.4686238164509362</v>
+        <v>-0.4665018274079458</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4203132666996297</v>
+        <v>-0.4183732540037681</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.407774528243614</v>
+        <v>-0.4056874741965686</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4787247363403964</v>
+        <v>-0.4759701219977117</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.4078611459387602</v>
+        <v>-0.405026795704245</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.4695157515879558</v>
+        <v>-0.4662776759178442</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.4357046698999909</v>
+        <v>-0.4328179693921825</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.5822744515478746</v>
+        <v>-0.5792238627720039</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.5776787071027485</v>
+        <v>-0.5745725293123343</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.496109729686367</v>
+        <v>-0.4931735576981993</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.474236641221367</v>
+        <v>-0.4714179552761451</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.4496603967804802</v>
+        <v>-0.4465543858598977</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.4768930142892032</v>
+        <v>-0.4737280695890931</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.4895514473026878</v>
+        <v>-0.4865317988665367</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.4556701546999093</v>
+        <v>-0.4526289151397265</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.003146</t>
+          <t>X &lt; 0.003145</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3306</v>
+        <v>3310</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.08445483921429542</v>
+        <v>-0.08549157787841466</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01714538729719095</v>
+        <v>0.01597272687367735</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.03642491789324964</v>
+        <v>0.03517120910617422</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.09096757051559479</v>
+        <v>0.0896192359607042</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.07344327670003281</v>
+        <v>0.07110608880130087</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1435432824473892</v>
+        <v>-0.1456135743977214</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.147165552753826</v>
+        <v>-0.1492635484316409</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.2580601752594447</v>
+        <v>-0.2600371981149152</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.3498972398748705</v>
+        <v>-0.3517633863664642</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4740335833725098</v>
+        <v>-0.4757824526475218</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.453470458947848</v>
+        <v>-0.4552343279587134</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4741566450427115</v>
+        <v>-0.4759079590047435</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4959480703479713</v>
+        <v>-0.4977192906329932</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.5488012885664375</v>
+        <v>-0.5505189073124157</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.4961408481556688</v>
+        <v>-0.4979495138153212</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.4865853220557881</v>
+        <v>-0.4883829250917842</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.5726704123634008</v>
+        <v>-0.574370814543002</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.5390365237696457</v>
+        <v>-0.5407829166476148</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.516438238386975</v>
+        <v>-0.5182044552123202</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.4928247734139006</v>
+        <v>-0.4946132140510642</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.4742596413944469</v>
+        <v>-0.4760935491147293</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.5020151986187997</v>
+        <v>-0.5038198939059413</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.5116391430329443</v>
+        <v>-0.513422411911634</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.5091752369429372</v>
+        <v>-0.5109657791456144</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.003395</t>
+          <t>X &lt; 0.003394</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3323</v>
+        <v>3327</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.207295344782473</v>
+        <v>-0.2080112925364475</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.07805626269706778</v>
+        <v>-0.07893833399737105</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.03631795864394149</v>
+        <v>-0.03729887479126859</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.07412225476351608</v>
+        <v>0.07298473471311695</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.005020386947421684</v>
+        <v>-0.006918235827292563</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1301805150074529</v>
+        <v>-0.1319235088578665</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1377140975540883</v>
+        <v>-0.1394752137536557</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.2195104178542664</v>
+        <v>-0.2211841473679783</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3106567835597929</v>
+        <v>-0.3122210835717709</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4081241560317395</v>
+        <v>-0.4095989346666755</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3862479489173083</v>
+        <v>-0.3877406664703713</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4082311990857619</v>
+        <v>-0.4097080365009305</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.4056314939285599</v>
+        <v>-0.4071505132988449</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4593170687331067</v>
+        <v>-0.4607802704154054</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.4102603421070938</v>
+        <v>-0.4118057141819307</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.4277118837328402</v>
+        <v>-0.4292172095770326</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.4239342932077221</v>
+        <v>-0.4254497395478722</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.3909635941785581</v>
+        <v>-0.3925232173363042</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.3973803340819728</v>
+        <v>-0.3989259745893037</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.3728960024045662</v>
+        <v>-0.3744657432898535</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.3270999880719216</v>
+        <v>-0.328744268049789</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.3550577202796603</v>
+        <v>-0.3566720800087424</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.3932671814316038</v>
+        <v>-0.3948273441886627</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.4212620527142903</v>
+        <v>-0.4227922070625709</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.003644</t>
+          <t>X &lt; 0.003643</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3351</v>
+        <v>3355</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.08787362863164816</v>
+        <v>-0.08844924487069505</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.02174874369782742</v>
+        <v>-0.02241100091414694</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.06701685039418237</v>
+        <v>0.06621485909243319</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1113119424917031</v>
+        <v>0.1104400567815276</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.0298030187852234</v>
+        <v>0.02842463966905484</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.03338622291221327</v>
+        <v>-0.0346860161865834</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.01756247680508949</v>
+        <v>-0.01890019970608137</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1306593856070037</v>
+        <v>-0.1318703303829452</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1909669518197674</v>
+        <v>-0.1921060828703318</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2940267805296273</v>
+        <v>-0.2950627241396546</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2700151325544624</v>
+        <v>-0.2710737627481308</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2643691426028596</v>
+        <v>-0.2654418544988957</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.3008576836697898</v>
+        <v>-0.3019145993715782</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.326155879957291</v>
+        <v>-0.3271887367042723</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.3424832312627615</v>
+        <v>-0.343513142531755</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.3250380471767613</v>
+        <v>-0.3260752034168632</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.2925998616946117</v>
+        <v>-0.2936795439141804</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2607406850938077</v>
+        <v>-0.2618615346848543</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2652619124261477</v>
+        <v>-0.2663729533808237</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2393815201192169</v>
+        <v>-0.2405196440153006</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.1984627822835776</v>
+        <v>-0.1996634302137394</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.2566070005785335</v>
+        <v>-0.2577409673281252</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.2623397253660684</v>
+        <v>-0.2634610198098173</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.2906961524970271</v>
+        <v>-0.2917862166942911</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/macd/macd_histogram_12_26.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/macd/macd_histogram_12_26.xlsx
@@ -618,2379 +618,2379 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.003461</t>
+          <t>X ≈ -0.003454</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-6.925468336236435</v>
+        <v>-10.61204974269894</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>12.60881828919685</v>
+        <v>10.42969456039268</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.18294187791616</v>
+        <v>9.185261367239697</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>17.10479631780503</v>
+        <v>15.69996832571394</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.14554651198183</v>
+        <v>8.326372322009092</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.33535893019047</v>
+        <v>8.485757489354107</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.937431906397364</v>
+        <v>0.5901798073363409</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.661463684167842</v>
+        <v>0.2869275954472812</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.34056066339808</v>
+        <v>7.525669887613184</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>15.2126894793408</v>
+        <v>13.84860777142693</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>22.13101165301274</v>
+        <v>21.23923917553222</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>15.21686229129224</v>
+        <v>13.85226411719495</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>20.74698966613148</v>
+        <v>19.86497373421344</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>20.53231759493858</v>
+        <v>19.62293000440399</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>19.88253619727286</v>
+        <v>18.94887536743557</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>20.48131962774706</v>
+        <v>19.51435352517369</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>13.70113683089994</v>
+        <v>12.2885098683068</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>13.60045719119979</v>
+        <v>12.15939529954561</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>13.81990542942136</v>
+        <v>12.37697011577767</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>7.351963214053171</v>
+        <v>5.46059971384544</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>13.47284234829105</v>
+        <v>12.03183827287327</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.07574407166104891</v>
+        <v>-2.316903694306582</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.3502079943754453</v>
+        <v>-2.073975393963956</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.2745327102788622</v>
+        <v>-2.236673155781766</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.003211</t>
+          <t>X ≈ -0.003204</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>13</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-15.07385567933158</v>
+        <v>-14.97711143532548</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-15.41171435442537</v>
+        <v>-15.22663605282227</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-32.13397545011695</v>
+        <v>-24.12300955748451</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-17.55947492792441</v>
+        <v>-24.71895817711997</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-25.54854008288658</v>
+        <v>-25.00158760209159</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-17.7184606093068</v>
+        <v>-17.20085121313412</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-18.49166112185159</v>
+        <v>-17.99689957073895</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-18.77402069400449</v>
+        <v>-18.30565713807286</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-18.73832559290889</v>
+        <v>-18.18372949073476</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-19.51351324124511</v>
+        <v>-18.98176931692039</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-11.58412694367732</v>
+        <v>-11.05376274955833</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.200741707754865</v>
+        <v>-3.667831727464986</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.01267602608241</v>
+        <v>18.22149311974545</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.125584831299712</v>
+        <v>2.64015518681402</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>1.470356011705249</v>
+        <v>1.961112724287332</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>2.063655460788794</v>
+        <v>2.521568542474881</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>9.606946346105204</v>
+        <v>17.771360271836</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-5.851847024558232</v>
+        <v>2.286782289929647</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-5.638206923255353</v>
+        <v>2.501441236901819</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-5.453229748169278</v>
+        <v>2.716567534005115</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-5.996883932598109</v>
+        <v>2.150484520672869</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1.613280102132066</v>
+        <v>2.07608977253382</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-5.801790367696654</v>
+        <v>2.320322554376077</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>1.812994248741916</v>
+        <v>9.851238932133704</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.002962</t>
+          <t>X ≈ -0.002955</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>16.54846634298178</v>
+        <v>15.10436366641316</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.911170502046033</v>
+        <v>5.550505917529534</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.336505344672531</v>
+        <v>1.199632847908752</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.732851390224809</v>
+        <v>-2.495069348535253</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-12.0105035506228</v>
+        <v>-12.09279141172006</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.833613557035548</v>
+        <v>6.709222549680426</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.3922258149888975</v>
+        <v>-0.2978337227537509</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.6790897525516115</v>
+        <v>-0.6013375744800129</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.797172005640171</v>
+        <v>-0.474182262141376</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.433836570661825</v>
+        <v>-4.37881474809457</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.286059560973996</v>
+        <v>-0.9964135543314114</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.000964508265767</v>
+        <v>-1.272470812986668</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>7.718834571952932</v>
+        <v>0.7305553162625174</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.6189226437442841</v>
+        <v>-2.632539326216367</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>3.374505621004509</v>
+        <v>-0.1965720735533907</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>3.990640783592106</v>
+        <v>0.3632239327872924</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>3.852481933031001</v>
+        <v>-2.858722801180612</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-3.140844652882237</v>
+        <v>-9.230921209513497</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-6.358620991091087</v>
+        <v>-12.14002432302458</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-6.167201935979463</v>
+        <v>-11.92929549048621</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-6.729452185999243</v>
+        <v>-12.49976748849119</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-1.30273707421928</v>
+        <v>-6.332324699659431</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>5.86578092630306</v>
+        <v>-2.96655668479071</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>9.240049951659692</v>
+        <v>-0.004530298638705688</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.002713</t>
+          <t>X ≈ -0.002705</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.83183524779006</v>
+        <v>6.874881947048486</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.51698352605559</v>
+        <v>-2.607756259682603</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1553760409658196</v>
+        <v>3.076973767397085</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.6275805792916316</v>
+        <v>0.17792659325751</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-7.773329971799129</v>
+        <v>-7.033351293944385</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.898772641734311</v>
+        <v>-6.879762077074012</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.668141383844301</v>
+        <v>-7.672333545059516</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.5661090835064044</v>
+        <v>-3.349480819294428</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.5251153540560338</v>
+        <v>-3.223177925866139</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.39708865058914</v>
+        <v>-1.700877059469718</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.022610054379939</v>
+        <v>-3.747044203522655</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>12.16719576206695</v>
+        <v>5.244460000810129</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2733113909309637</v>
+        <v>-5.136443350147836</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.05282606272655244</v>
+        <v>-5.385598699118859</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.6032719947274998</v>
+        <v>-6.067067215413402</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-2.707354259345379</v>
+        <v>-10.148928457532</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-10.93497418225673</v>
+        <v>-17.21745187366594</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-5.645752186361918</v>
+        <v>-12.7125399672538</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-5.431974373383937</v>
+        <v>-12.50243193491227</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-5.246939181793962</v>
+        <v>-12.29190173954179</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-8.491778558574829</v>
+        <v>-15.18600785372109</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-5.866559818919221</v>
+        <v>-12.94157836452314</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-2.89205501227508</v>
+        <v>-8.052194966442784</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-2.968710532962866</v>
+        <v>-8.216739600961809</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.002463</t>
+          <t>X ≈ -0.002456</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.634948516238495</v>
+        <v>11.8615718302678</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>15.02717158198169</v>
+        <v>14.59633656055657</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.058208051931416</v>
+        <v>-1.213298020469615</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.89025380597614</v>
+        <v>10.96376004744849</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>14.37348917286194</v>
+        <v>12.64219219752773</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.826273984601315</v>
+        <v>6.952036217936033</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.3696111380140295</v>
+        <v>-1.638220416517782</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-13.32365478974837</v>
+        <v>-17.55125209627833</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-7.536013548581167</v>
+        <v>-11.57425004474324</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.423098994118611</v>
+        <v>-10.41795719890081</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-9.972958600595483</v>
+        <v>-14.05618888221359</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.669103719440038</v>
+        <v>-2.615607716643311</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>7.755660535988035</v>
+        <v>6.043435422038478</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.693069033176087</v>
+        <v>1.888258097041572</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>3.006426510502749</v>
+        <v>3.164387269850124</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.135492173419493</v>
+        <v>-0.1865976602972736</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>3.482220636913659</v>
+        <v>5.57956719275905</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>3.374318748101977</v>
+        <v>5.448615664467056</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.681411361627994</v>
+        <v>3.706467944795769</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.876279127693536</v>
+        <v>3.92189832976424</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>8.229504954601673</v>
+        <v>9.233090583273608</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>4.308703325807535</v>
+        <v>7.201200468643357</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>5.733138634954955</v>
+        <v>9.40712334847192</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-2.033159597411938</v>
+        <v>3.365567740577958</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.002214</t>
+          <t>X ≈ -0.002206</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.717839342893946</v>
+        <v>4.24187502582506</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6.647967572037722</v>
+        <v>7.103262793970742</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.954310461808824</v>
+        <v>2.752117584436512</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.507438227483597</v>
+        <v>5.268171792643514</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.804247363385699</v>
+        <v>6.548662446035095</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.167371651671736</v>
+        <v>-1.061356188857921</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.935627675349657</v>
+        <v>-1.851203162931228</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.845533380354091</v>
+        <v>-3.708806650842448</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.173178473779366</v>
+        <v>-2.028109204742456</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.310735303408279</v>
+        <v>-1.265644902987958</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.306685070932538</v>
+        <v>-8.77559185112068</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.9513143231068071</v>
+        <v>0.2842593772612219</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.803937344157703</v>
+        <v>-3.940970588011304</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3892689317175808</v>
+        <v>-2.631985709085562</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>5.499024187942233</v>
+        <v>1.36160393956677</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>4.457582222763506</v>
+        <v>0.3635020944957148</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>4.325313635772133</v>
+        <v>0.2600344820971614</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>4.221952835579849</v>
+        <v>0.1274739618949212</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>4.438996968173484</v>
+        <v>0.3414863023716208</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>4.627211867311509</v>
+        <v>0.5558844926002138</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>7.362461432952436</v>
+        <v>1.550119913481495</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>8.925458927560889</v>
+        <v>3.037006206012727</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>7.560991255323742</v>
+        <v>3.281502837036122</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>9.126991726674198</v>
+        <v>7.807969701362715</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.001965</t>
+          <t>X ≈ -0.001956</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.840016921826582</v>
+        <v>-0.6888967137233308</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.521734590713194</v>
+        <v>-6.698597838542618</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.394105091565024</v>
+        <v>0.6767510875878031</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.868347251139937</v>
+        <v>2.961551511641886</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.086607271966258</v>
+        <v>-5.156522496843891</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-5.108578752008214</v>
+        <v>-6.4419488876459</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.713473030372647</v>
+        <v>-7.23330207799674</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.601568541704005</v>
+        <v>-4.654124141825314</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2517890155584013</v>
+        <v>-1.644544685058314</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.945028641963994</v>
+        <v>-3.880331921808988</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.14392592190049</v>
+        <v>3.606026213830859</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.5345267549033181</v>
+        <v>-1.001577905796402</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2815699223034045</v>
+        <v>0.7756104988603809</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.8979716914341651</v>
+        <v>0.5284244787047925</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3.034228329283131</v>
+        <v>2.738770013094772</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.984516736262549</v>
+        <v>-1.036895489112943</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.123916620215248</v>
+        <v>-2.586799937294145</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.8246022174671737</v>
+        <v>-1.273795792109929</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.6005446502286631</v>
+        <v>-1.060255079999692</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>3.241748824024803</v>
+        <v>3.495892967406867</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.1235132519645461</v>
+        <v>2.930056824379236</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-3.016707891022229</v>
+        <v>-0.04079838941255787</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.328862513137615</v>
+        <v>0.202740536629662</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-3.387439120705537</v>
+        <v>-4.30706653052134</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.001716</t>
+          <t>X ≈ -0.001707</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4.100112026862099</v>
+        <v>3.69012715831952</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.101419741770378</v>
+        <v>-2.963916301054901</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.674708033004997</v>
+        <v>-4.21002851756414</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-9.537238276080075</v>
+        <v>-9.607920192312903</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-12.44749019105711</v>
+        <v>-11.48387784349468</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-7.108595761742912</v>
+        <v>-6.520882776921468</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.442266919690624</v>
+        <v>-4.104580212559455</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.284787499440831</v>
+        <v>-1.199786975664757</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.244790473717181</v>
+        <v>-1.074123235570589</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.015675478021727</v>
+        <v>-2.669295225832052</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.901674258386862</v>
+        <v>-7.21702015909306</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-11.48341229949767</v>
+        <v>-11.51286930751716</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-8.306465083269174</v>
+        <v>-7.806629932954301</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.808723499765541</v>
+        <v>-6.449139985014106</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-9.189976187679626</v>
+        <v>-7.131320465375701</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-10.32139631390984</v>
+        <v>-8.182024193481453</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-4.428235494150634</v>
+        <v>-2.656369233437651</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-5.396307559553961</v>
+        <v>-3.594785818115398</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-3.458080670950416</v>
+        <v>-1.771893782874329</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.6850279644308657</v>
+        <v>-1.558368115692005</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.3655051668796432</v>
+        <v>-1.32016287554746</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.303420093805997</v>
+        <v>-3.007480962223234</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-2.753083312358413</v>
+        <v>-5.183487370064185</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-6.277191427650855</v>
+        <v>-9.379530298637285</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.001466</t>
+          <t>X ≈ -0.001457</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>139</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-8.667812023085808</v>
+        <v>-6.737689542224864</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-6.138604745588871</v>
+        <v>-3.405999448507444</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-13.31475279697172</v>
+        <v>-10.36833235589726</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-6.86371541974281</v>
+        <v>-3.810450941736015</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-8.634203808921299</v>
+        <v>-6.226987414631552</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-8.446906290737182</v>
+        <v>-6.073289390789391</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-7.788464375123155</v>
+        <v>-6.864706397136047</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-4.48644202636865</v>
+        <v>-3.593141785679634</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-7.314127052652069</v>
+        <v>-5.615422777913906</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-5.941282619054611</v>
+        <v>-3.545499922515269</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-7.104186287574699</v>
+        <v>-4.707484118798448</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-11.69293706428463</v>
+        <v>-9.284336391975785</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-7.798636173209836</v>
+        <v>-6.099081029666998</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-10.17841554416422</v>
+        <v>-7.782661208520835</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-6.532854381075865</v>
+        <v>-5.596738657194109</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-7.376362060947493</v>
+        <v>-5.755858523860127</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-6.074340715385965</v>
+        <v>-4.426730689822307</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-6.182254838670062</v>
+        <v>-4.560940844620333</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-6.255153357628849</v>
+        <v>-5.067018832637913</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-5.348883087229176</v>
+        <v>-2.699527195295538</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-5.172004794763545</v>
+        <v>-2.54873420109034</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-5.247850756172646</v>
+        <v>-2.624652502253724</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.815102662395631</v>
+        <v>-0.224539002371813</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-2.171510455187416</v>
+        <v>0.3326999171900482</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.001218</t>
+          <t>X ≈ -0.001207</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.728930882148624</v>
+        <v>-5.112932531158407</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.101769931741714</v>
+        <v>-6.615978894200829</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.86881352224956</v>
+        <v>-3.4692286868789</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.591220433944862</v>
+        <v>-5.318869844681466</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.592078195267646</v>
+        <v>-3.708171819666994</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.728622438226417</v>
+        <v>-5.082816729324172</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-5.216841651986634</v>
+        <v>-6.50237068661783</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-6.456460404640929</v>
+        <v>-7.437806431786285</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.674242366259158</v>
+        <v>-6.685023819981552</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.712469341948143</v>
+        <v>-5.590656582406702</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.021269539774444</v>
+        <v>-4.691160918631532</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.345256350229079</v>
+        <v>-8.119366703678878</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.469212970138614</v>
+        <v>-8.604025365390129</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.017862091578692</v>
+        <v>-7.593564460781877</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-4.653013818787052</v>
+        <v>-5.753527767026021</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-2.710394523282787</v>
+        <v>-4.564517864875604</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-6.222744464897566</v>
+        <v>-7.195712770075808</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-3.627373729414536</v>
+        <v>-4.173637120650284</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-3.41148234849021</v>
+        <v>-4.593342735737401</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-2.548960862846513</v>
+        <v>-3.117386475766743</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.064480003785519</v>
+        <v>-2.421095935804587</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-2.491677316545811</v>
+        <v>-3.761926469268538</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-5.595580982442449</v>
+        <v>-6.683276822071406</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-4.995737559989742</v>
+        <v>-6.214973336611827</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.0009683</t>
+          <t>X ≈ -0.0009572</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.379965099735905</v>
+        <v>-4.027564664604142</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.966440817220622</v>
+        <v>0.3368056444612009</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.065095431672447</v>
+        <v>0.117132539948777</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6.485464294399407</v>
+        <v>5.15662413670622</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.008893493246156</v>
+        <v>0.790578089446349</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.782565636116153</v>
+        <v>4.017455299535264</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6.070287037276948</v>
+        <v>4.767193587035045</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.687344845140281</v>
+        <v>2.416837660649527</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.6626366763723652</v>
+        <v>0.493882428979795</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.150678757974205</v>
+        <v>-1.323247362572694</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.6762123482817302</v>
+        <v>0.4858760330804088</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.3343133806763561</v>
+        <v>0.2108837625398721</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.1254388933569</v>
+        <v>1.151822343454512</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1313716294526017</v>
+        <v>0.3910687814687606</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.761030444270375</v>
+        <v>1.251289509292995</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>2.393158685266634</v>
+        <v>1.811505383970278</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.332079080096165</v>
+        <v>3.25003967251596</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>4.02211513769079</v>
+        <v>3.118047440912854</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.683602373537511</v>
+        <v>2.303885389798658</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.316044038427819</v>
+        <v>0.9743066614836522</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.817175704667754</v>
+        <v>-1.651704452660709</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.41115638110287</v>
+        <v>-1.727400819816403</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-4.209220528724209</v>
+        <v>-4.576246719451149</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-2.73064863686988</v>
+        <v>-2.678499370802349</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.000719</t>
+          <t>X ≈ -0.0007076</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.8204260435420991</v>
+        <v>-0.786594544117456</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.2077031004070307</v>
+        <v>0.3405959128717342</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2335344663232206</v>
+        <v>0.4628184066616967</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.849726086110358</v>
+        <v>-0.5870899956205164</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.290187550993075</v>
+        <v>1.884125131936898</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.100255642640761</v>
+        <v>1.125351912261799</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.880112919210852</v>
+        <v>0.596896353187212</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.687045928433996</v>
+        <v>-0.1625511033222082</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.644570172434356</v>
+        <v>0.8791933782753674</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.5224863655010807</v>
+        <v>1.004583267670881</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2297717307857852</v>
+        <v>3.56643648377699</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4223007628676001</v>
+        <v>3.751483546459468</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.421323584681538</v>
+        <v>2.182419126681047</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.21049598335582</v>
+        <v>5.606248805845929</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.027065754930639</v>
+        <v>4.927779043462472</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.672047399283485</v>
+        <v>5.030213418986605</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.5559950590552845</v>
+        <v>1.71197698436729</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.613216715257423</v>
+        <v>0.2006385003298661</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.03124609423822733</v>
+        <v>2.253510484271537</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-3.115241429127082</v>
+        <v>-1.212150967771308</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.705406644712163</v>
+        <v>-0.8589695100153492</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-2.781252606121264</v>
+        <v>-0.934412530036532</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-3.459158846020159</v>
+        <v>-0.6914365570527039</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-4.011181575433909</v>
+        <v>-1.315014169605021</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.0004698</t>
+          <t>X ≈ -0.0004579</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>205</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.703670076298344</v>
+        <v>2.539129609681069</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.316679736006421</v>
+        <v>4.714045489666809</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.384284709292288</v>
+        <v>3.956835728452241</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.157461362744407</v>
+        <v>1.429215335204432</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3314175649082571</v>
+        <v>-2.227574727242903</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.9420695938756722</v>
+        <v>-0.6213874425834121</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.180140269689453</v>
+        <v>-0.9229450539481761</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.460413040639487</v>
+        <v>-1.708609492278704</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.418410527175496</v>
+        <v>-3.521280351992736</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.732418852978235</v>
+        <v>-1.890957627246301</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.5074807634629863</v>
+        <v>-0.1689176501017116</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.788291493108062</v>
+        <v>0.04130515557084635</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.9397075457239836</v>
+        <v>0.3858087482270491</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.162000092414395</v>
+        <v>-1.804774399271828</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-2.310949230011815</v>
+        <v>-2.971758904049345</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.420916481892206</v>
+        <v>-2.413707786058026</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.859800527471897</v>
+        <v>0.3985488475925294</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.754959823650715</v>
+        <v>0.2658647164121106</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.46817318566886</v>
+        <v>-0.9809470840738541</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.744742009847066</v>
+        <v>-3.6885387180523</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.8238735436669771</v>
+        <v>-2.795805396736938</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.07589025102148383</v>
+        <v>-2.384916238333581</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.301584475698775</v>
+        <v>0.295058154895564</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.71355710052417</v>
+        <v>0.620469701362822</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.0002205</t>
+          <t>X ≈ -0.0002082</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>266</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.791324855175127</v>
+        <v>-1.472846718229981</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.255739093352794</v>
+        <v>-4.327018402100734</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.077449479042492</v>
+        <v>-3.336894796979692</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.920404516504249</v>
+        <v>-4.300915760042059</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-5.766498794987918</v>
+        <v>-4.571026151408248</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.697651891623579</v>
+        <v>-5.161539697939645</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-4.855357036298344</v>
+        <v>-6.695401989717162</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.137931419344824</v>
+        <v>-6.03378509480963</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6.975052750977305</v>
+        <v>-7.029523734245124</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-4.369963453264113</v>
+        <v>-4.094321200102485</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.091177294617459</v>
+        <v>-3.829921663346795</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.8888682583777268</v>
+        <v>0.3746880339297363</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.367567030217351</v>
+        <v>-0.7361508084310415</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.490066001918663</v>
+        <v>-1.732359357971269</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.545286899158668</v>
+        <v>-0.9169238628958993</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-4.582478924584187</v>
+        <v>-2.604184906312447</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-4.340456211937514</v>
+        <v>-2.33578947106534</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-4.069357066134728</v>
+        <v>-2.469943619269216</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-4.605345384458602</v>
+        <v>-3.383057581329695</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-4.042559724866422</v>
+        <v>-2.795361968533868</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-5.336985592080488</v>
+        <v>-4.114568534680942</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-4.285012004617329</v>
+        <v>-3.816616273671571</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-4.762416991383567</v>
+        <v>-4.327269692494852</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-4.462309394982697</v>
+        <v>-3.740432554276552</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 2.878e-05</t>
+          <t>X ≈ 4.146e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.83847557192999</v>
+        <v>-4.516930997819728</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.011197034311422</v>
+        <v>-0.767239945612296</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.263445332354273</v>
+        <v>-0.01554630275589375</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.581142434800924</v>
+        <v>-0.207045736649107</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3359052393640525</v>
+        <v>1.121631822969285</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-4.10150822322715</v>
+        <v>-1.119667799860217</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.316144654153071</v>
+        <v>1.688065631652478</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.199099181910192</v>
+        <v>1.386580708560714</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.738639667979498</v>
+        <v>-0.6430737675391498</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.511555344016081</v>
+        <v>-1.438637484817903</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-6.004294120826572</v>
+        <v>-3.974103611559208</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.468814275262538</v>
+        <v>-5.456316451939955</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-4.63940717215818</v>
+        <v>-2.565871125341531</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-6.441513716589043</v>
+        <v>-4.016813261347551</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-6.704400097173554</v>
+        <v>-4.299042748158378</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-6.110013175230478</v>
+        <v>-3.74214287280865</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-7.429701063196269</v>
+        <v>-3.448535242533403</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-9.115569435001554</v>
+        <v>-5.993807419926775</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-7.713907303088995</v>
+        <v>-4.981098916231019</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-7.527061493121145</v>
+        <v>-4.368162725425236</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-8.46486457808313</v>
+        <v>-6.145256942729318</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-8.145453622496277</v>
+        <v>-6.225013244408814</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-9.452006577998326</v>
+        <v>-6.792566277698455</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-8.7373249972295</v>
+        <v>-6.153723847024281</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.000278</t>
+          <t>X ≈ 0.0002912</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.916529935748358</v>
+        <v>3.359435115189669</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.5325728095297393</v>
+        <v>1.210463677484896</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4.422422612957718</v>
+        <v>3.776754464048217</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.889796462367393</v>
+        <v>3.187323402130737</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.963842055393883</v>
+        <v>4.445804377505631</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.150808241491319</v>
+        <v>4.601995199281085</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5.247712016617356</v>
+        <v>5.721862336611835</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>5.379336637438051</v>
+        <v>6.945781519118853</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5.830659884926526</v>
+        <v>7.078167134138916</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.828236012168723</v>
+        <v>4.386449417408649</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.282623523183155</v>
+        <v>3.89405542640759</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.18420198858756</v>
+        <v>2.474825182943555</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.061039921731442</v>
+        <v>-0.1624998420275716</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.528485635448803</v>
+        <v>3.026219444364031</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.2280183178694699</v>
+        <v>-1.47160922518443</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.3663686040734788</v>
+        <v>-1.296482058700235</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>2.691467860538673</v>
+        <v>1.273412502637854</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>4.225971419012524</v>
+        <v>3.822404634157749</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>3.622190668789358</v>
+        <v>4.036183016210181</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>2.989364347609843</v>
+        <v>3.485395189184885</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>4.086162441938903</v>
+        <v>4.07242926145377</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>4.010316480529802</v>
+        <v>5.150862068290898</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>3.055282996290487</v>
+        <v>3.474545502337499</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>3.799122874214802</v>
+        <v>3.697392778285838</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.0005273</t>
+          <t>X ≈ 0.0005408</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.032911751816258</v>
+        <v>2.558502139463904</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.698134953466408</v>
+        <v>1.24601209008808</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2601159044354517</v>
+        <v>0.3599252051336208</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.384041317616827</v>
+        <v>1.906967583611674</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.048250845069632</v>
+        <v>0.5742434547537911</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.171387243932898</v>
+        <v>1.086443209061663</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.817878276354634</v>
+        <v>2.438653461543105</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.894276760679489</v>
+        <v>1.783175482281493</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.063423517062326</v>
+        <v>4.052118506737578</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.162848266557781</v>
+        <v>2.055023921393342</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.045361594826467</v>
+        <v>-0.5290306110267267</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2602812110403789</v>
+        <v>0.2637875284332267</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.028833348818488</v>
+        <v>0.2258698230924665</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.086791657889187</v>
+        <v>-3.242556654589045</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.617275381001654</v>
+        <v>-2.844989845217746</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.668278529980611</v>
+        <v>-1.574148619793959</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-3.929855241426175</v>
+        <v>-4.1976435435352</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.680086016169305</v>
+        <v>-3.259328291399228</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-3.109584706167048</v>
+        <v>-3.771372411023904</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.7950793217308885</v>
+        <v>-0.6850270542733554</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.4354241556931058</v>
+        <v>0.5474764872002567</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.778017910596063</v>
+        <v>2.632483550656659</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>2.761712481234191</v>
+        <v>2.515845551183247</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>2.685880228010873</v>
+        <v>2.7143325172472</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.0007765</t>
+          <t>X ≈ 0.0007905</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>179</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.244199068739192</v>
+        <v>-4.29386529953657</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.2143202222964646</v>
+        <v>0.9618881261250323</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.686915698405109</v>
+        <v>2.478469035518174</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.208598550470747</v>
+        <v>3.530840348551095</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>6.666104167308887</v>
+        <v>6.029828400632709</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>6.294411135529231</v>
+        <v>3.986097902084573</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>9.99173619465558</v>
+        <v>7.049538229824471</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>9.154865532025539</v>
+        <v>6.20835427908851</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>8.079034278185986</v>
+        <v>5.237586726947654</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>6.188800166395168</v>
+        <v>3.915085267089971</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.786882154925941</v>
+        <v>2.543857387608405</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.273495879969566</v>
+        <v>0.06276338092980183</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.708993030990534</v>
+        <v>-0.4961768234414095</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.163891808175237</v>
+        <v>0.3644854545781016</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>3.064407728471835</v>
+        <v>1.90375562653422</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.982816996783477</v>
+        <v>0.2451674597087532</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.407559077682976</v>
+        <v>1.241710132448851</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.6267407202305009</v>
+        <v>-1.113666260477665</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.959950536909147</v>
+        <v>0.2026838013534089</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>3.822774000508403</v>
+        <v>2.0785792617556</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>4.39754626829663</v>
+        <v>3.739635936330366</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.763041089010422</v>
+        <v>1.435179385863741</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>5.713493455123768</v>
+        <v>3.910009806137431</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>5.637661201900492</v>
+        <v>3.190302103597233</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.001026</t>
+          <t>X ≈ 0.00104</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.592066625627119</v>
+        <v>1.070104335465714</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.560961454071844</v>
+        <v>3.238093834961276</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.513186307479906</v>
+        <v>1.393621541945727</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.02903600464575362</v>
+        <v>-1.022898800937959</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.194094769875953</v>
+        <v>-1.885104642406816</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.651408001587271</v>
+        <v>1.302112652827859</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.2697032201359448</v>
+        <v>-1.307696034216924</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.211003970504855</v>
+        <v>-0.387667993937491</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.406045432946364</v>
+        <v>-1.467469874291695</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.089331573944087</v>
+        <v>0.7871105031296395</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.192659508788829</v>
+        <v>3.256171801667492</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.352934495584734</v>
+        <v>4.805275117632192</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.620016331167676</v>
+        <v>2.487989007646966</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.447717942525998</v>
+        <v>6.504954834806746</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>8.838355132750216</v>
+        <v>8.278017516738821</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>6.993717664449377</v>
+        <v>7.014624964231203</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>8.689068820154901</v>
+        <v>7.517852055129005</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>7.364715921211769</v>
+        <v>6.169137216293834</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>5.751339009453098</v>
+        <v>4.54152897848639</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.499160429177216</v>
+        <v>2.909726905774946</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>6.00539474901607</v>
+        <v>4.802337052041466</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>4.710036592485018</v>
+        <v>5.345568244020988</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.935730817162188</v>
+        <v>1.895103758379591</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.689166856621839</v>
+        <v>4.200716614943033</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.001275</t>
+          <t>X ≈ 0.00129</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.643705732096535</v>
+        <v>-0.1779405811962889</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-6.00814423698499</v>
+        <v>-7.841644668740251</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.49692614487828</v>
+        <v>0.7920898153486462</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.468060394889704</v>
+        <v>-5.55987149697016</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.261189782969574</v>
+        <v>-2.520921110216854</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.074172229229596</v>
+        <v>0.09680508088990791</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.3888333652299</v>
+        <v>-4.801565656330297</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.3979958404234836</v>
+        <v>-0.1593201820390746</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.691515542663431</v>
+        <v>1.6209436165555</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.731607996708242</v>
+        <v>2.489033509084649</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.257700159195416</v>
+        <v>6.056099552478322</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>7.79195888582872</v>
+        <v>7.929962069466299</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>6.668796818972559</v>
+        <v>7.668410230608281</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.447717942525927</v>
+        <v>6.598137488706989</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>6.602582775026697</v>
+        <v>5.93528501675268</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>12.0750184774575</v>
+        <v>11.47559286252809</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>7.87606069007353</v>
+        <v>8.053546148745291</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>8.584228116333648</v>
+        <v>7.936483477516305</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>7.987111367176674</v>
+        <v>7.31940611600281</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>11.4259896974699</v>
+        <v>10.87067345382478</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>10.07043539942257</v>
+        <v>10.31753566158308</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>13.24662195833867</v>
+        <v>12.76818343280808</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>9.456056020414181</v>
+        <v>10.51678576729056</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>8.567215637109648</v>
+        <v>7.847360457665239</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.001525</t>
+          <t>X ≈ 0.00154</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.388594861179769</v>
+        <v>-1.103312869376929</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.624272560430455</v>
+        <v>-4.078191667697588</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-6.76499431216412</v>
+        <v>-8.97630260544215</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-7.477948331606761</v>
+        <v>-5.906137758942066</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-5.11103610145144</v>
+        <v>-3.409635965149853</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-6.725871717155862</v>
+        <v>-6.920056956823956</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.894216797442603</v>
+        <v>-3.123764393420636</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.370626440393828</v>
+        <v>-3.423897284465461</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.87806794872813</v>
+        <v>4.90052261779681</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.807854975394193</v>
+        <v>5.962086183232977</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.181013716655215</v>
+        <v>5.319876324601104</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.902264313207318</v>
+        <v>5.033719265402048</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.481804949053846</v>
+        <v>5.775880245398604</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.458924270805468</v>
+        <v>3.704755567607307</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.701681874125818</v>
+        <v>3.960951516493509</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>7.196969696969688</v>
+        <v>5.431140900655521</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>6.162151659091336</v>
+        <v>4.406031136287858</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>5.156410054369246</v>
+        <v>4.288806593564146</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>6.27320233619448</v>
+        <v>5.422865493334854</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>4.658246344360641</v>
+        <v>2.847940941688535</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.5120965727910658</v>
+        <v>-1.428944228822679</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.3655511904199</v>
+        <v>-3.372738553617339</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>1.611626224764905</v>
+        <v>-0.3349134971685785</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-4.770512334764668</v>
+        <v>-4.239343382749439</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.001773</t>
+          <t>X ≈ 0.001789</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>10.21457457331501</v>
+        <v>7.824511793410885</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.855701389423004</v>
+        <v>2.858860158079111</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.827320894608917</v>
+        <v>3.982181607460291</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.31918615227454</v>
+        <v>1.027891103120488</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>11.0074920652695</v>
+        <v>7.87428418253338</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>12.39927752847525</v>
+        <v>10.38907428262764</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.217690290368104</v>
+        <v>6.061239340685894</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>10.14429812272338</v>
+        <v>8.126270825679356</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>12.59542385885496</v>
+        <v>9.408937113799915</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>10.61768890571017</v>
+        <v>7.454116428708829</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>13.30138710208896</v>
+        <v>10.09227156027997</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>13.02263769864082</v>
+        <v>9.80762598293822</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.285017800459478</v>
+        <v>7.067296834702084</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>9.268758201121315</v>
+        <v>8.027874398293314</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>9.815434180649198</v>
+        <v>8.57577412366566</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>9.205001825483748</v>
+        <v>7.938551477060955</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>6.66144613428942</v>
+        <v>5.45186643553803</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>6.556605430468238</v>
+        <v>5.345706789499346</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.362858257175681</v>
+        <v>3.147971212823201</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>2.140065512926917</v>
+        <v>0.9348584044905479</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>2.802338622069257</v>
+        <v>1.58424663239348</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.521673383551786</v>
+        <v>0.2951646747670225</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>6.61542520446757</v>
+        <v>5.406709349859092</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>8.949231505461093</v>
+        <v>6.474128237948086</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.002023</t>
+          <t>X ≈ 0.002039</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.241505827744547</v>
+        <v>3.787070824061836</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.4361407941005666</v>
+        <v>-0.7504197486122521</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.943054725518657</v>
+        <v>-3.442551342946587</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-9.067773450843752</v>
+        <v>-8.34726601908271</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-12.34474039397926</v>
+        <v>-11.50806351424622</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-12.15777420788188</v>
+        <v>-12.81447832613787</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-7.047369950595758</v>
+        <v>-7.802806332616377</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-4.384404924760595</v>
+        <v>-5.227669606050206</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-7.28409421343413</v>
+        <v>-8.026437532145643</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.17465694829415</v>
+        <v>-3.01573502161073</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.040579164456055</v>
+        <v>0.1313749778789699</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.703006231596248</v>
+        <v>2.729668008292876</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.40337357650484</v>
+        <v>10.30158706657109</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.770529994175888</v>
+        <v>6.595757387232332</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>9.053563167183562</v>
+        <v>8.856362383312764</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>8.177361853832451</v>
+        <v>7.964941665976568</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>5.102268246266732</v>
+        <v>3.516267882999557</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>7.938604013033796</v>
+        <v>6.341406247201519</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>6.683907158663992</v>
+        <v>5.09104354818858</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>3.929576498043829</v>
+        <v>2.351725959455422</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1.91644209478364</v>
+        <v>0.3204132256209817</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.84059613337454</v>
+        <v>0.2409825124675322</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>3.585659081150709</v>
+        <v>1.97329392496777</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>9.392179769103898</v>
+        <v>7.784648805840327</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.002273</t>
+          <t>X ≈ 0.002289</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6105440831289854</v>
+        <v>1.861998375511156</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.630436694278785</v>
+        <v>12.06802533622268</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.677266130096278</v>
+        <v>4.951055271720698</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.96431211065358</v>
+        <v>4.444409011511247</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>8.689127698712369</v>
+        <v>10.08829745975484</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.815487824203686</v>
+        <v>4.311491820976855</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.558690655464851</v>
+        <v>5.032003096912725</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.825933756166322</v>
+        <v>7.629635321943042</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.837117907777944</v>
+        <v>6.199092974159214</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.549050716590031</v>
+        <v>3.973204129370103</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.307958843600396</v>
+        <v>2.715553199372756</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.516245105302104</v>
+        <v>-2.03634533743859</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.639407172158272</v>
+        <v>-4.623952773758489</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3150315031503084</v>
+        <v>-0.411162909284684</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-2.488326315882347</v>
+        <v>0.4046615505130902</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>1.13636363636364</v>
+        <v>-0.5448775592312529</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-5.058159561219902</v>
+        <v>-5.088091806841788</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-6.678151780192593</v>
+        <v>-5.223092403066119</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-4.947108884116759</v>
+        <v>-3.543161306034257</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-1.729960043845736</v>
+        <v>-0.3466552145912942</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-3.787657726963246</v>
+        <v>-2.418501379664463</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-6.893806718675371</v>
+        <v>-5.562237778987011</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-5.104180491041809</v>
+        <v>-5.34388703084354</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-3.664861229113569</v>
+        <v>-3.994914914021855</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.002521</t>
+          <t>X ≈ 0.002538</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.359152886568033</v>
+        <v>3.539816291832452</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.802153865996061</v>
+        <v>-1.153205928486877</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>17.91969037252063</v>
+        <v>15.78120253372422</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>14.9845141308556</v>
+        <v>15.32234734346295</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>19.09316810275277</v>
+        <v>17.25921797829241</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>12.61346762218348</v>
+        <v>12.9245205301595</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.174852271626463</v>
+        <v>5.403120854108941</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.4521963824289372</v>
+        <v>4.986911236911283</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-6.172983102322959</v>
+        <v>-4.024226804971619</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.723676556137356</v>
+        <v>-2.474302516715206</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-6.671839136197647</v>
+        <v>-6.782729895273256</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-9.172810761867865</v>
+        <v>-7.081569684502277</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-12.51819505094615</v>
+        <v>-12.68809285608418</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-10.51705170517052</v>
+        <v>-10.67938247307293</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-8.95297278052891</v>
+        <v>-13.67472660726699</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-15.02525252525253</v>
+        <v>-13.20913002384673</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-17.38139188445222</v>
+        <v>-15.56800645342314</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-13.04178814382899</v>
+        <v>-13.45499133612051</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-12.8258967629046</v>
+        <v>-13.35817315069647</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-17.08349539738109</v>
+        <v>-17.93933934731263</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-15.40381934312486</v>
+        <v>-16.23072575129994</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-17.70188752675618</v>
+        <v>-18.75626754927741</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-15.20519059205191</v>
+        <v>-13.88891528734716</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-17.50324506749744</v>
+        <v>-16.52238744149449</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.00277</t>
+          <t>X ≈ 0.002788</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.423669015600339</v>
+        <v>5.926459293394736</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.088892217250482</v>
+        <v>11.09318686629312</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5749332833934204</v>
+        <v>1.712148678379883</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8.389532052002551</v>
+        <v>9.240714221507233</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>11.27954803106817</v>
+        <v>11.67886575882721</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.014901313939752</v>
+        <v>6.412412268051078</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.017146178436505</v>
+        <v>2.900932406356155</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-8.938484621155283</v>
+        <v>-10.94565470371924</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-15.34861034246639</v>
+        <v>-16.23573654672325</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-22.57313892172873</v>
+        <v>-25.16485255807165</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-22.29907927956676</v>
+        <v>-22.18159603809104</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-19.35202223140185</v>
+        <v>-22.45683390654084</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-26.92679720148378</v>
+        <v>-23.57575828205616</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-23.92206962631752</v>
+        <v>-21.11297083811284</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-31.03182582712388</v>
+        <v>-25.52843321977266</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-30.43743890518084</v>
+        <v>-25.16381296945517</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-20.89393668731965</v>
+        <v>-17.16624844382197</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-14.54716448791498</v>
+        <v>-11.92383921901011</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-14.33127310699074</v>
+        <v>-11.83464844540368</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-20.59604020024839</v>
+        <v>-17.32594564801062</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-14.68697346498866</v>
+        <v>-12.4321175756702</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-11.5370129747849</v>
+        <v>-12.65139006694697</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-17.71415116552865</v>
+        <v>-15.37664188982797</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-21.01578987036474</v>
+        <v>-19.37953029863728</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.00302</t>
+          <t>X ≈ 0.003038</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-7.694901167486059</v>
+        <v>-9.566678577589443</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>8.18653825038038</v>
+        <v>7.518053587174919</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.045816498646687</v>
+        <v>9.137259778538528</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>19.54907869542016</v>
+        <v>20.06953783306328</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.402477412062083</v>
+        <v>8.298378519943441</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.184038192754052</v>
+        <v>2.503957977243928</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>13.22290031967447</v>
+        <v>13.14631897740675</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2.133878064110625</v>
+        <v>4.132460413295277</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.5273374566773725</v>
+        <v>1.328330869099382</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.30025313271382</v>
+        <v>3.260784265572759</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.728896193254641</v>
+        <v>0.6881980672345094</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-6.710348299405346</v>
+        <v>-2.46228418049197</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.428104960856011</v>
+        <v>2.141545208255025</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-13.45999464811342</v>
+        <v>-9.66044818682348</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-3.30732713488316</v>
+        <v>1.182077684624396</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-5.415642915642877</v>
+        <v>0.8580379631752706</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.1441546472149824</v>
+        <v>3.535849207428214</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>2.45370735166658</v>
+        <v>3.335855671143953</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-2.735806672814498</v>
+        <v>-2.414640703055447</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-2.548960862846471</v>
+        <v>-5.271646697778984</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-3.091507030812501</v>
+        <v>-3.010024341496397</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-3.167352992221602</v>
+        <v>-1.004842333442767</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-2.892878279739548</v>
+        <v>-1.641633728590243</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-5.671413235665568</v>
+        <v>-1.803772722879707</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.003269</t>
+          <t>X ≈ 0.003288</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-24.22908240754961</v>
+        <v>-18.77478019555811</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-18.68150626472296</v>
+        <v>-13.94471724940989</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-14.23717237257748</v>
+        <v>-10.14890630079643</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3.185420509667274</v>
+        <v>4.418694895692816</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-15.2859168645675</v>
+        <v>-11.00837839592168</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.548108145059302</v>
+        <v>4.240652655115028</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.77615946116903</v>
+        <v>3.428594155317562</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.38030095759234</v>
+        <v>3.0982089805619</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>7.421788139507044</v>
+        <v>3.209161402681303</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.53122540464703</v>
+        <v>7.42117373905532</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.80528504680895</v>
+        <v>7.70189699744185</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.52653564336096</v>
+        <v>12.4758200934756</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>17.28572651768122</v>
+        <v>16.4029447827476</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>17.06464764123471</v>
+        <v>16.13773423374976</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>16.40650434365407</v>
+        <v>10.41356304514206</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>11.11853832442051</v>
+        <v>10.98335530774406</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>28.63168001097262</v>
+        <v>29.72294448724528</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>28.52683930715143</v>
+        <v>29.7373572606155</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>22.86037774689928</v>
+        <v>24.95206410966034</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>23.04722355686724</v>
+        <v>25.27578413226044</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>28.38703033007767</v>
+        <v>30.08782094285533</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>28.31118436866866</v>
+        <v>24.74950052616327</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>22.70330613997423</v>
+        <v>24.99313501144164</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>16.74512094557441</v>
+        <v>19.56783812241543</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.003518</t>
+          <t>X ≈ 0.003537</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>14.21629574371089</v>
+        <v>19.29581055477113</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>6.738661802503927</v>
+        <v>8.431550878492217</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>12.44349989633009</v>
+        <v>10.81856486275316</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.587688734030195</v>
+        <v>-0.3921901766301801</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.251898261482921</v>
+        <v>2.79866181634732</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>11.58172159043745</v>
+        <v>6.378181067153299</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>14.38120147797567</v>
+        <v>12.69121727414991</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>10.53156146179406</v>
+        <v>8.65693976805089</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.14447721513733</v>
+        <v>12.29510329908071</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.37156153910081</v>
+        <v>14.92163744866922</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>13.64562118126273</v>
+        <v>15.23769695154252</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>16.93830034924331</v>
+        <v>15.00493948534016</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>12.24370971095865</v>
+        <v>6.694280172122198</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.59405940594057</v>
+        <v>9.956280732034777</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>7.793058965502944</v>
+        <v>5.676242752266113</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>11.95887445887449</v>
+        <v>6.281371259354785</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>15.39638589332563</v>
+        <v>9.775374445513357</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>15.29154518950438</v>
+        <v>12.18866256906362</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>15.5074365704287</v>
+        <v>12.40204854852159</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>15.69428238039673</v>
+        <v>12.63219851766051</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>15.1517362124307</v>
+        <v>14.68821080640319</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>11.50446167959303</v>
+        <v>14.61304828444788</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>15.35036496350365</v>
+        <v>14.85668276972626</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>15.27453271028045</v>
+        <v>14.69454377543673</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2461 +3180,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.003585</t>
+          <t>X &gt; -0.003579</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3355</v>
+        <v>3379</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.148377279700064</v>
+        <v>0.1316825017541845</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1256494077325812</v>
+        <v>0.1073794029600066</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.03659400601186746</v>
+        <v>0.01559586370571253</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.08081042715189568</v>
+        <v>0.05722097396763814</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1790442399989942</v>
+        <v>-0.2019472747725288</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.0346860161865834</v>
+        <v>-0.05805186696995435</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.04855619021616064</v>
+        <v>-0.07112675242656508</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.04287596669264815</v>
+        <v>-0.06486068341739326</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01406453984362344</v>
+        <v>-0.03805452088388961</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.03144365757598422</v>
+        <v>0.007829814555094572</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.02583835126612399</v>
+        <v>0.002214065378282726</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.02784161689866238</v>
+        <v>-0.05105548611732047</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.05459163948760448</v>
+        <v>0.03094787457158787</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.08944728053785411</v>
+        <v>-0.1114518503694271</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.07265808220071079</v>
+        <v>0.05018904540435898</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.03074906063309868</v>
+        <v>0.009078595958840197</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.06325085465810076</v>
+        <v>0.04076220712738632</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.005915912503489551</v>
+        <v>-0.01556197320689989</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.1175634295712982</v>
+        <v>-0.1382061569756345</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1512073486893115</v>
+        <v>-0.1722467296363277</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1401041687485787</v>
+        <v>-0.1605528004917289</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1683754624130174</v>
+        <v>-0.1886211756066771</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.1740688863175635</v>
+        <v>-0.1937226652945725</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.172561179436471</v>
+        <v>-0.1904210947308087</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.003336</t>
+          <t>X &gt; -0.003329</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3340</v>
+        <v>3365</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1801460474363026</v>
+        <v>0.1763815363522099</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.06958727203737425</v>
+        <v>0.06443366382060844</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.01346444251464618</v>
+        <v>-0.02255430480823861</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.004355400696866241</v>
+        <v>-0.007860292874688923</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2254121625378289</v>
+        <v>-0.237429139365382</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.08125807432899279</v>
+        <v>-0.09359817632761747</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.06196631639856065</v>
+        <v>-0.073878102155156</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.05502120464561244</v>
+        <v>-0.06632428992678285</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.05607632967853959</v>
+        <v>-0.06952321084494884</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.03673559012655403</v>
+        <v>-0.04975440279889654</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.07343637913094625</v>
+        <v>-0.08614205692251176</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.09630585600729802</v>
+        <v>-0.1088999064579923</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.03833829176977588</v>
+        <v>-0.05157110374489804</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1820599970444832</v>
+        <v>-0.1935562622466449</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.01630843628014844</v>
+        <v>-0.02843847569769764</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.06109481915932946</v>
+        <v>-0.0720726221716248</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.002002863746831451</v>
+        <v>-0.01019424673784641</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.05513741659245142</v>
+        <v>-0.06621558444569331</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.1801568525907271</v>
+        <v>-0.1902752410227535</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1849042224740813</v>
+        <v>-0.1956820491634375</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.2012401561005603</v>
+        <v>-0.2112789446305356</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1694718076259178</v>
+        <v>-0.1797665083669173</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.1764234232069128</v>
+        <v>-0.1858999199152578</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.1745690861268088</v>
+        <v>-0.1819077131989459</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.003087</t>
+          <t>X &gt; -0.00308</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3327</v>
+        <v>3352</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.2397499014934041</v>
+        <v>0.2351510496671807</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1300792832017947</v>
+        <v>0.1237367384973282</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1120440164871113</v>
+        <v>0.07091404790201494</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.07298473471311695</v>
+        <v>0.08797630393175382</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1264639620675823</v>
+        <v>-0.1413867586925122</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.01234204398492977</v>
+        <v>-0.02725143125647378</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.01004631734682704</v>
+        <v>-0.004367577366494402</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.01812186519558878</v>
+        <v>0.004412979472355971</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.0169231414431863</v>
+        <v>0.0007287824839750101</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.03936844037075105</v>
+        <v>0.02366928272722646</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.02845922934462664</v>
+        <v>-0.04360653514318358</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.08026808441946542</v>
+        <v>-0.09509736657938817</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.07761186740309967</v>
+        <v>-0.1224391929171418</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.191076944074382</v>
+        <v>-0.2045461932841661</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.02211746478144505</v>
+        <v>-0.03615451555444338</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.06939711962200334</v>
+        <v>-0.08213149303689704</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.03552772395099169</v>
+        <v>-0.07915612285403029</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.03248721373595487</v>
+        <v>-0.07534117286063235</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.1588299361739445</v>
+        <v>-0.2007144755731716</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1643186403177737</v>
+        <v>-0.2069765732031783</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1785941178996353</v>
+        <v>-0.2204385284756896</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1764377754127722</v>
+        <v>-0.1885153543250695</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.1544427288040353</v>
+        <v>-0.1956197564802338</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.1823353390132851</v>
+        <v>-0.22081908145352</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.002838</t>
+          <t>X &gt; -0.00283</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3298</v>
+        <v>3320</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.09634396553126123</v>
+        <v>0.09183333769855295</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.07924494561947881</v>
+        <v>0.07143052954280193</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.07489744931991993</v>
+        <v>0.06003483055255998</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1328298674066275</v>
+        <v>0.1128731294977001</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.02196513002752454</v>
+        <v>-0.02619249697659143</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.0461603315621204</v>
+        <v>-0.09218130095225519</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.01358357988100778</v>
+        <v>-0.001538988013365383</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.02425259197384122</v>
+        <v>0.01025153902851628</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.007524165124948468</v>
+        <v>0.005306238335791136</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.05232263846655627</v>
+        <v>0.0661028637471972</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.04881127449903033</v>
+        <v>-0.03442285303053438</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.09856879551342246</v>
+        <v>-0.0837491887826971</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.1461676426430429</v>
+        <v>-0.1306608267405664</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1981994389339121</v>
+        <v>-0.1811438498342213</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.05198467808884288</v>
+        <v>-0.03460832222432941</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.1050978774125468</v>
+        <v>-0.08642407545448094</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.0697158015897017</v>
+        <v>-0.05236511872558225</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.005154780220117061</v>
+        <v>0.0129053817095155</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.104313883841435</v>
+        <v>-0.08563679029654025</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.1115340388701682</v>
+        <v>-0.09399036677153561</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.1209910602965749</v>
+        <v>-0.1020835505478246</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.1665339914026518</v>
+        <v>-0.1292979148519677</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.2073798076391142</v>
+        <v>-0.1689119306651961</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.2651883327760203</v>
+        <v>-0.2229037926131809</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.002588</t>
+          <t>X &gt; -0.00258</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3261</v>
+        <v>3277</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.01992164800793716</v>
+        <v>0.002827817343941774</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1427409448381098</v>
+        <v>0.1065861694380388</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.07751018134707977</v>
+        <v>0.02044728881184454</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1272163205376486</v>
+        <v>0.1120195137083613</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.06598350509838014</v>
+        <v>0.06575374295920966</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.008898440433085852</v>
+        <v>-0.003116310603381578</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.07804964049365282</v>
+        <v>0.09911531957070707</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.03095096118352103</v>
+        <v>0.05433713298881315</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.001651465342533243</v>
+        <v>0.04766962529358665</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.03706463710238239</v>
+        <v>0.08928874616962901</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.03776234630043973</v>
+        <v>0.01429326478184834</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2377387705610943</v>
+        <v>-0.1536646587712482</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1509271410307278</v>
+        <v>-0.06497616134339523</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2010476276985429</v>
+        <v>-0.1128522543141557</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.045729654870307</v>
+        <v>0.04454814173877963</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.0755721226957391</v>
+        <v>0.04561366895483587</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.05356373232157807</v>
+        <v>0.1728709906617922</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.05884463837149667</v>
+        <v>0.1798855922696063</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.04386511410422145</v>
+        <v>0.07729338706644029</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.05326663921111674</v>
+        <v>0.0660676707716874</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.02601432388556901</v>
+        <v>0.09584404940225966</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1018602852946699</v>
+        <v>0.03882172485992896</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.1769189114197047</v>
+        <v>-0.06546940074806429</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2345135945340999</v>
+        <v>-0.1180106160007313</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.002339</t>
+          <t>X &gt; -0.002331</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3209</v>
+        <v>3226</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1358843342756373</v>
+        <v>-0.1846476769707266</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.0984526959008889</v>
+        <v>-0.1224830400929733</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.04541411114752236</v>
+        <v>0.03995163189099316</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.04719251375427547</v>
+        <v>-0.05953621078660376</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1658613982122219</v>
+        <v>-0.1330678197137587</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1339820607500712</v>
+        <v>-0.1130706748177417</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.07332505405829437</v>
+        <v>0.126580949620454</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.2473546692073469</v>
+        <v>0.3326647990435632</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1204385403690296</v>
+        <v>0.2314011513852918</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1417478745045315</v>
+        <v>0.2553983379856817</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1232317968043759</v>
+        <v>0.2367342410672606</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.230748749575838</v>
+        <v>-0.1147436742853642</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2790488484800804</v>
+        <v>-0.1615443543850787</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2641495492832888</v>
+        <v>-0.144487910829703</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.09518809070682721</v>
+        <v>-0.004773555574821842</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.04219230261544737</v>
+        <v>0.04928470980787125</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.001995681526601345</v>
+        <v>0.08739625219094194</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.005119286640123732</v>
+        <v>0.09659196744566145</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.07182222745357336</v>
+        <v>0.01991957973718428</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.08453381898021206</v>
+        <v>0.005110645474530884</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.1597902673200835</v>
+        <v>-0.04860715122620007</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.1733309327790238</v>
+        <v>-0.07440868925444732</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.2726879959979058</v>
+        <v>-0.2152221069508613</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.205367570180826</v>
+        <v>-0.173082685494073</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.00209</t>
+          <t>X &gt; -0.002081</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3148</v>
+        <v>3162</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.2105594118828051</v>
+        <v>-0.2742420643770913</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.229180661702749</v>
+        <v>-0.268734695178388</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.008424696474612858</v>
+        <v>-0.01494356765451244</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1354493356143536</v>
+        <v>-0.1673709078832246</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2815464790436906</v>
+        <v>-0.2683084070027917</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.09458029294631132</v>
+        <v>-0.09387704012495846</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1316306819153112</v>
+        <v>0.1666120006019014</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.3460415087954232</v>
+        <v>0.4144656127034949</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.18426021694561</v>
+        <v>0.2771344413258987</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.189270579032069</v>
+        <v>0.2861847919459422</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2284493727039703</v>
+        <v>0.4191469133949184</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2536540378330301</v>
+        <v>-0.1228196373780222</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2495005008827675</v>
+        <v>-0.08504742872028714</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2617250631560708</v>
+        <v>-0.09414007430586224</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.2035892816209355</v>
+        <v>-0.03242952005586375</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.1293861546002404</v>
+        <v>0.04292483864404062</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.08584760921250734</v>
+        <v>0.08390199326811398</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.07659190982916897</v>
+        <v>0.0959669049394023</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1592300962379625</v>
+        <v>0.01341095537013359</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.1758351172215669</v>
+        <v>-0.006037212278805271</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.3055518155146828</v>
+        <v>-0.08096595329492118</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.3496416638720206</v>
+        <v>-0.1373848288170976</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.4244841949593479</v>
+        <v>-0.2859970583788041</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.3862042655773195</v>
+        <v>-0.3346220127422797</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.001841</t>
+          <t>X &gt; -0.001831</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3077</v>
+        <v>3093</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.257875277886491</v>
+        <v>-0.2649917666710095</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1070580328565569</v>
+        <v>-0.1252944892643413</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.02354907929771599</v>
+        <v>-0.03037419526903307</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2509090553607223</v>
+        <v>-0.2371722809667176</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.262970165654842</v>
+        <v>-0.1592599840480489</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.02111482911848128</v>
+        <v>0.04773852970334502</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2203542319875993</v>
+        <v>0.331692528058511</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.4140559103506547</v>
+        <v>0.5275379350644656</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.1827020288723205</v>
+        <v>0.3200041017592952</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2385183023634667</v>
+        <v>0.3791332734361106</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2073252794335971</v>
+        <v>0.3480526128032295</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.2471730619110346</v>
+        <v>-0.1032159126703291</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.2487605174830705</v>
+        <v>-0.1042473630892005</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2884843967849022</v>
+        <v>-0.1080285172925244</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.2783000552232124</v>
+        <v>-0.09425065416106548</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.08658008658008498</v>
+        <v>0.06701394391892279</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.03882034246528576</v>
+        <v>0.1434811827956892</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.0593320034780831</v>
+        <v>0.1265241717019023</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.1490470174815925</v>
+        <v>0.03736276799234872</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2546938951963824</v>
+        <v>-0.0841598060060349</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.3097522503577324</v>
+        <v>-0.1481371694797033</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.2881006492059015</v>
+        <v>-0.1395395214517237</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.4036161869675894</v>
+        <v>-0.2969000309153671</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.3169525025893094</v>
+        <v>-0.2460029788829985</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.001591</t>
+          <t>X &gt; -0.001582</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2961</v>
+        <v>2969</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4286035883731003</v>
+        <v>-0.4301769289138022</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.01024894391952813</v>
+        <v>-0.006739721779659646</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1194885561734367</v>
+        <v>0.1441886662885921</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1128917516651029</v>
+        <v>0.1541961060345969</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.214370031220092</v>
+        <v>0.3137115937799706</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.300428043755403</v>
+        <v>0.3220763680399799</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4030168640695635</v>
+        <v>0.5169730332240974</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.480609721744031</v>
+        <v>0.5996794941518502</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2386254095884226</v>
+        <v>0.3782296961779252</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.32682849436776</v>
+        <v>0.5064505970835427</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4858271188078476</v>
+        <v>0.6640071509356531</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1930173303753762</v>
+        <v>0.3733071661309566</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.06690774649234044</v>
+        <v>0.2174419055747379</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.03304780916391792</v>
+        <v>0.1568073944614312</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.07082335962479647</v>
+        <v>0.199651891002496</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.3143786038522904</v>
+        <v>0.4115342298864704</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.1331391839094209</v>
+        <v>0.2604166666666643</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.1497491057771683</v>
+        <v>0.2819443262109473</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.01941246705862909</v>
+        <v>0.112926194165297</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.2378351474654821</v>
+        <v>-0.02258963746407261</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.3075680766608286</v>
+        <v>-0.09918762837077821</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.2483245412783006</v>
+        <v>-0.01976022247709608</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3115735707753089</v>
+        <v>-0.09281217976869982</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.08345445621742442</v>
+        <v>0.1354579128817406</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.001342</t>
+          <t>X &gt; -0.001332</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2822</v>
+        <v>2830</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.0227743989949758</v>
+        <v>-0.1203733058571785</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3131159399654848</v>
+        <v>0.1602203849394783</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7812034917110537</v>
+        <v>0.6605280380496623</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4565304465005724</v>
+        <v>0.3489261200417104</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6502140297245731</v>
+        <v>0.6349685415429391</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.7312854046676875</v>
+        <v>0.6361950395867311</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.80649521001137</v>
+        <v>0.8795360865174047</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.7252660622782869</v>
+        <v>0.8056166524191823</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.6106426286711368</v>
+        <v>0.6726175738806717</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.6355696158297377</v>
+        <v>0.7054686614737307</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8596796572512204</v>
+        <v>0.9278365807918405</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7784700805021458</v>
+        <v>0.8476578567941502</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.4543317737207531</v>
+        <v>0.5276880850795465</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.4666708709087501</v>
+        <v>0.5467671597669224</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.3960930995104803</v>
+        <v>0.4843509320623269</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.6931925487166311</v>
+        <v>0.7144556407595388</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.4388938635699731</v>
+        <v>0.4906334449535805</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.4616373227432149</v>
+        <v>0.5198104176404641</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.2877342316618723</v>
+        <v>0.3673475223369067</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.0139138474413798</v>
+        <v>0.1088924545990224</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.06796612633613108</v>
+        <v>0.02112578986527325</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.002068643379537605</v>
+        <v>0.1081832499218223</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.1882601250860034</v>
+        <v>-0.08634220508960766</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.01939451042212426</v>
+        <v>0.1257700547196094</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.001093</t>
+          <t>X &gt; -0.001082</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1823531849641569</v>
+        <v>0.1748453908485104</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.6681657189530128</v>
+        <v>0.5609088153676893</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9832238799182988</v>
+        <v>0.9047277246285219</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.6805645266448934</v>
+        <v>0.6840727377162068</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.8296677504795653</v>
+        <v>0.8917859730815607</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.8674358761517311</v>
+        <v>0.9743701367004647</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.139873615237889</v>
+        <v>1.316041052892921</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.122758776228942</v>
+        <v>1.29306457431457</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9031493523995167</v>
+        <v>1.107687686242286</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8762239784890937</v>
+        <v>1.07776948053553</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.9637860451195053</v>
+        <v>1.260097660473321</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.11740482685525</v>
+        <v>1.377893590534683</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.837534698960539</v>
+        <v>1.067662158872288</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.8255754626993692</v>
+        <v>1.028119104395174</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.675550026925599</v>
+        <v>0.8532075317838732</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.881573583367306</v>
+        <v>1.026610511227496</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.8076008465965856</v>
+        <v>0.9451404441955944</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.6879550623540425</v>
+        <v>0.7973421208777296</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.4924777073022995</v>
+        <v>0.6606817516691379</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.155763307846243</v>
+        <v>0.2996679302718519</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.01281128195972769</v>
+        <v>0.1655386014879667</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.1357257035271999</v>
+        <v>0.3370295581673659</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.11102315348122</v>
+        <v>0.3037459945672509</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.2969710049699827</v>
+        <v>0.5007092223207934</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.0008436</t>
+          <t>X &gt; -0.0008325</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2481</v>
+        <v>2478</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3816790329879822</v>
+        <v>0.5038476308637669</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4893801107443636</v>
+        <v>0.5784536156727142</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.8212725661381484</v>
+        <v>0.9663877189093384</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.2289943310880105</v>
+        <v>0.333921417537006</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.7379343492889276</v>
+        <v>0.8997094312838243</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.5628731822085129</v>
+        <v>0.7361302167690909</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.7563307734589486</v>
+        <v>1.045853969913274</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.00104772774047</v>
+        <v>1.205085567555493</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.9218591252625714</v>
+        <v>1.15574185085444</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.033899201438473</v>
+        <v>1.265742550577087</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.9861567518868029</v>
+        <v>1.320710653094061</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.230335747473397</v>
+        <v>1.469257556083917</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.8151382823871884</v>
+        <v>1.061073347004275</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9000175379856898</v>
+        <v>1.07799310062105</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.6689004015537563</v>
+        <v>0.8220421146584656</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.7639855444045622</v>
+        <v>0.9651619215131575</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.5334274088435009</v>
+        <v>0.7646923205901999</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.4285867050223189</v>
+        <v>0.6156565550638362</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.3220274611985516</v>
+        <v>0.5320370762062154</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.06550366213796366</v>
+        <v>0.2468511773036965</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.1275524155745913</v>
+        <v>0.3078086388184076</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.3338507508200692</v>
+        <v>0.4986516297286414</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.4471001509280725</v>
+        <v>0.6857954645105835</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.5324932100788473</v>
+        <v>0.7496061016855506</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.0005944</t>
+          <t>X &gt; -0.0005828</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2271</v>
+        <v>2261</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4928380228916964</v>
+        <v>0.6276981182458599</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5538395886579721</v>
+        <v>0.6012820639291618</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.9188108650447475</v>
+        <v>1.014717900580166</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.5136844621367445</v>
+        <v>0.422315701771943</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.9254753440309926</v>
+        <v>0.8052299058341532</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.7166631660122746</v>
+        <v>0.6987745741676221</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.000123453098169</v>
+        <v>1.088942781425679</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.24961649383323</v>
+        <v>1.336344814605681</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.159177554375894</v>
+        <v>1.182283654724259</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.177818606571591</v>
+        <v>1.290807373394721</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.056099884617417</v>
+        <v>1.105176595040909</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.305054966657558</v>
+        <v>1.250220386728984</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.9294742542429475</v>
+        <v>0.9534519254253908</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.778837232601397</v>
+        <v>0.6433927078595332</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.5433104745572237</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.6800168127777084</v>
+        <v>0.5750176601457468</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.6341666066676979</v>
+        <v>0.6737764550264558</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.6173928337139714</v>
+        <v>0.6554880092333448</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.3489160948672705</v>
+        <v>0.3668182661442216</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.3596280431003791</v>
+        <v>0.3868792469548552</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.3895169257728384</v>
+        <v>0.419790442576442</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.621905222399846</v>
+        <v>0.6361902952169345</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.8083130040144368</v>
+        <v>0.8179756275708314</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.9526480779598145</v>
+        <v>0.9477585116236611</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.0003451</t>
+          <t>X &gt; -0.0003331</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2066</v>
+        <v>2056</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.372692538405559</v>
+        <v>0.4371127798488814</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2796952371543853</v>
+        <v>0.1912059441450111</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.8726239637520266</v>
+        <v>0.7213647124898088</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.449805340827659</v>
+        <v>0.3219195807341606</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9844210578355188</v>
+        <v>1.107625309424023</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8812518474145179</v>
+        <v>0.8304055145537959</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.414912447856857</v>
+        <v>1.289544438162856</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.716971796140534</v>
+        <v>1.63995163995164</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.613391279796041</v>
+        <v>1.651267419985437</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.565814095055487</v>
+        <v>1.608055342816606</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.211247044760931</v>
+        <v>1.232214202168457</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.512768434349688</v>
+        <v>1.370759113571118</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.114944858789514</v>
+        <v>1.01005058852153</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.9714178965066367</v>
+        <v>0.8874949729188302</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.8265259825129974</v>
+        <v>0.7669761104194706</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.8884830883862875</v>
+        <v>0.8730180086242285</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.5125523986498592</v>
+        <v>0.7012188964291468</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.5045171159322592</v>
+        <v>0.694336635219905</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.429992233545839</v>
+        <v>0.5012014844295862</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.5684353329620677</v>
+        <v>0.7932317191467178</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.5099162705139548</v>
+        <v>0.7404116230527364</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.676083861863809</v>
+        <v>0.9374193026964406</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.6601423110351092</v>
+        <v>0.8701147724630687</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.777920900019005</v>
+        <v>0.9803918803510356</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -9.584e-05</t>
+          <t>X &gt; -8.338e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1800</v>
+        <v>1790</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6924862199013688</v>
+        <v>0.7209391633622673</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.8021538659959973</v>
+        <v>0.8626292268832003</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.308579261409449</v>
+        <v>1.324435678701477</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.095625241966708</v>
+        <v>1.008888407910973</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.982056991641656</v>
+        <v>1.951491951089608</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.557912066627928</v>
+        <v>1.720828657862882</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.341518938293135</v>
+        <v>2.47613424252939</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.729974160206716</v>
+        <v>2.780294640759749</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.882572453232541</v>
+        <v>2.94126208312808</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.442990110529379</v>
+        <v>2.455447611205692</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.994827530469074</v>
+        <v>1.984464559837207</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.604967015909978</v>
+        <v>1.518778614791565</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.48180494905386</v>
+        <v>1.269541969297727</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.482948294829491</v>
+        <v>1.276814108123737</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.324804997248933</v>
+        <v>1.017209290811586</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.696969696969703</v>
+        <v>1.389742017212583</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.229719226658887</v>
+        <v>1.152528519755151</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.180434078393269</v>
+        <v>1.164559287562973</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.174103237095373</v>
+        <v>1.078415401464206</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.249837935952279</v>
+        <v>1.326508769941704</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.37395843465292</v>
+        <v>1.461877948168464</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.409223584354926</v>
+        <v>1.64388492465951</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.461476074614765</v>
+        <v>1.642463525356256</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.552310488058154</v>
+        <v>1.681922215329202</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0001534</t>
+          <t>X &gt; 0.0001663</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.43349031384664</v>
+        <v>1.563346296937574</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.098713515496826</v>
+        <v>1.124761233873393</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.729214182044366</v>
+        <v>1.539945102437812</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.533390091496258</v>
+        <v>1.20444720677667</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.361141958961923</v>
+        <v>2.08495843083918</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.483466903947473</v>
+        <v>2.177665961050501</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.939701801181876</v>
+        <v>2.602879388766397</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.37254400865892</v>
+        <v>3.004445779012251</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.801878637244606</v>
+        <v>3.517731143416967</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.41681040787909</v>
+        <v>3.081733670747759</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.303022603370039</v>
+        <v>2.942781619828324</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.088914441033872</v>
+        <v>2.64058378765111</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.482882303072387</v>
+        <v>1.886391805530231</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.778933355520429</v>
+        <v>2.128188678570474</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>2.637919986834504</v>
+        <v>1.872222588907924</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>2.973741944330179</v>
+        <v>2.215103530004583</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>2.645901084017218</v>
+        <v>1.892518022380031</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>2.864266585755182</v>
+        <v>2.315840055045115</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>2.627669278896704</v>
+        <v>2.052967639329573</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>2.685232606641073</v>
+        <v>2.242383303567522</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.983022573128821</v>
+        <v>2.685334143332319</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>2.971817852831549</v>
+        <v>2.909440531617328</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>3.246292565313603</v>
+        <v>2.999070134407845</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>3.235101553202156</v>
+        <v>2.942129882945075</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0004027</t>
+          <t>X &gt; 0.000416</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1303</v>
+        <v>1282</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.155776063851221</v>
+        <v>1.199084914140748</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.20472911968406</v>
+        <v>1.107380083062949</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.224883516547166</v>
+        <v>1.086302018179843</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.279389205469734</v>
+        <v>0.8023038286237352</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.248280237143497</v>
+        <v>1.606159720906824</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.358500452404343</v>
+        <v>1.685992324591879</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.507503418552361</v>
+        <v>1.970324344741577</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.9967516821646</v>
+        <v>2.205110917524173</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.421968718261951</v>
+        <v>2.795645841086461</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.339766779754243</v>
+        <v>2.817126733047417</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.306842538570038</v>
+        <v>2.749855574812244</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.258331047631643</v>
+        <v>2.674200977373403</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.749136747467773</v>
+        <v>2.301923652928842</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.451311900184649</v>
+        <v>1.946060754150565</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>3.174596077661654</v>
+        <v>2.550378807054578</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>3.461999116258525</v>
+        <v>2.927281574515703</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.63736824175227</v>
+        <v>2.018077644168606</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>2.609273508767622</v>
+        <v>2.010296536660341</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.441435035509286</v>
+        <v>1.650755472411518</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>2.628280845477313</v>
+        <v>1.990290409448548</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>2.776448415040065</v>
+        <v>2.404020000811578</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>2.77734842446749</v>
+        <v>2.454862060841087</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>3.282061049459145</v>
+        <v>2.902639872581247</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>3.129482825399336</v>
+        <v>2.788956440832287</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.0006519</t>
+          <t>X &gt; 0.0006657</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.9135113586542261</v>
+        <v>0.8243997684546613</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.068450525044859</v>
+        <v>1.069170067196325</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.49135214202758</v>
+        <v>1.286507368641345</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.9742845084810199</v>
+        <v>0.497834316054913</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.303528316051271</v>
+        <v>1.890578433070395</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.686380888044837</v>
+        <v>1.851241185290263</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.697977747739202</v>
+        <v>1.84124258817041</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.301255039518949</v>
+        <v>2.321405559874641</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.244799028485559</v>
+        <v>2.44933446955875</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.941031246670413</v>
+        <v>3.027178950786904</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.50892046767661</v>
+        <v>3.653588384242497</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.230171064228614</v>
+        <v>3.33856368917084</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.792611348009125</v>
+        <v>2.874129534386242</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4.25713482219917</v>
+        <v>3.37615729367382</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>4.774309839995688</v>
+        <v>4.037460515193317</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>4.878980797198238</v>
+        <v>4.167974274837867</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>4.451234081376484</v>
+        <v>3.731266469038211</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>4.346393377555302</v>
+        <v>3.46272049424492</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>3.974625600791093</v>
+        <v>3.145212610433013</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>3.573812253070571</v>
+        <v>2.727666466613691</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>3.423038856896909</v>
+        <v>2.915724033916391</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.053363316643534</v>
+        <v>2.405905690016304</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>3.425781222073681</v>
+        <v>3.009248854697901</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>3.252005775902312</v>
+        <v>2.809524427730871</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.0009012</t>
+          <t>X &gt; 0.0009154</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>842</v>
+        <v>826</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.584806093218859</v>
+        <v>1.933563748079884</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.250029294869044</v>
+        <v>1.092418817137919</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.237188393106464</v>
+        <v>1.028200905722521</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.2867046824523243</v>
+        <v>-0.1594393883237899</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.376092357173462</v>
+        <v>0.9935739001482986</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.919353080087944</v>
+        <v>1.388602744241616</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.147404396197594</v>
+        <v>0.7125683510565182</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.056841407501523</v>
+        <v>1.479076479076475</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.217093435021923</v>
+        <v>1.845100626855825</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.463180134282354</v>
+        <v>2.834763417350764</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.449828850078475</v>
+        <v>3.894074883513078</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.646138829053278</v>
+        <v>4.048452617954311</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.235565835831366</v>
+        <v>3.604498587716932</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.489546341807582</v>
+        <v>4.028807728538403</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>5.137816345889725</v>
+        <v>4.499849346997159</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>5.494673576621324</v>
+        <v>5.018074056808942</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>4.885697057221051</v>
+        <v>4.27077080832332</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>5.137150890216972</v>
+        <v>4.454455638428136</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>4.402923506295686</v>
+        <v>3.782879265185137</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.520885705812404</v>
+        <v>2.868328221661635</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.215869229057773</v>
+        <v>2.737176539325468</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.902493576437273</v>
+        <v>2.61626889636414</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.939438597707927</v>
+        <v>2.814047631565124</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.744841498878948</v>
+        <v>2.727007231629067</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.00115</t>
+          <t>X &gt; 0.001165</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.111365275948565</v>
+        <v>2.144227038506827</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4491548492801627</v>
+        <v>0.5689258158014923</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.9285399300426818</v>
+        <v>0.9390470758005947</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3630785359686755</v>
+        <v>0.05122390210315331</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.239677443952374</v>
+        <v>1.695902098783733</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.984165753943564</v>
+        <v>1.409704242447994</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.359709695421941</v>
+        <v>1.205464179993704</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.261439253618711</v>
+        <v>1.934517148697353</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.335374813114548</v>
+        <v>2.65328800815989</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.037385390765373</v>
+        <v>3.334341387386644</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.753922909033491</v>
+        <v>4.049707864324802</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.475173505585495</v>
+        <v>3.863806164719641</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.384459816310496</v>
+        <v>3.876900021408694</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.015888314495164</v>
+        <v>3.424687500804247</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.242700769127005</v>
+        <v>3.578067353777058</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>5.132072941807451</v>
+        <v>4.530963745058337</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.965707427248866</v>
+        <v>3.478561227024336</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>4.598329850271341</v>
+        <v>4.036114651057304</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>4.07675810435201</v>
+        <v>3.597787015855616</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.526140787476372</v>
+        <v>2.858227940296644</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.541116743404146</v>
+        <v>2.233327137126686</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.465270781995045</v>
+        <v>1.950385621785209</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3.182223370583294</v>
+        <v>3.038247793396543</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>2.516420615885096</v>
+        <v>2.367457653169943</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.0014</t>
+          <t>X &gt; 0.001415</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.215008742423883</v>
+        <v>2.651269142625488</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.880231944074069</v>
+        <v>2.405362306921617</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.8025732554034448</v>
+        <v>0.9711349913855187</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.9905201368616119</v>
+        <v>1.276398860799908</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.456531466116132</v>
+        <v>2.616639643501301</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.742596751312604</v>
+        <v>1.696373967632233</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.412089508863701</v>
+        <v>2.517090878200236</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.674418604651166</v>
+        <v>2.391703648436135</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.256446327106417</v>
+        <v>2.878698985409287</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.105152272691541</v>
+        <v>3.518913199346159</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.199031734673284</v>
+        <v>3.611615000305953</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.740102151045107</v>
+        <v>2.975966618545613</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.87820134545025</v>
+        <v>3.049028984904567</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.47694228882348</v>
+        <v>2.731769063078694</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3.719699892143829</v>
+        <v>3.063372120943853</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.593366093366093</v>
+        <v>3.014613534087871</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.099088596028267</v>
+        <v>2.479619565217384</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>3.714968612927798</v>
+        <v>3.18447448528002</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.210139273131411</v>
+        <v>2.78517660683265</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.775363461477809</v>
+        <v>1.108721488718928</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.8724569331514189</v>
+        <v>0.4681513308692402</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.07589025102159752</v>
+        <v>-0.4116656433739152</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>1.791806404945099</v>
+        <v>1.4053193183628</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>1.175433611181276</v>
+        <v>1.17092841695905</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.001649</t>
+          <t>X &gt; 0.001664</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.115909643324791</v>
+        <v>3.568484383000516</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.006358070200193</v>
+        <v>3.989244213963303</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.694465147295332</v>
+        <v>3.401216778738394</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.107637253978716</v>
+        <v>3.031036802152393</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.348423358008027</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.859713868429722</v>
+        <v>3.801301156940028</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.988666085440279</v>
+        <v>3.895108033596202</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.935679865912419</v>
+        <v>3.812409812409811</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.851040921700999</v>
+        <v>2.384783166538362</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.429476597015871</v>
+        <v>2.922065004652353</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.703536239177794</v>
+        <v>3.194300019256687</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.19956161050456</v>
+        <v>2.473273620340947</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.97730044454935</v>
+        <v>2.382880389304432</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.981446793327983</v>
+        <v>2.494076012885635</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>3.224204396648325</v>
+        <v>2.844100442122347</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>2.692465192465193</v>
+        <v>2.424274656867006</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.333322830262496</v>
+        <v>2.009012172284642</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.354608252567438</v>
+        <v>2.914694723667225</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.44437350736564</v>
+        <v>2.1408096870707</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.054642740757096</v>
+        <v>0.6838436771487366</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.9625470232415125</v>
+        <v>0.9315970497894028</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.4362506113819649</v>
+        <v>0.311701483101082</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.836851449990142</v>
+        <v>1.830444686540559</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.66192009766776</v>
+        <v>2.492615820084175</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.001898</t>
+          <t>X &gt; 0.001914</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.483806626180218</v>
+        <v>2.58816346262509</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.811079689326256</v>
+        <v>4.249613575150114</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.204085571043187</v>
+        <v>3.26739903729122</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.599164792597676</v>
+        <v>3.492435530581091</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.817390940549011</v>
+        <v>3.216877390481756</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.89632388564916</v>
+        <v>2.28389274034906</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.786425063254654</v>
+        <v>3.396167676345215</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.508213618501578</v>
+        <v>2.818767668903909</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.6106426286711368</v>
+        <v>0.7668600663264371</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.776785124379792</v>
+        <v>1.878165519335973</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.4968281460431</v>
+        <v>1.60544140587492</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.9410704323458035</v>
+        <v>0.7839003233382158</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.756966537234831</v>
+        <v>1.303885590083631</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.535887660788241</v>
+        <v>1.219437058943406</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.708769293955605</v>
+        <v>1.523883470530919</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>1.195122974901366</v>
+        <v>1.154132243226833</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.338214148173201</v>
+        <v>1.215995179063356</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>2.618414995598563</v>
+        <v>2.35474250625645</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.003281445774967</v>
+        <v>1.908823043498479</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.8050857044964559</v>
+        <v>0.6260256781542637</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.5395478467797332</v>
+        <v>0.7812676515491432</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0.1866935751213248</v>
+        <v>0.3155105232229616</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.7381765978526857</v>
+        <v>1.00669833150652</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>1.216360965128018</v>
+        <v>1.575525881137999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.002148</t>
+          <t>X &gt; 0.002164</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.30795834731888</v>
+        <v>2.310216081253948</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.362260047262588</v>
+        <v>5.408790850901255</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.630725639869823</v>
+        <v>4.82299307007991</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.306850118720597</v>
+        <v>6.237279834482386</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.336247359483906</v>
+        <v>6.630618015453287</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.158025832270702</v>
+        <v>5.784207139846018</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.068671005035647</v>
+        <v>5.992469609218652</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.107865703627276</v>
+        <v>4.68420468420468</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.442868243903753</v>
+        <v>2.805444630678089</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.693843352850202</v>
+        <v>3.012737617064104</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.602715281701535</v>
+        <v>1.947179989527967</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.300075093270614</v>
+        <v>0.3328053929161925</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.481790045257867</v>
+        <v>-0.7820867245345795</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.3210218632784816</v>
+        <v>-0.02697630436232856</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.004175494025574267</v>
+        <v>-0.1760337860655738</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.4253283690143732</v>
+        <v>-0.4248443357497393</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.4646452789910924</v>
+        <v>0.6827139639639697</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>1.383695360152842</v>
+        <v>1.430498663199977</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.9169928844218731</v>
+        <v>1.171076421303901</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.07994790940696106</v>
+        <v>0.2259498343924164</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.2199955980962329</v>
+        <v>0.8881093350688118</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.197147291640519</v>
+        <v>0.332788643363493</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.07732742084153443</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.6810986890370287</v>
+        <v>0.1360406356187696</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.002397</t>
+          <t>X &gt; 0.002414</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.865760816083451</v>
+        <v>2.440279254795385</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.412041286456109</v>
+        <v>3.476423701142792</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.617194043592519</v>
+        <v>4.785832163353781</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.98794046467841</v>
+        <v>6.75753252864812</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.652149992131136</v>
+        <v>5.627273533847934</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.839116178228515</v>
+        <v>6.211557567196444</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.507696128699394</v>
+        <v>6.271176409664577</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.026841512140152</v>
+        <v>3.829503829503821</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.746742790971162</v>
+        <v>1.8206806024358</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.735941652379594</v>
+        <v>2.734030816618166</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.688415391457816</v>
+        <v>1.724214549171222</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.40966598800982</v>
+        <v>1.0202821673495</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.7270325555149384</v>
+        <v>0.3327404772491533</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.5059536790683481</v>
+        <v>0.08450641581604401</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.7288676502102547</v>
+        <v>-0.3445391292691937</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.8793885996529127</v>
+        <v>-0.3900132664359219</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>2.070394703898245</v>
+        <v>2.35727813852813</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.727668537522</v>
+        <v>3.361228213678984</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2.621974015362625</v>
+        <v>2.539047190397561</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.6061766535244786</v>
+        <v>0.3921075494992863</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.385216388642149</v>
+        <v>1.847616908540537</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>1.749899061594284</v>
+        <v>2.043398989134857</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.583845139715102</v>
+        <v>2.560386473429958</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.1864269834081256</v>
+        <v>1.334755415648424</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.002646</t>
+          <t>X &gt; 0.002663</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>182</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.7547572821724273</v>
+        <v>2.186539938556066</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.068332132174262</v>
+        <v>4.544799769518868</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.08086253369272356</v>
+        <v>2.248439000960616</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.763512909854377</v>
+        <v>4.781036802152393</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.328821338406009</v>
+        <v>2.942978662053058</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.16413917285503</v>
+        <v>4.662412268051142</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.589992686766877</v>
+        <v>6.471496922485095</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3.663429593662158</v>
+        <v>3.562409812409804</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.704916775576862</v>
+        <v>3.169505388760584</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.580352747892015</v>
+        <v>3.935953893541246</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.755511291152843</v>
+        <v>3.687355574812244</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.026212437155394</v>
+        <v>2.889940287007612</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.001951469200371</v>
+        <v>3.33754816955684</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.231422043303233</v>
+        <v>2.568480774790402</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>3.122729295173222</v>
+        <v>2.731657981037984</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>2.618215118215119</v>
+        <v>2.568244446812727</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>6.87990237684204</v>
+        <v>6.493882275132272</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>7.873962771921967</v>
+        <v>7.241894263632716</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>6.441502504494629</v>
+        <v>6.207636499880792</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>4.97999666611102</v>
+        <v>4.622441448763581</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>5.536351597046085</v>
+        <v>6.01954213773449</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>6.559406734538079</v>
+        <v>6.843322036460755</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>5.734980348119038</v>
+        <v>6.356379187455452</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>4.560246995994667</v>
+        <v>5.455634536527548</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.002895</t>
+          <t>X &gt; 0.002913</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.001536992528293979</v>
+        <v>1.296082949308754</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.653515161065897</v>
+        <v>2.985659984572628</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2154961120349057</v>
+        <v>2.376127173003631</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.813800370737866</v>
+        <v>3.719208845163145</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.4912549313031747</v>
+        <v>0.8630055437734896</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.989479395546248</v>
+        <v>4.245745601384478</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.528788989801598</v>
+        <v>7.321631331087239</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.250577545048522</v>
+        <v>7.01671088767862</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.616568038221502</v>
+        <v>7.789801087685312</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>10.15491064033071</v>
+        <v>10.86471733440146</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.104466971234352</v>
+        <v>9.846629768360643</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.825717567786356</v>
+        <v>8.924886523566755</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.35156212344679</v>
+        <v>9.745478277083727</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.805979935741931</v>
+        <v>8.206921635005465</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>10.13459160504879</v>
+        <v>9.460251124088138</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>9.404475215733498</v>
+        <v>9.171115260209845</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>12.58181635690173</v>
+        <v>12.12724673202614</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>12.47697565308054</v>
+        <v>11.80516414045243</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>10.70611206711745</v>
+        <v>10.50341862971044</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>10.23070622145633</v>
+        <v>9.848247900376492</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>9.6881600534903</v>
+        <v>10.41279445044989</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>10.27456574771035</v>
+        <v>11.48492015631974</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>10.5490404601924</v>
+        <v>11.53090801538007</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>9.810956551339977</v>
+        <v>11.36876902109061</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.003145</t>
+          <t>X &gt; 0.003163</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>114</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.499503763761012</v>
+        <v>4.440566549200334</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4668519819572197</v>
+        <v>1.673651310135114</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.027678048532067</v>
+        <v>0.4189572082435333</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.617825050430952</v>
+        <v>-1.013781125018475</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.076422540522081</v>
+        <v>-1.28933926511781</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.250894522768277</v>
+        <v>4.749947282056745</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.356138821334071</v>
+        <v>5.63553753873159</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.586699306405549</v>
+        <v>7.851625498684314</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>10.25976543568868</v>
+        <v>9.660226677275979</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>13.87281467193289</v>
+        <v>13.06585585432556</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>13.26968133163867</v>
+        <v>12.4977547344761</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>13.86812491064681</v>
+        <v>12.22117278000481</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>14.49934880870297</v>
+        <v>11.94661679700783</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>16.03265589716867</v>
+        <v>13.37905500448228</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>14.49731961713197</v>
+        <v>11.85656448814344</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>14.21451355661881</v>
+        <v>11.57753237250932</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>16.71217536700978</v>
+        <v>14.6142302259887</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>15.73014168073244</v>
+        <v>14.25680606577858</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>15.06884007920063</v>
+        <v>14.24285685761635</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>14.37849290671251</v>
+        <v>14.22505949457938</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>13.83594673874648</v>
+        <v>14.29834725864487</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>14.63729375979353</v>
+        <v>15.10037771914573</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>14.91176847227558</v>
+        <v>15.34401220442411</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>14.83593621905231</v>
+        <v>15.18187321013465</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.003394</t>
+          <t>X &gt; 0.003412</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>7.183895154609267</v>
+        <v>9.083635898152032</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.725407016053268</v>
+        <v>4.79732502204412</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.287387967022276</v>
+        <v>2.532529910051529</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-2.5183495575751</v>
+        <v>-2.100276329160735</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2386434750322621</v>
+        <v>0.6544685610429539</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.549321001335827</v>
+        <v>4.851806207445087</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.808300152497026</v>
+        <v>6.076926215414389</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.622872212898585</v>
+        <v>8.802308802308801</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.75714289996793</v>
+        <v>10.95043973219493</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>14.10793856413763</v>
+        <v>14.19479227737962</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>13.35107037124801</v>
+        <v>13.45692628188296</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>14.10324880285155</v>
+        <v>12.17024331731065</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.01101457104698</v>
+        <v>11.05535119985988</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.85179136470349</v>
+        <v>12.82731915862878</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>14.16272023207139</v>
+        <v>12.14516477674372</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>14.75710715401438</v>
+        <v>11.69636778546239</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>14.6231900170369</v>
+        <v>11.59248737373738</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>13.48742147816417</v>
+        <v>11.16069582681119</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>13.70331285908849</v>
+        <v>12.10101540720754</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>12.85923083400498</v>
+        <v>12.01491456704316</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>11.2857568309874</v>
+        <v>11.14045252180277</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>12.24083870462984</v>
+        <v>13.17055315774223</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>13.54624125216344</v>
+        <v>13.4141876430206</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>14.50133683399172</v>
+        <v>14.3046802276785</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.003643</t>
+          <t>X &gt; 0.003662</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4.330167379321658</v>
+        <v>5.028801843317979</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.096839856334164</v>
+        <v>3.354323579042671</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-3.239729917334515</v>
+        <v>-0.7575133799917637</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-5.401959299096092</v>
+        <v>-2.77848700737141</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-1.389923684686842</v>
+        <v>-0.1969022903278912</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.695593226048217</v>
+        <v>4.245745601384478</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.9236445421578665</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>6.442534546680143</v>
+        <v>8.860028860028848</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>9.382572453232527</v>
+        <v>10.41652919828439</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>14.40675822647141</v>
+        <v>13.90619198877934</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>13.23154250631449</v>
+        <v>12.74985557481224</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>12.95279310286649</v>
+        <v>11.04470219176952</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>14.72818176064805</v>
+        <v>12.78695293146161</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>15.95637824652032</v>
+        <v>13.96729029859991</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>16.74751031125859</v>
+        <v>14.7137073452863</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>15.89262187088275</v>
+        <v>13.84643993553452</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>14.30942937158642</v>
+        <v>12.31398809523809</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>12.75531330544641</v>
+        <v>10.75253256150506</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>12.97120468637073</v>
+        <v>11.98148754227402</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>11.70877513401992</v>
+        <v>11.76981652782747</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>9.716953603735043</v>
+        <v>9.731783791152608</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>12.53965836696363</v>
+        <v>12.59779773978557</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>12.81413307944568</v>
+        <v>12.84143222506395</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>14.18757618854124</v>
+        <v>14.1498814660686</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2461 +5824,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.003585</t>
+          <t>X &lt; -0.003579</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.264035519229068</v>
+        <v>-6.399769585253459</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.149536955260039</v>
+        <v>-5.217104992385899</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.790454555015664</v>
+        <v>-0.7575133799917637</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-3.952683936777255</v>
+        <v>-2.77848700737141</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.755003851545041</v>
+        <v>9.803097709672102</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.695593226048217</v>
+        <v>2.817174172813054</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.372919904476703</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.094708459723627</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.6869202793194944</v>
+        <v>1.845100626855825</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.535270759035839</v>
+        <v>-0.379522296934951</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.261211116873916</v>
+        <v>-0.107287282330617</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.358590204315767</v>
+        <v>2.473273620340947</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-2.66312258717803</v>
+        <v>-1.498761354252686</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>4.362175347969576</v>
+        <v>5.395861727171358</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-3.542344761205179</v>
+        <v>-2.429149797570851</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-1.498682476943344</v>
+        <v>-0.4392743501797511</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-3.081874976239661</v>
+        <v>-1.971726190476197</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.2881649554231629</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>5.72482787477653</v>
+        <v>6.681280502936545</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>7.360949047063386</v>
+        <v>8.32443837656696</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>6.818402879097356</v>
+        <v>7.756993875186225</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>8.191832280007112</v>
+        <v>9.110402781802371</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>8.466306992489166</v>
+        <v>9.354037267080749</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>8.39047473926589</v>
+        <v>9.191898272791285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.003336</t>
+          <t>X &lt; -0.003329</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>84</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-7.212275684860536</v>
+        <v>-7.114055299539167</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.785147721305592</v>
+        <v>-2.598057373338278</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.5387379915681834</v>
+        <v>0.9091532866749077</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1742160278745573</v>
+        <v>0.3167510878666846</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9.013803023387695</v>
+        <v>9.565002471576875</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.248388257104118</v>
+        <v>3.769555125194003</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.476439573213767</v>
+        <v>2.974473112961284</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.198228128460691</v>
+        <v>2.669552669552665</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.239715310375395</v>
+        <v>2.797481579236774</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.466799634338905</v>
+        <v>2.001430084017436</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.931335466977011</v>
+        <v>3.464141289097952</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>3.843062254005211</v>
+        <v>4.378035525102852</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>1.529423996672897</v>
+        <v>2.072667217175884</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.260726072607255</v>
+        <v>7.776814108123723</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.650201822645748</v>
+        <v>1.142278773857718</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>2.435064935064936</v>
+        <v>2.894058983153577</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.07980458286491654</v>
+        <v>0.4092261904761898</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>2.196307094266281</v>
+        <v>2.657294466266968</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>7.174103237095359</v>
+        <v>7.633661455317494</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>7.360949047063386</v>
+        <v>7.848247900376478</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>8.00887906957356</v>
+        <v>8.471279589471948</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>7.205640877040459</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>7.017031630170308</v>
+        <v>7.449275362318836</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.003087</t>
+          <t>X &lt; -0.00308</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>97</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-8.280022371163923</v>
+        <v>-8.181801985842554</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.491087829307553</v>
+        <v>-4.30399748134024</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.867251208235459</v>
+        <v>-2.465908078077177</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.5183495575751</v>
+        <v>-3.0583102768854</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.362354815238447</v>
+        <v>4.913554263427628</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.4256096611296414</v>
+        <v>0.9467765292195267</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.3463390227607093</v>
+        <v>0.151694516986808</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.6245504675137852</v>
+        <v>-0.1532259264218112</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.5830632855990814</v>
+        <v>-0.0252970167377029</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.355978961635572</v>
+        <v>-0.8213485119570407</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.9799363506294512</v>
+        <v>1.512742172750393</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.76304261728454</v>
+        <v>3.298015888382182</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.670808385479972</v>
+        <v>4.244979441034502</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>6.57344084923956</v>
+        <v>7.089528884756028</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.760658376401274</v>
+        <v>1.252735327613244</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>2.385973133395815</v>
+        <v>2.844967181484456</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.221128161366792</v>
+        <v>2.741086769759448</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.11628745754561</v>
+        <v>2.608202664597847</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>5.455890178676121</v>
+        <v>6.946376231949799</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>5.642735988644148</v>
+        <v>7.160962677008783</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>6.13111765572966</v>
+        <v>7.624446010679591</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>6.05527169432056</v>
+        <v>6.518355653672764</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>5.29881857175107</v>
+        <v>6.761990138951141</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>6.253914153579338</v>
+        <v>7.63077897971322</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.002838</t>
+          <t>X &lt; -0.00283</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.478056415757543</v>
+        <v>-2.379836030436174</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.03763941565775</v>
+        <v>-1.850549067690437</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.925270867789521</v>
+        <v>-1.554855572682797</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.413418685681862</v>
+        <v>-2.92245156994062</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.5688625471972131</v>
+        <v>0.6779592822081</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.204893693924511</v>
+        <v>2.385280485105412</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3544565647689879</v>
+        <v>0.03981087597346544</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.6326680095220638</v>
+        <v>-0.2651095674351538</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1962207471957882</v>
+        <v>-0.1371806577510455</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.36409650364385</v>
+        <v>-1.708425951419997</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.272167862927517</v>
+        <v>0.8893904585331782</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.568221609085832</v>
+        <v>2.163196100961095</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.807264266639159</v>
+        <v>3.373885378859164</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.160988539798865</v>
+        <v>4.676038914325282</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.353238943005714</v>
+        <v>0.8931093386417714</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2.735027439751853</v>
+        <v>2.229607155911047</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.813708727971232</v>
+        <v>1.350532945736425</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.1340648745437534</v>
+        <v>-0.3327387563243889</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>2.712160979877524</v>
+        <v>2.207304866170212</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2.899006789845551</v>
+        <v>2.421891311229196</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>3.143862196682669</v>
+        <v>2.629640608298075</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>4.361604536735889</v>
+        <v>3.329671884792404</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>5.429730042868727</v>
+        <v>4.348500168520395</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>5.736748771130159</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.002588</t>
+          <t>X &lt; -0.00258</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.3864092436094779</v>
+        <v>-0.05425463508734651</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.785147721305592</v>
+        <v>-2.044347517302839</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.521427391950496</v>
+        <v>-0.3920648750083799</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.51213914893021</v>
+        <v>-2.14725777149102</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.310872301287638</v>
+        <v>-1.260025213915938</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1778602910956479</v>
+        <v>0.05969908975657034</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.559565072546974</v>
+        <v>-1.898173620150573</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.6182643221781063</v>
+        <v>-1.040303365884768</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.03297895729757272</v>
+        <v>-0.9123744562006593</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7399367187389174</v>
+        <v>-1.708425951419997</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.7536351185449561</v>
+        <v>-0.273400239141246</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.743178398023794</v>
+        <v>2.938389899410708</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.010260233606701</v>
+        <v>1.242102433122731</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.008693552282061</v>
+        <v>2.156659069364039</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.9115258644576016</v>
+        <v>-0.8510767078698436</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.505912786400593</v>
+        <v>-0.8711680378873936</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-1.067028740820788</v>
+        <v>-3.300629844961243</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.17186944464197</v>
+        <v>-3.433513950122844</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.8732902289652884</v>
+        <v>-1.474865676465441</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.060136038933315</v>
+        <v>-1.260279231406457</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.517589870967285</v>
+        <v>-1.827723732787192</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>2.039080435070673</v>
+        <v>-0.7400955570680523</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>3.540549012583405</v>
+        <v>1.24772497472194</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>4.691710624390801</v>
+        <v>2.248376678106901</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.002339</t>
+          <t>X &lt; -0.002331</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.964534052487323</v>
+        <v>2.652063537376129</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.429781493623622</v>
+        <v>1.767021991741089</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.6625117390933113</v>
+        <v>-0.5789419514203402</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.6915848379263068</v>
+        <v>0.8666122879520941</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.441722136238312</v>
+        <v>1.93634562767339</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.981459467239539</v>
+        <v>1.644848740397933</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.084067198302186</v>
+        <v>-1.84081623147604</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.65585662470663</v>
+        <v>-4.836319634525921</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.77950705747083</v>
+        <v>-3.363099245021182</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.093707137177049</v>
+        <v>-3.710720246966979</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.819647495015126</v>
+        <v>-3.438485232362645</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.406190257500185</v>
+        <v>1.666098732448575</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.11789057596517</v>
+        <v>2.344928588091967</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.89681169951858</v>
+        <v>2.096694526658858</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1.403806016616919</v>
+        <v>0.06924866495317161</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.6220461495690799</v>
+        <v>-0.71473879604779</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.02941341626133465</v>
+        <v>-1.267049701046339</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.0754272875598474</v>
+        <v>-1.39993380620794</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.057895286025037</v>
+        <v>-0.2886105925150773</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.244741095993064</v>
+        <v>-0.0740241474560932</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>2.363717779250969</v>
+        <v>0.7038228309837891</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2.575890251021598</v>
+        <v>1.077090802302052</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>4.07129519606179</v>
+        <v>3.114447260674602</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>3.065230384698978</v>
+        <v>2.503877773111597</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.00209</t>
+          <t>X &lt; -0.002081</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.345068379525785</v>
+        <v>3.009097409820441</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.561478561716456</v>
+        <v>2.958871280476195</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.09449402464255741</v>
+        <v>0.1651056676272873</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.524648571345914</v>
+        <v>1.855659334092003</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.180469690054352</v>
+        <v>2.973829416989183</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.072248984190644</v>
+        <v>1.040170688492488</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.491814395040201</v>
+        <v>-1.845503658235003</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.920563474201877</v>
+        <v>-4.589448491887516</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.086961596946679</v>
+        <v>-3.067791359206893</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.143031394846972</v>
+        <v>-3.166978742927981</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.585817630821246</v>
+        <v>-4.63690400706929</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.870199990820367</v>
+        <v>1.358291041943737</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.822306741168546</v>
+        <v>0.9402630359912223</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.959650803790062</v>
+        <v>1.040461030307235</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>2.301507506209504</v>
+        <v>0.3583066484221789</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.462202671880092</v>
+        <v>-0.474117555754674</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.9698625958345275</v>
+        <v>-0.9264300232288036</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.8650218920133455</v>
+        <v>-1.059314128390405</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.797759151073862</v>
+        <v>-0.1479877897463737</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.984604961041889</v>
+        <v>0.06659865531261033</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>3.461088730416307</v>
+        <v>0.8928823769283909</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>3.974807218530621</v>
+        <v>1.514583966471363</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>4.843118586692057</v>
+        <v>3.151946674746256</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>4.404967492889064</v>
+        <v>3.686671791955057</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.001841</t>
+          <t>X &lt; -0.001831</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.225074674277529</v>
+        <v>2.290706605222738</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.9263368725319481</v>
+        <v>1.086118246770496</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2043345672771153</v>
+        <v>0.2640349041263548</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.183262174674063</v>
+        <v>2.06745136797872</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.294674694089871</v>
+        <v>1.392182781903244</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1847697086317481</v>
+        <v>-0.417175746930134</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.933733586959391</v>
+        <v>-2.897651017589808</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.632399577167014</v>
+        <v>-4.607065843020898</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.602276031615951</v>
+        <v>-2.793743674909834</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.091100798561527</v>
+        <v>-3.308896293724672</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.817041156399604</v>
+        <v>-3.036661279120338</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.165573076516033</v>
+        <v>0.9002399124757758</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.178774646023555</v>
+        <v>0.9089433006429886</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.525877587758778</v>
+        <v>0.9416081156143647</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2.43591610836004</v>
+        <v>0.8212514865383014</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.7575757575757578</v>
+        <v>-0.5837366294734991</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.3395677115073781</v>
+        <v>-1.2494147940075</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.5188179167771025</v>
+        <v>-1.101400022764594</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.302891115883241</v>
+        <v>-0.325140042809835</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2.232743918858269</v>
+        <v>0.732143031462634</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>2.723164783859268</v>
+        <v>1.288294035699877</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>2.54007363211042</v>
+        <v>1.213131513744592</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>3.568755768101354</v>
+        <v>2.58036150464094</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>2.810555765035417</v>
+        <v>2.137323633946984</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.001591</t>
+          <t>X &lt; -0.001582</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.688266810618664</v>
+        <v>2.65572037932742</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.06441883778600754</v>
+        <v>0.04169417945675491</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.752626011660233</v>
+        <v>-0.8938500723450531</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.7125842414020127</v>
+        <v>-0.957875186759594</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.356004474079384</v>
+        <v>-1.952854671280278</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.90441913450924</v>
+        <v>-2.004254398615522</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.560190463416276</v>
+        <v>-3.216003077514905</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.052077121844562</v>
+        <v>-3.72925685425686</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.514863444203357</v>
+        <v>-2.351327944572759</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.074103906564638</v>
+        <v>-3.147379439792097</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.082095546453992</v>
+        <v>-4.125144425187756</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.224092813149859</v>
+        <v>-2.318393046325717</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.42417795692905</v>
+        <v>-1.34995183044316</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.2094440213252113</v>
+        <v>-0.9731858918762626</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.448699276255347</v>
+        <v>-1.238673607094654</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.991064491064492</v>
+        <v>-2.552369588274992</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.8429303459906805</v>
+        <v>-1.614583333333343</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.9477710498118626</v>
+        <v>-1.747467438494944</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.122821185813315</v>
+        <v>-0.6996718780158275</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.507986877184742</v>
+        <v>0.1399145670431565</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.954311319726841</v>
+        <v>0.6141367323290865</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.581266595107621</v>
+        <v>0.1223075437071373</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>1.988295997986413</v>
+        <v>0.5742753623188435</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.53371197593912</v>
+        <v>-0.8378636319706132</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.001342</t>
+          <t>X &lt; -0.001332</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>602</v>
+        <v>619</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.1050812253302524</v>
+        <v>0.5504711852120323</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.44707578780136</v>
+        <v>-0.7338711843932444</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.616257339897736</v>
+        <v>-3.030345218040992</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.116777012988734</v>
+        <v>-1.603371799998143</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.019764501983111</v>
+        <v>-2.9224965668107</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.401858048314601</v>
+        <v>-2.927113849342497</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.757896266385224</v>
+        <v>-4.045297638634992</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.378212974296204</v>
+        <v>-3.704014527924066</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.843304739749918</v>
+        <v>-3.091432952650294</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.958325678944306</v>
+        <v>-3.241280893750087</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.000055510466595</v>
+        <v>-4.26145298738485</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.620910177072481</v>
+        <v>-3.891831387736595</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.112493296560181</v>
+        <v>-2.42190928870918</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.169098488796251</v>
+        <v>-2.508592461612402</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.840399681113645</v>
+        <v>-2.22144151231813</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-3.219696969696969</v>
+        <v>-3.27564637879734</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-2.03782463299023</v>
+        <v>-2.24867057081314</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.142665336811412</v>
+        <v>-2.381554675974741</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.337703462520224</v>
+        <v>-1.682439783239303</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.06479352719402698</v>
+        <v>-0.4985480070010055</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.3170254686290477</v>
+        <v>-0.09668717720241204</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.009665085458678391</v>
+        <v>-0.4949514762174729</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.881044897168664</v>
+        <v>0.3948865631804566</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.09091579470301525</v>
+        <v>-0.5750068737584471</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.001093</t>
+          <t>X &lt; -0.001082</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>750</v>
+        <v>777</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.6382361473745277</v>
+        <v>-0.6014502575223588</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.341636983677198</v>
+        <v>-1.931939453699229</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.450292175472462</v>
+        <v>-3.120150742629122</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.391341410137557</v>
+        <v>-2.362202393397453</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.919080366188609</v>
+        <v>-3.083424508469655</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.055973172093054</v>
+        <v>-3.373302017663136</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.021054161122073</v>
+        <v>-4.554484415996242</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.965897600882428</v>
+        <v>-4.473304473304474</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.194384450901154</v>
+        <v>-3.830575048819853</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.103245028176033</v>
+        <v>-3.725725643138297</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.417870882229337</v>
+        <v>-4.354391529434857</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.961170550227592</v>
+        <v>-4.759673612606285</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.967930500681589</v>
+        <v>-3.686663542154868</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.924459112577928</v>
+        <v>-3.548797217487589</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.392126219682289</v>
+        <v>-2.943950312371356</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-3.120490620490621</v>
+        <v>-3.540947451852858</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.857582360642695</v>
+        <v>-3.258727477477485</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.433322535363345</v>
+        <v>-2.748110939138435</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.744219058710371</v>
+        <v>-2.276248454592405</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.5524019697358966</v>
+        <v>-1.032060979932389</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.04549451256350068</v>
+        <v>-0.5699044517120981</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.4826203872762775</v>
+        <v>-1.159867488467903</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.3953074732473496</v>
+        <v>-1.044933131889643</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.05880062305296</v>
+        <v>-1.721872640979626</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.0008436</t>
+          <t>X &lt; -0.0008325</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>943</v>
+        <v>971</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.9873611612987716</v>
+        <v>-1.288528367454852</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.267290578448446</v>
+        <v>-1.480841256122154</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.128971427966057</v>
+        <v>-2.476492552769699</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5942378988358854</v>
+        <v>-0.8565959487897103</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.916932907348247</v>
+        <v>-2.310364959346117</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.463705785533854</v>
+        <v>-1.892256458347752</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.968835919182141</v>
+        <v>-2.687338470580471</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.608600263273367</v>
+        <v>-3.095245525729567</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.40476577691787</v>
+        <v>-2.967316616045458</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.699867032327759</v>
+        <v>-3.248435052562435</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.577902928696709</v>
+        <v>-3.388146484919986</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.219594387598804</v>
+        <v>-3.767715051131759</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.132230138665449</v>
+        <v>-2.719888322032581</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.353309015112039</v>
+        <v>-2.762149159984752</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.748294417955748</v>
+        <v>-2.105477589243641</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.996012759170647</v>
+        <v>-2.471053076088246</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.393087790884962</v>
+        <v>-1.957013817370409</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.120467455384983</v>
+        <v>-1.574964863829642</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.8427744000354309</v>
+        <v>-1.360502636683869</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.1716099110499414</v>
+        <v>-0.6309831329225233</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.3345217156876998</v>
+        <v>-0.7864811873413586</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.8764907013593515</v>
+        <v>-1.273590156258543</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.175058765309906</v>
+        <v>-1.750861953163472</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.400971001278485</v>
+        <v>-1.913000947452936</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.0005944</t>
+          <t>X &lt; -0.0005828</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1153</v>
+        <v>1188</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.9554251185470619</v>
+        <v>-1.19756810164494</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.074600020996797</v>
+        <v>-1.148131216790162</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.78426635961722</v>
+        <v>-1.939200820068464</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.9983918520503821</v>
+        <v>-0.8077541298375266</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.800283090099619</v>
+        <v>-1.541440105453944</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.395284280404042</v>
+        <v>-1.338779209380867</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.948826677245286</v>
+        <v>-2.088056949568774</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.437073676652432</v>
+        <v>-2.561327561327566</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.262634985966322</v>
+        <v>-2.265048483293285</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.300996143766149</v>
+        <v>-2.471874389287038</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.064979482046446</v>
+        <v>-2.115464290507617</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.553954383975281</v>
+        <v>-2.392046244978914</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.820520632341491</v>
+        <v>-1.823436678928005</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.52480364315501</v>
+        <v>-1.229919898610277</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.063222565197236</v>
+        <v>-0.8177981862192283</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.330162085976035</v>
+        <v>-1.098245009150411</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.241545141157196</v>
+        <v>-1.286300505050505</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.209749029650062</v>
+        <v>-1.250834441861933</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.6842732741308879</v>
+        <v>-0.6996718780158275</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.7058904804502859</v>
+        <v>-0.7376106854821032</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.7652188048703366</v>
+        <v>-0.8000046818123252</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.222811047679706</v>
+        <v>-1.211867540467949</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.590709559893227</v>
+        <v>-1.557458644415163</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.876377957542694</v>
+        <v>-1.803772722879707</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.0003451</t>
+          <t>X &lt; -0.0003331</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1358</v>
+        <v>1393</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.5589036761585859</v>
+        <v>-0.6477017817203219</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.4197458276018082</v>
+        <v>-0.283526410738645</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.310520230239057</v>
+        <v>-1.070428811017429</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.676015584906672</v>
+        <v>-0.4780367413051039</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.480569270984603</v>
+        <v>-1.645955029703217</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.326367409354603</v>
+        <v>-1.23488567551653</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.131128144332102</v>
+        <v>-1.919042082061452</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.587972065902768</v>
+        <v>-2.439325052390387</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.43362010694252</v>
+        <v>-2.454971160653152</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.363579232536317</v>
+        <v>-2.389572548191232</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.829699699463553</v>
+        <v>-1.830187497693139</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.286845849587102</v>
+        <v>-2.034981943190992</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.686690539851284</v>
+        <v>-1.498761354252686</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.468852079063062</v>
+        <v>-1.316270361845163</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.249160702173974</v>
+        <v>-1.136974636048947</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.343781889169875</v>
+        <v>-1.29354570696367</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.77577527883561</v>
+        <v>-1.038488573821496</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.7641732855689369</v>
+        <v>-1.02779766103621</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.6517710597987332</v>
+        <v>-0.7415479249170076</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.862252127679632</v>
+        <v>-1.173049060618965</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.7740536479660705</v>
+        <v>-1.094405981238758</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.027050925448989</v>
+        <v>-1.384931030114359</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.003571754671484</v>
+        <v>-1.284871562782854</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.183493799292521</v>
+        <v>-1.447010557072318</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -9.584e-05</t>
+          <t>X &lt; -8.338e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1624</v>
+        <v>1659</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.7568155408757988</v>
+        <v>-0.7815222863338889</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.8772034986590569</v>
+        <v>-0.9356807109616199</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.431880042879641</v>
+        <v>-1.437458434936822</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.19958968098544</v>
+        <v>-1.09564189097248</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.171456229430902</v>
+        <v>-2.120574286202057</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.707820779494689</v>
+        <v>-1.87105150879011</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.568393716592105</v>
+        <v>-2.693914724101255</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.996313102665901</v>
+        <v>-3.026649862092903</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.165729356814239</v>
+        <v>-3.20010732974454</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.684604517065246</v>
+        <v>-2.670058764686608</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.193457272354514</v>
+        <v>-2.156714648213679</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.765856129974296</v>
+        <v>-1.649692021612033</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.631344898040943</v>
+        <v>-1.378206803318378</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.633602772761975</v>
+        <v>-1.385331762882892</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.460287198437271</v>
+        <v>-1.103049737293567</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.871657754010698</v>
+        <v>-1.506182125948285</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.357139551187018</v>
+        <v>-1.248398884870404</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.303546835035505</v>
+        <v>-1.260728439097711</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.297351643199292</v>
+        <v>-1.166820762886232</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.381884695770353</v>
+        <v>-1.434452521564445</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.520052355485717</v>
+        <v>-1.579956094675126</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.560026108141997</v>
+        <v>-1.775673167564719</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.618865805727118</v>
+        <v>-1.773147784154936</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.720541181345233</v>
+        <v>-1.814732227510099</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0001534</t>
+          <t>X &lt; 0.0001663</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1877</v>
+        <v>1907</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.167162902905652</v>
+        <v>-1.271086258136712</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.8950551914026335</v>
+        <v>-0.9149703454236615</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.409427997693705</v>
+        <v>-1.253368805277411</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.250476790482189</v>
+        <v>-0.9808181490331052</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.926522473899837</v>
+        <v>-1.698733792159395</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.027400158525985</v>
+        <v>-1.775196806992483</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.401118630637995</v>
+        <v>-2.122935153645514</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.756114939986972</v>
+        <v>-2.45174113098642</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.108618526330538</v>
+        <v>-2.872106654588478</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.79524362823318</v>
+        <v>-2.514513682057427</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.703585167943615</v>
+        <v>-2.399593822146329</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.529672122964215</v>
+        <v>-2.151791927640176</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.034437988799255</v>
+        <v>-1.53621734346536</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.278224642814038</v>
+        <v>-1.732013020000721</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.16376575802385</v>
+        <v>-1.522714858624106</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-2.440519250864078</v>
+        <v>-1.800424998168374</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.172616229816697</v>
+        <v>-1.537236715609154</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-2.353170689412238</v>
+        <v>-1.87987436036174</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-2.159938562408705</v>
+        <v>-1.665412133215966</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.208428943367224</v>
+        <v>-1.817894382441196</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.454646766292704</v>
+        <v>-2.17558534423096</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-2.446728163028432</v>
+        <v>-2.355624635981734</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.674129179201351</v>
+        <v>-2.426620460089822</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.666330369101622</v>
+        <v>-2.379005914788301</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0004027</t>
+          <t>X &lt; 0.000416</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2121</v>
+        <v>2167</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.7024142776110764</v>
+        <v>-0.7150405212140498</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.7325067862568204</v>
+        <v>-0.6606586788098667</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.7451088805139889</v>
+        <v>-0.6483818304552429</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7786287411149289</v>
+        <v>-0.4790921112914361</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.368929508877557</v>
+        <v>-0.9595528134574636</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.436711589286055</v>
+        <v>-1.007710619813672</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.528193149847397</v>
+        <v>-1.178197637219839</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.827219205362873</v>
+        <v>-1.319201503703354</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.087464999950981</v>
+        <v>-1.673259185920237</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.038274526472961</v>
+        <v>-1.684815988015437</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.019126442247781</v>
+        <v>-1.643314706682908</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.990438516204421</v>
+        <v>-1.596869434573676</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.680171286093113</v>
+        <v>-1.373505899047984</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.498854718883422</v>
+        <v>-1.160272493937491</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.942018163940425</v>
+        <v>-1.519399649242011</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-2.118828017137083</v>
+        <v>-1.742590323546487</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.614892302163163</v>
+        <v>-1.200416282110446</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.59844070612327</v>
+        <v>-1.194860147308958</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.496326364660668</v>
+        <v>-0.9803979201631847</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.61159997254444</v>
+        <v>-1.181132194993459</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.70325437137344</v>
+        <v>-1.425549469793665</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.704609042431066</v>
+        <v>-1.454565245094585</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.015327779191921</v>
+        <v>-1.718544973014183</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.922544140261813</v>
+        <v>-1.649950234031841</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.0006519</t>
+          <t>X &lt; 0.0006657</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2403</v>
+        <v>2444</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3844579955424337</v>
+        <v>-0.3424636624766748</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.449850715905491</v>
+        <v>-0.444324754679073</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.6281644129579931</v>
+        <v>-0.5348637326175165</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.4105425023355807</v>
+        <v>-0.2070584359428409</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.9710579730340072</v>
+        <v>-0.7866473757855204</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.132918168811969</v>
+        <v>-0.7705942678965627</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.138279041504852</v>
+        <v>-0.7667454831817082</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.393378005518329</v>
+        <v>-0.9670941396207198</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.370115718810482</v>
+        <v>-1.020806472180112</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.664788126955102</v>
+        <v>-1.262150307222527</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.905466803600092</v>
+        <v>-1.521830186235221</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.788407725290853</v>
+        <v>-1.389246837924198</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.604082927223416</v>
+        <v>-1.194809986471519</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.801299068986879</v>
+        <v>-1.402127517626404</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-2.020966147029675</v>
+        <v>-1.675116596729133</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-2.06612998504329</v>
+        <v>-1.727560532082961</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.885771783022996</v>
+        <v>-1.545025231860343</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.842120231832276</v>
+        <v>-1.432410155352549</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.685254459471629</v>
+        <v>-1.299780988763239</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.515937810712529</v>
+        <v>-1.126111073982493</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.452586314585091</v>
+        <v>-1.202557212024438</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.296251121119774</v>
+        <v>-0.9913040220320894</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.454959495730954</v>
+        <v>-1.238667900092501</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.381730294297235</v>
+        <v>-1.15530771271257</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.0009012</t>
+          <t>X &lt; 0.0009154</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2582</v>
+        <v>2623</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.512248265063441</v>
+        <v>-0.6170948132169798</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.4041953403532119</v>
+        <v>-0.348776817330247</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4001969369941065</v>
+        <v>-0.3283987683676415</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.09277684190040958</v>
+        <v>0.0509429768702816</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.445470882252998</v>
+        <v>-0.3175806986775314</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.6215751128592544</v>
+        <v>-0.4440145813334553</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.3717254719501213</v>
+        <v>-0.2279350399419187</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6666129580894093</v>
+        <v>-0.4733044733044807</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.7188265969535763</v>
+        <v>-0.5906572128654304</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.123265667590807</v>
+        <v>-0.9078159628572777</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.443836567154555</v>
+        <v>-1.245569510967393</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.508114454149137</v>
+        <v>-1.293405754420775</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.375374637011191</v>
+        <v>-1.150196461272998</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.458409729861877</v>
+        <v>-1.284057667197146</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.669641591369796</v>
+        <v>-1.432472056707056</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.786299286299283</v>
+        <v>-1.595529456110803</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.588936625021297</v>
+        <v>-1.356291301308943</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.671360529197329</v>
+        <v>-1.412926836131234</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.433035018284087</v>
+        <v>-1.198464608985461</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.146398207383626</v>
+        <v>-0.907629593587167</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.047490093178581</v>
+        <v>-0.8650855322534525</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.9457815756037888</v>
+        <v>-0.8258751986997765</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.9581909791986334</v>
+        <v>-0.8872349947786304</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.8951032308505376</v>
+        <v>-0.8587525632198236</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.00115</t>
+          <t>X &lt; 0.001165</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2746</v>
+        <v>2785</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.5169756797013818</v>
+        <v>-0.5193709141571148</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.1100169753655962</v>
+        <v>-0.1378535351816907</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.2275208068554235</v>
+        <v>-0.2276172109978489</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.08899755870815795</v>
+        <v>-0.01242069545983071</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5491867294754798</v>
+        <v>-0.4113671518726534</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4867092551279839</v>
+        <v>-0.3420680186872005</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3336529762924627</v>
+        <v>-0.2926135711207394</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.5551252041830139</v>
+        <v>-0.4697518327360584</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.8190453181063475</v>
+        <v>-0.6445195484478887</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.9917924981662765</v>
+        <v>-0.8102473507755832</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.16823477068673</v>
+        <v>-0.984435268993856</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.1001332983274</v>
+        <v>-0.9378574389050058</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.078224067993659</v>
+        <v>-0.9396436317597292</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.9879434968170244</v>
+        <v>-0.8288112659037949</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.044120189280612</v>
+        <v>-0.8646460786685637</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.263451508549551</v>
+        <v>-1.09328819988481</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.9766616911277666</v>
+        <v>-0.8381021843207677</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.132873415146783</v>
+        <v>-0.9709862894823686</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.004740819611278</v>
+        <v>-0.8642439905233132</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.8693539832396269</v>
+        <v>-0.6855641881932328</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.6267286838952373</v>
+        <v>-0.5348758349958658</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.6082436645533633</v>
+        <v>-0.4664117860355361</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.7854195286696282</v>
+        <v>-0.7254702989618238</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.6213157966387755</v>
+        <v>-0.5644495086911476</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.0014</t>
+          <t>X &lt; 0.001415</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2869</v>
+        <v>2904</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4250794785771959</v>
+        <v>-0.5066061449202053</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3609577063165474</v>
+        <v>-0.4597758424692344</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1541273898785107</v>
+        <v>-0.1856924786137029</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1902868383378902</v>
+        <v>-0.2441463480307533</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4720827436615167</v>
+        <v>-0.5006761530162152</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.334998682708175</v>
+        <v>-0.3247011340107093</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.463863367089175</v>
+        <v>-0.4819593053136941</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.5144895409294179</v>
+        <v>-0.458108298548467</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.626673963780874</v>
+        <v>-0.5515773425775663</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7902738506221993</v>
+        <v>-0.6744785450914677</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.8086268607715681</v>
+        <v>-0.6924852169261442</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.7204986788719268</v>
+        <v>-0.5708035146452772</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.7473617176128116</v>
+        <v>-0.5837672574403996</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6702684856884389</v>
+        <v>-0.5220839635016077</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.7173153023418308</v>
+        <v>-0.584403634642868</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.6931936676462271</v>
+        <v>-0.5740638031510272</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.5980508243378608</v>
+        <v>-0.4713326446280988</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.7171504626695366</v>
+        <v>-0.6042167497896997</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.6199120725775629</v>
+        <v>-0.5274955694758887</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.3429609192900145</v>
+        <v>-0.2096033392929399</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.1685980494077413</v>
+        <v>-0.08834260651389059</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.01467052919435474</v>
+        <v>0.0775417034867516</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.3464991479946065</v>
+        <v>-0.2642232602706898</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.2273843339859241</v>
+        <v>-0.219750684312217</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.001649</t>
+          <t>X &lt; 0.001664</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2980</v>
+        <v>3011</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4606939332787903</v>
+        <v>-0.5313759008438907</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.444644564679848</v>
+        <v>-0.594227042794941</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3986479591466647</v>
+        <v>-0.5068038246464468</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4599303135888491</v>
+        <v>-0.4517941573264608</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6437812507354295</v>
+        <v>-0.6096638164094941</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.571618731682058</v>
+        <v>-0.5669822739884012</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.5909134941393006</v>
+        <v>-0.5811666495750316</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.5832582978855498</v>
+        <v>-0.5690163899119156</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.422658487223778</v>
+        <v>-0.3560558808700307</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.5085796957498445</v>
+        <v>-0.4364186034163851</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.5494053091195923</v>
+        <v>-0.4772360586538866</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.4748012550347624</v>
+        <v>-0.3696357121067422</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4419663648879677</v>
+        <v>-0.3553348704077308</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.4427298917182583</v>
+        <v>-0.3710880284864757</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.4789383580166771</v>
+        <v>-0.4222228155525301</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.400085189241814</v>
+        <v>-0.359092161063657</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.3468347293728016</v>
+        <v>-0.2969147846783997</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.4988098004487398</v>
+        <v>-0.4297988898400007</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.3635852051156903</v>
+        <v>-0.3149713355603865</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.1569240539196244</v>
+        <v>-0.1003848905014024</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.1432688160641007</v>
+        <v>-0.1364444699293017</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.06495481940093839</v>
+        <v>-0.04554920377432126</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.2735867305587476</v>
+        <v>-0.2668765252046867</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.3966082293169393</v>
+        <v>-0.3625924042500372</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.001898</t>
+          <t>X &lt; 0.001914</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3063</v>
+        <v>3093</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1735755645013128</v>
+        <v>-0.3059117522651889</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.3289464401448328</v>
+        <v>-0.5024510895876659</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2580009374664627</v>
+        <v>-0.3864439080521649</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3043459260874997</v>
+        <v>-0.4131927271835139</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3300058823939551</v>
+        <v>-0.380713963981556</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2221917957544122</v>
+        <v>-0.2703834308735864</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.3265907298165445</v>
+        <v>-0.4021921707708032</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.2940776603699362</v>
+        <v>-0.3339211538049511</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.07161857990585929</v>
+        <v>-0.09087427973580731</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.2084561033152781</v>
+        <v>-0.2226378377249105</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.1756680626533011</v>
+        <v>-0.1903705964316984</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.1104801385615772</v>
+        <v>-0.09298365179868284</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.2063321144898467</v>
+        <v>-0.1547125805239844</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.1804280655856019</v>
+        <v>-0.1442980806897225</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.2008026416399602</v>
+        <v>-0.1798310594063324</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.1404882428978809</v>
+        <v>-0.135824163121427</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.1573600350131983</v>
+        <v>-0.1427113643711593</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.3079986358459053</v>
+        <v>-0.2755954695327603</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.2357185795061056</v>
+        <v>-0.2227885931790965</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.09476228866097358</v>
+        <v>-0.07286428843696768</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.06352797543623012</v>
+        <v>-0.0906805971245177</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.02198903119700191</v>
+        <v>-0.03651883844610637</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.08697185111775241</v>
+        <v>-0.1161950547519552</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.143358246298142</v>
+        <v>-0.1813408385661575</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.002148</t>
+          <t>X &lt; 0.002164</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3131</v>
+        <v>3160</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1215065934573332</v>
+        <v>-0.2176976389205549</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.3124459859968169</v>
+        <v>-0.5098450392243024</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3375008288330719</v>
+        <v>-0.454769765989866</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4934646413154979</v>
+        <v>-0.5883112525268857</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5893715797869135</v>
+        <v>-0.6256089575956238</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.4799306347587518</v>
+        <v>-0.5459210652821866</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.4717663927812765</v>
+        <v>-0.5657557351298905</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.382460963191221</v>
+        <v>-0.4423806697969752</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.2275144295816176</v>
+        <v>-0.2650325259313604</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2509685540175255</v>
+        <v>-0.284705609197907</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1493624610491509</v>
+        <v>-0.1840679155450076</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.02797391101758961</v>
+        <v>-0.03147021267613326</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.0449282250988432</v>
+        <v>0.07397783316540796</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.02994568797853958</v>
+        <v>0.002552504748209117</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.0003896241240397558</v>
+        <v>0.01660065450871429</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.03970092772259193</v>
+        <v>0.0399299897840848</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.04338466116774953</v>
+        <v>-0.06395042194092326</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1292389992109548</v>
+        <v>-0.1335433878620194</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.0856756744692504</v>
+        <v>-0.1089545784377677</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.007472005568189388</v>
+        <v>-0.02095041185980051</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.02056755272565169</v>
+        <v>-0.0820657993164815</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.01843733049813778</v>
+        <v>-0.03064604279076377</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.007234014784984311</v>
+        <v>-0.07182168409465106</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.06373743720467928</v>
+        <v>-0.01244169104234061</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.002397</t>
+          <t>X &lt; 0.002414</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3197</v>
+        <v>3225</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1315303432456361</v>
+        <v>-0.1763512494200441</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1700942441831543</v>
+        <v>-0.2513077374320147</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2551594306698277</v>
+        <v>-0.3460706817752666</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.422524863376438</v>
+        <v>-0.4887983343751614</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3989546169818965</v>
+        <v>-0.4071682148795333</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4122797425996581</v>
+        <v>-0.4495838140191708</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3890003177395016</v>
+        <v>-0.4540393811452645</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.2138478130270158</v>
+        <v>-0.2773456812454</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1234466418276625</v>
+        <v>-0.1319006999907089</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1934159934880668</v>
+        <v>-0.1981304462956501</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1193988454395338</v>
+        <v>-0.1249895305161317</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.09971772492309583</v>
+        <v>-0.07398389437859976</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.05144525875994077</v>
+        <v>-0.02413554608688884</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.03581274872107088</v>
+        <v>-0.006131628310377835</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.05160728527688718</v>
+        <v>0.02489228437821112</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.06228430955420095</v>
+        <v>0.02805676831415127</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.1466852677231358</v>
+        <v>-0.1688468992248033</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.2641838145543147</v>
+        <v>-0.2397155005104352</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.1858801066481277</v>
+        <v>-0.1802920330545916</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.04298722285225409</v>
+        <v>-0.02772109187157668</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.09826378756930154</v>
+        <v>-0.1300493141825427</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.124172268515764</v>
+        <v>-0.1431963322618515</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.1124242797733999</v>
+        <v>-0.1786316144253419</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.01323707389229156</v>
+        <v>-0.09270859321093639</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.002646</t>
+          <t>X &lt; 0.002663</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3242</v>
+        <v>3267</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.04207222828648582</v>
+        <v>-0.1279925817691279</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1153297941347233</v>
+        <v>-0.2661181932746715</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.004510260843417768</v>
+        <v>-0.1316962441075091</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2099814069875805</v>
+        <v>-0.2801217778496436</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1299740826709268</v>
+        <v>-0.1724822659078669</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2324764814293374</v>
+        <v>-0.2733383680811698</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3121751055512689</v>
+        <v>-0.3795135641775076</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.2046483075649164</v>
+        <v>-0.2089772942201975</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2070294298909872</v>
+        <v>-0.1859856462842444</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2560270884878193</v>
+        <v>-0.2310312282359845</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.2099855775698316</v>
+        <v>-0.2165052814568682</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.2251907386485215</v>
+        <v>-0.1697364744892766</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.2239026029494227</v>
+        <v>-0.1960860613693143</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1808483431368941</v>
+        <v>-0.150948365093285</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1748190500527542</v>
+        <v>-0.1597020735776695</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.1466200466200434</v>
+        <v>-0.1493622420858287</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.3853931156002659</v>
+        <v>-0.3756791398836867</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4412134311852824</v>
+        <v>-0.4167358804906485</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.3610574240277202</v>
+        <v>-0.3553192609359357</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.2792234729612559</v>
+        <v>-0.2631693019498016</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.3105134023612877</v>
+        <v>-0.3408678590391432</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.3680061731460924</v>
+        <v>-0.3854212594762174</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.3218521194442445</v>
+        <v>-0.3560506248253219</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.2560039954568225</v>
+        <v>-0.3039257684873036</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.002895</t>
+          <t>X &lt; 0.002913</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3273</v>
+        <v>3302</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-7.041440284183409e-05</v>
+        <v>-0.06056462379947192</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.07577565685006959</v>
+        <v>-0.1395588955394373</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.009878540654909784</v>
+        <v>-0.1111009688734654</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1290263759433401</v>
+        <v>-0.1739521336754066</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.02253326082223595</v>
+        <v>-0.04037605170083935</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1830481278418361</v>
+        <v>-0.1986988430599652</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.2996495858541195</v>
+        <v>-0.3427522972873902</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2869678349961404</v>
+        <v>-0.3285770959487024</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3497876440910659</v>
+        <v>-0.3648894435150254</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.4665018274079458</v>
+        <v>-0.5090783515212252</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4183732540037681</v>
+        <v>-0.4615142467783144</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.4056874741965686</v>
+        <v>-0.4184384183765388</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4759701219977117</v>
+        <v>-0.4570496620114852</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.405026795704245</v>
+        <v>-0.3850099435308252</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.4662776759178442</v>
+        <v>-0.4439415453326276</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.4328179693921825</v>
+        <v>-0.4275966545783589</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.5792238627720039</v>
+        <v>-0.5617525734181044</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.5745725293123343</v>
+        <v>-0.5432591430059901</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.4931735576981993</v>
+        <v>-0.4801744514339319</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.4714179552761451</v>
+        <v>-0.4472410490634147</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.4465543858598977</v>
+        <v>-0.4697264223787556</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.4737280695890931</v>
+        <v>-0.514613437219289</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.4865317988665367</v>
+        <v>-0.5131830088588742</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.4526289151397265</v>
+        <v>-0.5061202441248653</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.003145</t>
+          <t>X &lt; 0.003163</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3310</v>
+        <v>3335</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.08549157787841466</v>
+        <v>-0.1575983952743272</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01597272687367735</v>
+        <v>-0.05941661870706838</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.03517120910617422</v>
+        <v>-0.01487791936167326</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.0896192359607042</v>
+        <v>0.03601192653050589</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.07110608880130087</v>
+        <v>0.0458140855625615</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1456135743977214</v>
+        <v>-0.168830264804285</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1492635484316409</v>
+        <v>-0.2003671846755424</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.2600371981149152</v>
+        <v>-0.2792419110410762</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.3517633863664642</v>
+        <v>-0.3436672569793302</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4757824526475218</v>
+        <v>-0.4649631718495044</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4552343279587134</v>
+        <v>-0.4448796929113641</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4759079590047435</v>
+        <v>-0.4351644407003405</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4977192906329932</v>
+        <v>-0.4255155339251431</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.5505189073124157</v>
+        <v>-0.4766789058483312</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.4979495138153212</v>
+        <v>-0.4225609985292209</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.4883829250917842</v>
+        <v>-0.412740069601135</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.574370814543002</v>
+        <v>-0.516620481326143</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.5407829166476148</v>
+        <v>-0.4997142928987799</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.5182044552123202</v>
+        <v>-0.4949584767775619</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.4946132140510642</v>
+        <v>-0.4900784427431475</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.4760935491147293</v>
+        <v>-0.4883198284857713</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.5038198939059413</v>
+        <v>-0.515865465982202</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.513422411911634</v>
+        <v>-0.5243457407986583</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.5109657791456144</v>
+        <v>-0.5189605834948523</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.003394</t>
+          <t>X &lt; 0.003412</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3327</v>
+        <v>3354</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2080112925364475</v>
+        <v>-0.2666113115674662</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.07893833399737105</v>
+        <v>-0.1408467310742552</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.03729887479126859</v>
+        <v>-0.07437569299764846</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.07298473471311695</v>
+        <v>0.06169951234032567</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.006918235827292563</v>
+        <v>-0.01923193456314465</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1319235088578665</v>
+        <v>-0.1426154437461662</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1394752137536557</v>
+        <v>-0.1786800401918711</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.2211841473679783</v>
+        <v>-0.2588914353620311</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3122210835717709</v>
+        <v>-0.3221674690898411</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4095989346666755</v>
+        <v>-0.417742103287928</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3877406664703713</v>
+        <v>-0.3961450198948597</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4097080365009305</v>
+        <v>-0.3583742083324637</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.4071505132988449</v>
+        <v>-0.3256411094275862</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4607802704154054</v>
+        <v>-0.3779477966381677</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.4118057141819307</v>
+        <v>-0.3579551392967062</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.4292172095770326</v>
+        <v>-0.344830378427865</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.4254497395478722</v>
+        <v>-0.3418696008340731</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.3925232173363042</v>
+        <v>-0.3258111978038443</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.3989259745893037</v>
+        <v>-0.3496569837650085</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.3744657432898535</v>
+        <v>-0.3435900501745976</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.328744268049789</v>
+        <v>-0.3152645187879841</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.3566720800087424</v>
+        <v>-0.3728255512471819</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.3948273441886627</v>
+        <v>-0.3798354176116092</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.4227922070625709</v>
+        <v>-0.4051713242783066</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.003643</t>
+          <t>X &lt; 0.003662</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3355</v>
+        <v>3381</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.08844924487069505</v>
+        <v>-0.1034732889571544</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.02241100091414694</v>
+        <v>-0.06903929742222203</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.06621485909243319</v>
+        <v>0.01559586370571253</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1104400567815276</v>
+        <v>0.05722097396763814</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.02842463966905484</v>
+        <v>0.00405625671659493</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.0346860161865834</v>
+        <v>-0.08748960615157841</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.01890019970608137</v>
+        <v>-0.07112675242656508</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1318703303829452</v>
+        <v>-0.1826810074232839</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1921060828703318</v>
+        <v>-0.2148370783382276</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2950627241396546</v>
+        <v>-0.2868946181003693</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2710737627481308</v>
+        <v>-0.2631161233009678</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2654418544988957</v>
+        <v>-0.2279944421774829</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.3019145993715782</v>
+        <v>-0.2640373761658665</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3271887367042723</v>
+        <v>-0.2884952259964564</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.343513142531755</v>
+        <v>-0.3040022178778159</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.3260752034168632</v>
+        <v>-0.2861679348944222</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.2936795439141804</v>
+        <v>-0.2545715199842462</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2618615346848543</v>
+        <v>-0.2223566556293477</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2663729533808237</v>
+        <v>-0.2442312083949503</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2405196440153006</v>
+        <v>-0.236439445758414</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.1996634302137394</v>
+        <v>-0.19555593906572</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.2577409673281252</v>
+        <v>-0.2532220651213137</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.2634610198098173</v>
+        <v>-0.2581955621834169</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.2917862166942911</v>
+        <v>-0.2845879738812869</v>
       </c>
     </row>
   </sheetData>
